--- a/eduservices/SIMULATION_CORRIGE.xlsx
+++ b/eduservices/SIMULATION_CORRIGE.xlsx
@@ -11908,16 +11908,16 @@
         <v>112</v>
       </c>
       <c r="S13" s="74">
-        <f>IF($R13="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M13,$M13+SUMIFS($M$13:$M$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"Fermer")*$I13/SUMIFS($I$13:$I$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M13,$M13+SUMIFS($M$13:$M$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"Fermer")*$I13/SUMIFS($I$13:$I$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T13" s="75">
-        <f>IF($R13="Fermer","",$J13-$K13-$S13)</f>
+        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",$J13-$K13-$S13))</f>
       </c>
       <c r="U13" s="74">
-        <f>IF($R13="Fermer",-$L13,0)</f>
+        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer",-$L13,0))</f>
       </c>
       <c r="V13" s="76">
-        <f>IF($R13="Fermer","Fermer = perdre "&amp;TEXT($L13,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O13&gt;=0,$T13&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O13&lt;0,$L13&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O13&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P13,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q13,"0%")&amp;"."))))</f>
+        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","Fermer = perdre "&amp;TEXT($L13,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O13&gt;=0,$T13&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O13&lt;0,$L13&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O13&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P13,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q13,"0%")&amp;".")))))</f>
       </c>
       <c r="W13" s="77"/>
       <c r="X13" s="77"/>
@@ -11975,16 +11975,16 @@
         <v>115</v>
       </c>
       <c r="S14" s="74">
-        <f>IF($R14="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M14,$M14+SUMIFS($M$13:$M$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"Fermer")*$I14/SUMIFS($I$13:$I$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M14,$M14+SUMIFS($M$13:$M$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"Fermer")*$I14/SUMIFS($I$13:$I$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T14" s="75">
-        <f>IF($R14="Fermer","",$J14-$K14-$S14)</f>
+        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",$J14-$K14-$S14))</f>
       </c>
       <c r="U14" s="74">
-        <f>IF($R14="Fermer",-$L14,0)</f>
+        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer",-$L14,0))</f>
       </c>
       <c r="V14" s="76">
-        <f>IF($R14="Fermer","Fermer = perdre "&amp;TEXT($L14,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O14&gt;=0,$T14&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O14&lt;0,$L14&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O14&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P14,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q14,"0%")&amp;"."))))</f>
+        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","Fermer = perdre "&amp;TEXT($L14,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O14&gt;=0,$T14&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O14&lt;0,$L14&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O14&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P14,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q14,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -12037,16 +12037,16 @@
         <v>115</v>
       </c>
       <c r="S15" s="74">
-        <f>IF($R15="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M15,$M15+SUMIFS($M$13:$M$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"Fermer")*$I15/SUMIFS($I$13:$I$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M15,$M15+SUMIFS($M$13:$M$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"Fermer")*$I15/SUMIFS($I$13:$I$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T15" s="75">
-        <f>IF($R15="Fermer","",$J15-$K15-$S15)</f>
+        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",$J15-$K15-$S15))</f>
       </c>
       <c r="U15" s="74">
-        <f>IF($R15="Fermer",-$L15,0)</f>
+        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer",-$L15,0))</f>
       </c>
       <c r="V15" s="76">
-        <f>IF($R15="Fermer","Fermer = perdre "&amp;TEXT($L15,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O15&gt;=0,$T15&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O15&lt;0,$L15&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O15&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P15,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q15,"0%")&amp;"."))))</f>
+        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","Fermer = perdre "&amp;TEXT($L15,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O15&gt;=0,$T15&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O15&lt;0,$L15&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O15&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P15,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q15,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -12099,16 +12099,16 @@
         <v>112</v>
       </c>
       <c r="S16" s="74">
-        <f>IF($R16="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M16,$M16+SUMIFS($M$13:$M$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"Fermer")*$I16/SUMIFS($I$13:$I$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M16,$M16+SUMIFS($M$13:$M$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"Fermer")*$I16/SUMIFS($I$13:$I$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T16" s="75">
-        <f>IF($R16="Fermer","",$J16-$K16-$S16)</f>
+        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",$J16-$K16-$S16))</f>
       </c>
       <c r="U16" s="74">
-        <f>IF($R16="Fermer",-$L16,0)</f>
+        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer",-$L16,0))</f>
       </c>
       <c r="V16" s="76">
-        <f>IF($R16="Fermer","Fermer = perdre "&amp;TEXT($L16,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O16&gt;=0,$T16&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O16&lt;0,$L16&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O16&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P16,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q16,"0%")&amp;"."))))</f>
+        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","Fermer = perdre "&amp;TEXT($L16,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O16&gt;=0,$T16&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O16&lt;0,$L16&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O16&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P16,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q16,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -12161,16 +12161,16 @@
         <v>115</v>
       </c>
       <c r="S17" s="74">
-        <f>IF($R17="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M17,$M17+SUMIFS($M$13:$M$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"Fermer")*$I17/SUMIFS($I$13:$I$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M17,$M17+SUMIFS($M$13:$M$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"Fermer")*$I17/SUMIFS($I$13:$I$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T17" s="75">
-        <f>IF($R17="Fermer","",$J17-$K17-$S17)</f>
+        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",$J17-$K17-$S17))</f>
       </c>
       <c r="U17" s="74">
-        <f>IF($R17="Fermer",-$L17,0)</f>
+        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer",-$L17,0))</f>
       </c>
       <c r="V17" s="76">
-        <f>IF($R17="Fermer","Fermer = perdre "&amp;TEXT($L17,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O17&gt;=0,$T17&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O17&lt;0,$L17&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O17&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P17,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q17,"0%")&amp;"."))))</f>
+        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","Fermer = perdre "&amp;TEXT($L17,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O17&gt;=0,$T17&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O17&lt;0,$L17&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O17&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P17,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q17,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -12223,16 +12223,16 @@
         <v>115</v>
       </c>
       <c r="S18" s="74">
-        <f>IF($R18="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M18,$M18+SUMIFS($M$13:$M$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"Fermer")*$I18/SUMIFS($I$13:$I$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M18,$M18+SUMIFS($M$13:$M$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"Fermer")*$I18/SUMIFS($I$13:$I$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T18" s="75">
-        <f>IF($R18="Fermer","",$J18-$K18-$S18)</f>
+        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",$J18-$K18-$S18))</f>
       </c>
       <c r="U18" s="74">
-        <f>IF($R18="Fermer",-$L18,0)</f>
+        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer",-$L18,0))</f>
       </c>
       <c r="V18" s="76">
-        <f>IF($R18="Fermer","Fermer = perdre "&amp;TEXT($L18,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O18&gt;=0,$T18&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O18&lt;0,$L18&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O18&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P18,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q18,"0%")&amp;"."))))</f>
+        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","Fermer = perdre "&amp;TEXT($L18,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O18&gt;=0,$T18&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O18&lt;0,$L18&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O18&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P18,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q18,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -12285,16 +12285,16 @@
         <v>112</v>
       </c>
       <c r="S19" s="74">
-        <f>IF($R19="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M19,$M19+SUMIFS($M$13:$M$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"Fermer")*$I19/SUMIFS($I$13:$I$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M19,$M19+SUMIFS($M$13:$M$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"Fermer")*$I19/SUMIFS($I$13:$I$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T19" s="75">
-        <f>IF($R19="Fermer","",$J19-$K19-$S19)</f>
+        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",$J19-$K19-$S19))</f>
       </c>
       <c r="U19" s="74">
-        <f>IF($R19="Fermer",-$L19,0)</f>
+        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer",-$L19,0))</f>
       </c>
       <c r="V19" s="76">
-        <f>IF($R19="Fermer","Fermer = perdre "&amp;TEXT($L19,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O19&gt;=0,$T19&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O19&lt;0,$L19&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O19&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P19,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q19,"0%")&amp;"."))))</f>
+        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","Fermer = perdre "&amp;TEXT($L19,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O19&gt;=0,$T19&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O19&lt;0,$L19&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O19&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P19,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q19,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -12347,16 +12347,16 @@
         <v>115</v>
       </c>
       <c r="S20" s="74">
-        <f>IF($R20="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M20,$M20+SUMIFS($M$13:$M$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"Fermer")*$I20/SUMIFS($I$13:$I$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M20,$M20+SUMIFS($M$13:$M$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"Fermer")*$I20/SUMIFS($I$13:$I$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T20" s="75">
-        <f>IF($R20="Fermer","",$J20-$K20-$S20)</f>
+        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",$J20-$K20-$S20))</f>
       </c>
       <c r="U20" s="74">
-        <f>IF($R20="Fermer",-$L20,0)</f>
+        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer",-$L20,0))</f>
       </c>
       <c r="V20" s="76">
-        <f>IF($R20="Fermer","Fermer = perdre "&amp;TEXT($L20,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O20&gt;=0,$T20&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O20&lt;0,$L20&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O20&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P20,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q20,"0%")&amp;"."))))</f>
+        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","Fermer = perdre "&amp;TEXT($L20,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O20&gt;=0,$T20&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O20&lt;0,$L20&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O20&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P20,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q20,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -12409,16 +12409,16 @@
         <v>115</v>
       </c>
       <c r="S21" s="74">
-        <f>IF($R21="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M21,$M21+SUMIFS($M$13:$M$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"Fermer")*$I21/SUMIFS($I$13:$I$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M21,$M21+SUMIFS($M$13:$M$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"Fermer")*$I21/SUMIFS($I$13:$I$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T21" s="75">
-        <f>IF($R21="Fermer","",$J21-$K21-$S21)</f>
+        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",$J21-$K21-$S21))</f>
       </c>
       <c r="U21" s="74">
-        <f>IF($R21="Fermer",-$L21,0)</f>
+        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer",-$L21,0))</f>
       </c>
       <c r="V21" s="76">
-        <f>IF($R21="Fermer","Fermer = perdre "&amp;TEXT($L21,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O21&gt;=0,$T21&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O21&lt;0,$L21&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O21&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P21,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q21,"0%")&amp;"."))))</f>
+        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","Fermer = perdre "&amp;TEXT($L21,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O21&gt;=0,$T21&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O21&lt;0,$L21&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O21&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P21,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q21,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -12471,16 +12471,16 @@
         <v>112</v>
       </c>
       <c r="S22" s="74">
-        <f>IF($R22="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M22,$M22+SUMIFS($M$13:$M$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"Fermer")*$I22/SUMIFS($I$13:$I$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M22,$M22+SUMIFS($M$13:$M$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"Fermer")*$I22/SUMIFS($I$13:$I$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T22" s="75">
-        <f>IF($R22="Fermer","",$J22-$K22-$S22)</f>
+        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",$J22-$K22-$S22))</f>
       </c>
       <c r="U22" s="74">
-        <f>IF($R22="Fermer",-$L22,0)</f>
+        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer",-$L22,0))</f>
       </c>
       <c r="V22" s="76">
-        <f>IF($R22="Fermer","Fermer = perdre "&amp;TEXT($L22,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O22&gt;=0,$T22&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O22&lt;0,$L22&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O22&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P22,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q22,"0%")&amp;"."))))</f>
+        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","Fermer = perdre "&amp;TEXT($L22,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O22&gt;=0,$T22&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O22&lt;0,$L22&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O22&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P22,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q22,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -12533,16 +12533,16 @@
         <v>115</v>
       </c>
       <c r="S23" s="74">
-        <f>IF($R23="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M23,$M23+SUMIFS($M$13:$M$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"Fermer")*$I23/SUMIFS($I$13:$I$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M23,$M23+SUMIFS($M$13:$M$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"Fermer")*$I23/SUMIFS($I$13:$I$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T23" s="75">
-        <f>IF($R23="Fermer","",$J23-$K23-$S23)</f>
+        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",$J23-$K23-$S23))</f>
       </c>
       <c r="U23" s="74">
-        <f>IF($R23="Fermer",-$L23,0)</f>
+        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer",-$L23,0))</f>
       </c>
       <c r="V23" s="76">
-        <f>IF($R23="Fermer","Fermer = perdre "&amp;TEXT($L23,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O23&gt;=0,$T23&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O23&lt;0,$L23&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O23&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P23,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q23,"0%")&amp;"."))))</f>
+        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","Fermer = perdre "&amp;TEXT($L23,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O23&gt;=0,$T23&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O23&lt;0,$L23&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O23&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P23,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q23,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -12595,16 +12595,16 @@
         <v>115</v>
       </c>
       <c r="S24" s="74">
-        <f>IF($R24="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M24,$M24+SUMIFS($M$13:$M$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"Fermer")*$I24/SUMIFS($I$13:$I$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M24,$M24+SUMIFS($M$13:$M$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"Fermer")*$I24/SUMIFS($I$13:$I$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T24" s="75">
-        <f>IF($R24="Fermer","",$J24-$K24-$S24)</f>
+        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",$J24-$K24-$S24))</f>
       </c>
       <c r="U24" s="74">
-        <f>IF($R24="Fermer",-$L24,0)</f>
+        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer",-$L24,0))</f>
       </c>
       <c r="V24" s="76">
-        <f>IF($R24="Fermer","Fermer = perdre "&amp;TEXT($L24,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O24&gt;=0,$T24&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O24&lt;0,$L24&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O24&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P24,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q24,"0%")&amp;"."))))</f>
+        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","Fermer = perdre "&amp;TEXT($L24,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O24&gt;=0,$T24&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O24&lt;0,$L24&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O24&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P24,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q24,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
@@ -12657,16 +12657,16 @@
         <v>112</v>
       </c>
       <c r="S25" s="74">
-        <f>IF($R25="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M25,$M25+SUMIFS($M$13:$M$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"Fermer")*$I25/SUMIFS($I$13:$I$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M25,$M25+SUMIFS($M$13:$M$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"Fermer")*$I25/SUMIFS($I$13:$I$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T25" s="75">
-        <f>IF($R25="Fermer","",$J25-$K25-$S25)</f>
+        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",$J25-$K25-$S25))</f>
       </c>
       <c r="U25" s="74">
-        <f>IF($R25="Fermer",-$L25,0)</f>
+        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer",-$L25,0))</f>
       </c>
       <c r="V25" s="76">
-        <f>IF($R25="Fermer","Fermer = perdre "&amp;TEXT($L25,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O25&gt;=0,$T25&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O25&lt;0,$L25&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O25&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P25,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q25,"0%")&amp;"."))))</f>
+        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","Fermer = perdre "&amp;TEXT($L25,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O25&gt;=0,$T25&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O25&lt;0,$L25&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O25&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P25,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q25,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -12719,16 +12719,16 @@
         <v>115</v>
       </c>
       <c r="S26" s="74">
-        <f>IF($R26="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M26,$M26+SUMIFS($M$13:$M$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"Fermer")*$I26/SUMIFS($I$13:$I$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M26,$M26+SUMIFS($M$13:$M$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"Fermer")*$I26/SUMIFS($I$13:$I$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T26" s="75">
-        <f>IF($R26="Fermer","",$J26-$K26-$S26)</f>
+        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",$J26-$K26-$S26))</f>
       </c>
       <c r="U26" s="74">
-        <f>IF($R26="Fermer",-$L26,0)</f>
+        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer",-$L26,0))</f>
       </c>
       <c r="V26" s="76">
-        <f>IF($R26="Fermer","Fermer = perdre "&amp;TEXT($L26,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O26&gt;=0,$T26&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O26&lt;0,$L26&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O26&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P26,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q26,"0%")&amp;"."))))</f>
+        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","Fermer = perdre "&amp;TEXT($L26,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O26&gt;=0,$T26&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O26&lt;0,$L26&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O26&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P26,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q26,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -12781,16 +12781,16 @@
         <v>112</v>
       </c>
       <c r="S27" s="74">
-        <f>IF($R27="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M27,$M27+SUMIFS($M$13:$M$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"Fermer")*$I27/SUMIFS($I$13:$I$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M27,$M27+SUMIFS($M$13:$M$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"Fermer")*$I27/SUMIFS($I$13:$I$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T27" s="75">
-        <f>IF($R27="Fermer","",$J27-$K27-$S27)</f>
+        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",$J27-$K27-$S27))</f>
       </c>
       <c r="U27" s="74">
-        <f>IF($R27="Fermer",-$L27,0)</f>
+        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer",-$L27,0))</f>
       </c>
       <c r="V27" s="76">
-        <f>IF($R27="Fermer","Fermer = perdre "&amp;TEXT($L27,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O27&gt;=0,$T27&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O27&lt;0,$L27&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O27&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P27,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q27,"0%")&amp;"."))))</f>
+        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","Fermer = perdre "&amp;TEXT($L27,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O27&gt;=0,$T27&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O27&lt;0,$L27&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O27&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P27,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q27,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
@@ -12843,16 +12843,16 @@
         <v>115</v>
       </c>
       <c r="S28" s="74">
-        <f>IF($R28="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M28,$M28+SUMIFS($M$13:$M$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"Fermer")*$I28/SUMIFS($I$13:$I$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M28,$M28+SUMIFS($M$13:$M$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"Fermer")*$I28/SUMIFS($I$13:$I$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T28" s="75">
-        <f>IF($R28="Fermer","",$J28-$K28-$S28)</f>
+        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",$J28-$K28-$S28))</f>
       </c>
       <c r="U28" s="74">
-        <f>IF($R28="Fermer",-$L28,0)</f>
+        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer",-$L28,0))</f>
       </c>
       <c r="V28" s="76">
-        <f>IF($R28="Fermer","Fermer = perdre "&amp;TEXT($L28,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O28&gt;=0,$T28&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O28&lt;0,$L28&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O28&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P28,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q28,"0%")&amp;"."))))</f>
+        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","Fermer = perdre "&amp;TEXT($L28,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O28&gt;=0,$T28&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O28&lt;0,$L28&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O28&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P28,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q28,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -12905,16 +12905,16 @@
         <v>115</v>
       </c>
       <c r="S29" s="74">
-        <f>IF($R29="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M29,$M29+SUMIFS($M$13:$M$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"Fermer")*$I29/SUMIFS($I$13:$I$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M29,$M29+SUMIFS($M$13:$M$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"Fermer")*$I29/SUMIFS($I$13:$I$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T29" s="75">
-        <f>IF($R29="Fermer","",$J29-$K29-$S29)</f>
+        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",$J29-$K29-$S29))</f>
       </c>
       <c r="U29" s="74">
-        <f>IF($R29="Fermer",-$L29,0)</f>
+        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer",-$L29,0))</f>
       </c>
       <c r="V29" s="76">
-        <f>IF($R29="Fermer","Fermer = perdre "&amp;TEXT($L29,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O29&gt;=0,$T29&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O29&lt;0,$L29&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O29&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P29,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q29,"0%")&amp;"."))))</f>
+        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","Fermer = perdre "&amp;TEXT($L29,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O29&gt;=0,$T29&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O29&lt;0,$L29&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O29&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P29,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q29,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
@@ -12967,16 +12967,16 @@
         <v>112</v>
       </c>
       <c r="S30" s="74">
-        <f>IF($R30="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M30,$M30+SUMIFS($M$13:$M$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"Fermer")*$I30/SUMIFS($I$13:$I$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M30,$M30+SUMIFS($M$13:$M$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"Fermer")*$I30/SUMIFS($I$13:$I$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T30" s="75">
-        <f>IF($R30="Fermer","",$J30-$K30-$S30)</f>
+        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",$J30-$K30-$S30))</f>
       </c>
       <c r="U30" s="74">
-        <f>IF($R30="Fermer",-$L30,0)</f>
+        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer",-$L30,0))</f>
       </c>
       <c r="V30" s="76">
-        <f>IF($R30="Fermer","Fermer = perdre "&amp;TEXT($L30,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O30&gt;=0,$T30&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O30&lt;0,$L30&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O30&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P30,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q30,"0%")&amp;"."))))</f>
+        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","Fermer = perdre "&amp;TEXT($L30,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O30&gt;=0,$T30&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O30&lt;0,$L30&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O30&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P30,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q30,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
@@ -13029,16 +13029,16 @@
         <v>115</v>
       </c>
       <c r="S31" s="74">
-        <f>IF($R31="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M31,$M31+SUMIFS($M$13:$M$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"Fermer")*$I31/SUMIFS($I$13:$I$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M31,$M31+SUMIFS($M$13:$M$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"Fermer")*$I31/SUMIFS($I$13:$I$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T31" s="75">
-        <f>IF($R31="Fermer","",$J31-$K31-$S31)</f>
+        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",$J31-$K31-$S31))</f>
       </c>
       <c r="U31" s="74">
-        <f>IF($R31="Fermer",-$L31,0)</f>
+        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer",-$L31,0))</f>
       </c>
       <c r="V31" s="76">
-        <f>IF($R31="Fermer","Fermer = perdre "&amp;TEXT($L31,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O31&gt;=0,$T31&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O31&lt;0,$L31&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O31&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P31,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q31,"0%")&amp;"."))))</f>
+        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","Fermer = perdre "&amp;TEXT($L31,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O31&gt;=0,$T31&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O31&lt;0,$L31&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O31&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P31,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q31,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -13091,16 +13091,16 @@
         <v>112</v>
       </c>
       <c r="S32" s="74">
-        <f>IF($R32="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M32,$M32+SUMIFS($M$13:$M$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"Fermer")*$I32/SUMIFS($I$13:$I$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M32,$M32+SUMIFS($M$13:$M$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"Fermer")*$I32/SUMIFS($I$13:$I$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T32" s="75">
-        <f>IF($R32="Fermer","",$J32-$K32-$S32)</f>
+        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",$J32-$K32-$S32))</f>
       </c>
       <c r="U32" s="74">
-        <f>IF($R32="Fermer",-$L32,0)</f>
+        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer",-$L32,0))</f>
       </c>
       <c r="V32" s="76">
-        <f>IF($R32="Fermer","Fermer = perdre "&amp;TEXT($L32,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O32&gt;=0,$T32&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O32&lt;0,$L32&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O32&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P32,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q32,"0%")&amp;"."))))</f>
+        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","Fermer = perdre "&amp;TEXT($L32,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O32&gt;=0,$T32&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O32&lt;0,$L32&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O32&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P32,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q32,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -13153,16 +13153,16 @@
         <v>115</v>
       </c>
       <c r="S33" s="74">
-        <f>IF($R33="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M33,$M33+SUMIFS($M$13:$M$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"Fermer")*$I33/SUMIFS($I$13:$I$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M33,$M33+SUMIFS($M$13:$M$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"Fermer")*$I33/SUMIFS($I$13:$I$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T33" s="75">
-        <f>IF($R33="Fermer","",$J33-$K33-$S33)</f>
+        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",$J33-$K33-$S33))</f>
       </c>
       <c r="U33" s="74">
-        <f>IF($R33="Fermer",-$L33,0)</f>
+        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer",-$L33,0))</f>
       </c>
       <c r="V33" s="76">
-        <f>IF($R33="Fermer","Fermer = perdre "&amp;TEXT($L33,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O33&gt;=0,$T33&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O33&lt;0,$L33&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O33&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P33,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q33,"0%")&amp;"."))))</f>
+        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","Fermer = perdre "&amp;TEXT($L33,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O33&gt;=0,$T33&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O33&lt;0,$L33&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O33&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P33,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q33,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -13215,16 +13215,16 @@
         <v>115</v>
       </c>
       <c r="S34" s="74">
-        <f>IF($R34="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M34,$M34+SUMIFS($M$13:$M$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"Fermer")*$I34/SUMIFS($I$13:$I$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M34,$M34+SUMIFS($M$13:$M$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"Fermer")*$I34/SUMIFS($I$13:$I$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T34" s="75">
-        <f>IF($R34="Fermer","",$J34-$K34-$S34)</f>
+        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",$J34-$K34-$S34))</f>
       </c>
       <c r="U34" s="74">
-        <f>IF($R34="Fermer",-$L34,0)</f>
+        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer",-$L34,0))</f>
       </c>
       <c r="V34" s="76">
-        <f>IF($R34="Fermer","Fermer = perdre "&amp;TEXT($L34,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O34&gt;=0,$T34&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O34&lt;0,$L34&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O34&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P34,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q34,"0%")&amp;"."))))</f>
+        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","Fermer = perdre "&amp;TEXT($L34,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O34&gt;=0,$T34&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O34&lt;0,$L34&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O34&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P34,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q34,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
@@ -13277,16 +13277,16 @@
         <v>112</v>
       </c>
       <c r="S35" s="74">
-        <f>IF($R35="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M35,$M35+SUMIFS($M$13:$M$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"Fermer")*$I35/SUMIFS($I$13:$I$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M35,$M35+SUMIFS($M$13:$M$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"Fermer")*$I35/SUMIFS($I$13:$I$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T35" s="75">
-        <f>IF($R35="Fermer","",$J35-$K35-$S35)</f>
+        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",$J35-$K35-$S35))</f>
       </c>
       <c r="U35" s="74">
-        <f>IF($R35="Fermer",-$L35,0)</f>
+        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer",-$L35,0))</f>
       </c>
       <c r="V35" s="76">
-        <f>IF($R35="Fermer","Fermer = perdre "&amp;TEXT($L35,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O35&gt;=0,$T35&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O35&lt;0,$L35&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O35&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P35,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q35,"0%")&amp;"."))))</f>
+        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","Fermer = perdre "&amp;TEXT($L35,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O35&gt;=0,$T35&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O35&lt;0,$L35&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O35&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P35,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q35,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -13339,16 +13339,16 @@
         <v>115</v>
       </c>
       <c r="S36" s="74">
-        <f>IF($R36="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M36,$M36+SUMIFS($M$13:$M$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"Fermer")*$I36/SUMIFS($I$13:$I$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M36,$M36+SUMIFS($M$13:$M$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"Fermer")*$I36/SUMIFS($I$13:$I$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T36" s="75">
-        <f>IF($R36="Fermer","",$J36-$K36-$S36)</f>
+        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",$J36-$K36-$S36))</f>
       </c>
       <c r="U36" s="74">
-        <f>IF($R36="Fermer",-$L36,0)</f>
+        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer",-$L36,0))</f>
       </c>
       <c r="V36" s="76">
-        <f>IF($R36="Fermer","Fermer = perdre "&amp;TEXT($L36,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O36&gt;=0,$T36&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O36&lt;0,$L36&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O36&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P36,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q36,"0%")&amp;"."))))</f>
+        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","Fermer = perdre "&amp;TEXT($L36,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O36&gt;=0,$T36&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O36&lt;0,$L36&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O36&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P36,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q36,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -13401,16 +13401,16 @@
         <v>112</v>
       </c>
       <c r="S37" s="74">
-        <f>IF($R37="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M37,$M37+SUMIFS($M$13:$M$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"Fermer")*$I37/SUMIFS($I$13:$I$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M37,$M37+SUMIFS($M$13:$M$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"Fermer")*$I37/SUMIFS($I$13:$I$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T37" s="75">
-        <f>IF($R37="Fermer","",$J37-$K37-$S37)</f>
+        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",$J37-$K37-$S37))</f>
       </c>
       <c r="U37" s="74">
-        <f>IF($R37="Fermer",-$L37,0)</f>
+        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer",-$L37,0))</f>
       </c>
       <c r="V37" s="76">
-        <f>IF($R37="Fermer","Fermer = perdre "&amp;TEXT($L37,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O37&gt;=0,$T37&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O37&lt;0,$L37&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O37&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P37,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q37,"0%")&amp;"."))))</f>
+        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","Fermer = perdre "&amp;TEXT($L37,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O37&gt;=0,$T37&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O37&lt;0,$L37&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O37&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P37,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q37,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -13464,16 +13464,16 @@
         <v>115</v>
       </c>
       <c r="S38" s="74">
-        <f>IF($R38="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M38,$M38+SUMIFS($M$13:$M$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"Fermer")*$I38/SUMIFS($I$13:$I$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M38,$M38+SUMIFS($M$13:$M$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"Fermer")*$I38/SUMIFS($I$13:$I$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T38" s="75">
-        <f>IF($R38="Fermer","",$J38-$K38-$S38)</f>
+        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",$J38-$K38-$S38))</f>
       </c>
       <c r="U38" s="74">
-        <f>IF($R38="Fermer",-$L38,0)</f>
+        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer",-$L38,0))</f>
       </c>
       <c r="V38" s="76">
-        <f>IF($R38="Fermer","Fermer = perdre "&amp;TEXT($L38,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O38&gt;=0,$T38&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O38&lt;0,$L38&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O38&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P38,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q38,"0%")&amp;"."))))</f>
+        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","Fermer = perdre "&amp;TEXT($L38,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O38&gt;=0,$T38&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O38&lt;0,$L38&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O38&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P38,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q38,"0%")&amp;".")))))</f>
       </c>
       <c r="W38" s="47"/>
       <c r="X38" s="47"/>
@@ -13536,16 +13536,16 @@
         <v>115</v>
       </c>
       <c r="S39" s="74">
-        <f>IF($R39="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M39,$M39+SUMIFS($M$13:$M$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"Fermer")*$I39/SUMIFS($I$13:$I$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M39,$M39+SUMIFS($M$13:$M$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"Fermer")*$I39/SUMIFS($I$13:$I$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T39" s="75">
-        <f>IF($R39="Fermer","",$J39-$K39-$S39)</f>
+        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",$J39-$K39-$S39))</f>
       </c>
       <c r="U39" s="74">
-        <f>IF($R39="Fermer",-$L39,0)</f>
+        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer",-$L39,0))</f>
       </c>
       <c r="V39" s="76">
-        <f>IF($R39="Fermer","Fermer = perdre "&amp;TEXT($L39,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O39&gt;=0,$T39&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O39&lt;0,$L39&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O39&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P39,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q39,"0%")&amp;"."))))</f>
+        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","Fermer = perdre "&amp;TEXT($L39,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O39&gt;=0,$T39&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O39&lt;0,$L39&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O39&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P39,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q39,"0%")&amp;".")))))</f>
       </c>
       <c r="W39" s="47"/>
       <c r="X39" s="47"/>
@@ -13608,16 +13608,16 @@
         <v>112</v>
       </c>
       <c r="S40" s="74">
-        <f>IF($R40="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M40,$M40+SUMIFS($M$13:$M$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"Fermer")*$I40/SUMIFS($I$13:$I$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M40,$M40+SUMIFS($M$13:$M$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"Fermer")*$I40/SUMIFS($I$13:$I$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T40" s="75">
-        <f>IF($R40="Fermer","",$J40-$K40-$S40)</f>
+        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",$J40-$K40-$S40))</f>
       </c>
       <c r="U40" s="74">
-        <f>IF($R40="Fermer",-$L40,0)</f>
+        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer",-$L40,0))</f>
       </c>
       <c r="V40" s="76">
-        <f>IF($R40="Fermer","Fermer = perdre "&amp;TEXT($L40,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O40&gt;=0,$T40&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O40&lt;0,$L40&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O40&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P40,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q40,"0%")&amp;"."))))</f>
+        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","Fermer = perdre "&amp;TEXT($L40,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O40&gt;=0,$T40&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O40&lt;0,$L40&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O40&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P40,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q40,"0%")&amp;".")))))</f>
       </c>
       <c r="W40" s="47"/>
       <c r="X40" s="47"/>
@@ -13680,16 +13680,16 @@
         <v>115</v>
       </c>
       <c r="S41" s="74">
-        <f>IF($R41="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M41,$M41+SUMIFS($M$13:$M$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"Fermer")*$I41/SUMIFS($I$13:$I$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M41,$M41+SUMIFS($M$13:$M$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"Fermer")*$I41/SUMIFS($I$13:$I$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T41" s="75">
-        <f>IF($R41="Fermer","",$J41-$K41-$S41)</f>
+        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",$J41-$K41-$S41))</f>
       </c>
       <c r="U41" s="74">
-        <f>IF($R41="Fermer",-$L41,0)</f>
+        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer",-$L41,0))</f>
       </c>
       <c r="V41" s="76">
-        <f>IF($R41="Fermer","Fermer = perdre "&amp;TEXT($L41,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O41&gt;=0,$T41&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O41&lt;0,$L41&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O41&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P41,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q41,"0%")&amp;"."))))</f>
+        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","Fermer = perdre "&amp;TEXT($L41,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O41&gt;=0,$T41&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O41&lt;0,$L41&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O41&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P41,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q41,"0%")&amp;".")))))</f>
       </c>
       <c r="W41" s="47"/>
       <c r="X41" s="47"/>
@@ -13752,16 +13752,16 @@
         <v>112</v>
       </c>
       <c r="S42" s="74">
-        <f>IF($R42="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M42,$M42+SUMIFS($M$13:$M$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"Fermer")*$I42/SUMIFS($I$13:$I$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M42,$M42+SUMIFS($M$13:$M$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"Fermer")*$I42/SUMIFS($I$13:$I$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T42" s="75">
-        <f>IF($R42="Fermer","",$J42-$K42-$S42)</f>
+        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",$J42-$K42-$S42))</f>
       </c>
       <c r="U42" s="74">
-        <f>IF($R42="Fermer",-$L42,0)</f>
+        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer",-$L42,0))</f>
       </c>
       <c r="V42" s="76">
-        <f>IF($R42="Fermer","Fermer = perdre "&amp;TEXT($L42,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O42&gt;=0,$T42&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O42&lt;0,$L42&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O42&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P42,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q42,"0%")&amp;"."))))</f>
+        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","Fermer = perdre "&amp;TEXT($L42,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O42&gt;=0,$T42&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O42&lt;0,$L42&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O42&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P42,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q42,"0%")&amp;".")))))</f>
       </c>
       <c r="W42" s="47"/>
       <c r="X42" s="47"/>
@@ -13824,16 +13824,16 @@
         <v>115</v>
       </c>
       <c r="S43" s="74">
-        <f>IF($R43="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M43,$M43+SUMIFS($M$13:$M$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"Fermer")*$I43/SUMIFS($I$13:$I$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M43,$M43+SUMIFS($M$13:$M$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"Fermer")*$I43/SUMIFS($I$13:$I$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T43" s="75">
-        <f>IF($R43="Fermer","",$J43-$K43-$S43)</f>
+        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",$J43-$K43-$S43))</f>
       </c>
       <c r="U43" s="74">
-        <f>IF($R43="Fermer",-$L43,0)</f>
+        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer",-$L43,0))</f>
       </c>
       <c r="V43" s="76">
-        <f>IF($R43="Fermer","Fermer = perdre "&amp;TEXT($L43,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O43&gt;=0,$T43&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O43&lt;0,$L43&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O43&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P43,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q43,"0%")&amp;"."))))</f>
+        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","Fermer = perdre "&amp;TEXT($L43,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O43&gt;=0,$T43&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O43&lt;0,$L43&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O43&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P43,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q43,"0%")&amp;".")))))</f>
       </c>
       <c r="W43" s="47"/>
       <c r="X43" s="47"/>
@@ -13896,16 +13896,16 @@
         <v>115</v>
       </c>
       <c r="S44" s="74">
-        <f>IF($R44="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M44,$M44+SUMIFS($M$13:$M$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"Fermer")*$I44/SUMIFS($I$13:$I$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M44,$M44+SUMIFS($M$13:$M$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"Fermer")*$I44/SUMIFS($I$13:$I$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T44" s="75">
-        <f>IF($R44="Fermer","",$J44-$K44-$S44)</f>
+        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",$J44-$K44-$S44))</f>
       </c>
       <c r="U44" s="74">
-        <f>IF($R44="Fermer",-$L44,0)</f>
+        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer",-$L44,0))</f>
       </c>
       <c r="V44" s="76">
-        <f>IF($R44="Fermer","Fermer = perdre "&amp;TEXT($L44,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O44&gt;=0,$T44&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O44&lt;0,$L44&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O44&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P44,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q44,"0%")&amp;"."))))</f>
+        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","Fermer = perdre "&amp;TEXT($L44,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O44&gt;=0,$T44&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O44&lt;0,$L44&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O44&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P44,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q44,"0%")&amp;".")))))</f>
       </c>
       <c r="W44" s="47"/>
       <c r="X44" s="47"/>
@@ -13968,16 +13968,16 @@
         <v>112</v>
       </c>
       <c r="S45" s="74">
-        <f>IF($R45="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M45,$M45+SUMIFS($M$13:$M$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"Fermer")*$I45/SUMIFS($I$13:$I$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M45,$M45+SUMIFS($M$13:$M$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"Fermer")*$I45/SUMIFS($I$13:$I$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T45" s="75">
-        <f>IF($R45="Fermer","",$J45-$K45-$S45)</f>
+        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",$J45-$K45-$S45))</f>
       </c>
       <c r="U45" s="74">
-        <f>IF($R45="Fermer",-$L45,0)</f>
+        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer",-$L45,0))</f>
       </c>
       <c r="V45" s="76">
-        <f>IF($R45="Fermer","Fermer = perdre "&amp;TEXT($L45,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O45&gt;=0,$T45&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O45&lt;0,$L45&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O45&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P45,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q45,"0%")&amp;"."))))</f>
+        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","Fermer = perdre "&amp;TEXT($L45,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O45&gt;=0,$T45&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O45&lt;0,$L45&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O45&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P45,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q45,"0%")&amp;".")))))</f>
       </c>
       <c r="W45" s="47"/>
       <c r="X45" s="47"/>
@@ -14040,16 +14040,16 @@
         <v>115</v>
       </c>
       <c r="S46" s="74">
-        <f>IF($R46="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M46,$M46+SUMIFS($M$13:$M$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"Fermer")*$I46/SUMIFS($I$13:$I$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M46,$M46+SUMIFS($M$13:$M$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"Fermer")*$I46/SUMIFS($I$13:$I$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T46" s="75">
-        <f>IF($R46="Fermer","",$J46-$K46-$S46)</f>
+        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",$J46-$K46-$S46))</f>
       </c>
       <c r="U46" s="74">
-        <f>IF($R46="Fermer",-$L46,0)</f>
+        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer",-$L46,0))</f>
       </c>
       <c r="V46" s="76">
-        <f>IF($R46="Fermer","Fermer = perdre "&amp;TEXT($L46,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O46&gt;=0,$T46&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O46&lt;0,$L46&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O46&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P46,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q46,"0%")&amp;"."))))</f>
+        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","Fermer = perdre "&amp;TEXT($L46,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O46&gt;=0,$T46&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O46&lt;0,$L46&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O46&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P46,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q46,"0%")&amp;".")))))</f>
       </c>
       <c r="W46" s="47"/>
       <c r="X46" s="47"/>
@@ -14112,16 +14112,16 @@
         <v>112</v>
       </c>
       <c r="S47" s="74">
-        <f>IF($R47="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M47,$M47+SUMIFS($M$13:$M$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"Fermer")*$I47/SUMIFS($I$13:$I$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M47,$M47+SUMIFS($M$13:$M$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"Fermer")*$I47/SUMIFS($I$13:$I$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T47" s="75">
-        <f>IF($R47="Fermer","",$J47-$K47-$S47)</f>
+        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",$J47-$K47-$S47))</f>
       </c>
       <c r="U47" s="74">
-        <f>IF($R47="Fermer",-$L47,0)</f>
+        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer",-$L47,0))</f>
       </c>
       <c r="V47" s="76">
-        <f>IF($R47="Fermer","Fermer = perdre "&amp;TEXT($L47,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O47&gt;=0,$T47&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O47&lt;0,$L47&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O47&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P47,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q47,"0%")&amp;"."))))</f>
+        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","Fermer = perdre "&amp;TEXT($L47,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O47&gt;=0,$T47&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O47&lt;0,$L47&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O47&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P47,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q47,"0%")&amp;".")))))</f>
       </c>
       <c r="W47" s="47"/>
       <c r="X47" s="47"/>
@@ -14184,16 +14184,16 @@
         <v>115</v>
       </c>
       <c r="S48" s="74">
-        <f>IF($R48="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M48,$M48+SUMIFS($M$13:$M$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"Fermer")*$I48/SUMIFS($I$13:$I$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M48,$M48+SUMIFS($M$13:$M$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"Fermer")*$I48/SUMIFS($I$13:$I$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T48" s="75">
-        <f>IF($R48="Fermer","",$J48-$K48-$S48)</f>
+        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",$J48-$K48-$S48))</f>
       </c>
       <c r="U48" s="74">
-        <f>IF($R48="Fermer",-$L48,0)</f>
+        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer",-$L48,0))</f>
       </c>
       <c r="V48" s="76">
-        <f>IF($R48="Fermer","Fermer = perdre "&amp;TEXT($L48,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O48&gt;=0,$T48&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O48&lt;0,$L48&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O48&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P48,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q48,"0%")&amp;"."))))</f>
+        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","Fermer = perdre "&amp;TEXT($L48,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O48&gt;=0,$T48&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O48&lt;0,$L48&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O48&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P48,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q48,"0%")&amp;".")))))</f>
       </c>
       <c r="W48" s="47"/>
       <c r="X48" s="47"/>
@@ -14256,16 +14256,16 @@
         <v>115</v>
       </c>
       <c r="S49" s="74">
-        <f>IF($R49="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M49,$M49+SUMIFS($M$13:$M$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"Fermer")*$I49/SUMIFS($I$13:$I$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M49,$M49+SUMIFS($M$13:$M$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"Fermer")*$I49/SUMIFS($I$13:$I$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T49" s="75">
-        <f>IF($R49="Fermer","",$J49-$K49-$S49)</f>
+        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",$J49-$K49-$S49))</f>
       </c>
       <c r="U49" s="74">
-        <f>IF($R49="Fermer",-$L49,0)</f>
+        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer",-$L49,0))</f>
       </c>
       <c r="V49" s="76">
-        <f>IF($R49="Fermer","Fermer = perdre "&amp;TEXT($L49,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O49&gt;=0,$T49&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O49&lt;0,$L49&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O49&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P49,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q49,"0%")&amp;"."))))</f>
+        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","Fermer = perdre "&amp;TEXT($L49,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O49&gt;=0,$T49&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O49&lt;0,$L49&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O49&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P49,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q49,"0%")&amp;".")))))</f>
       </c>
       <c r="W49" s="47"/>
       <c r="X49" s="47"/>
@@ -14328,16 +14328,16 @@
         <v>112</v>
       </c>
       <c r="S50" s="74">
-        <f>IF($R50="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M50,$M50+SUMIFS($M$13:$M$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"Fermer")*$I50/SUMIFS($I$13:$I$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M50,$M50+SUMIFS($M$13:$M$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"Fermer")*$I50/SUMIFS($I$13:$I$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T50" s="75">
-        <f>IF($R50="Fermer","",$J50-$K50-$S50)</f>
+        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",$J50-$K50-$S50))</f>
       </c>
       <c r="U50" s="74">
-        <f>IF($R50="Fermer",-$L50,0)</f>
+        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer",-$L50,0))</f>
       </c>
       <c r="V50" s="76">
-        <f>IF($R50="Fermer","Fermer = perdre "&amp;TEXT($L50,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O50&gt;=0,$T50&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O50&lt;0,$L50&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O50&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P50,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q50,"0%")&amp;"."))))</f>
+        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","Fermer = perdre "&amp;TEXT($L50,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O50&gt;=0,$T50&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O50&lt;0,$L50&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O50&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P50,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q50,"0%")&amp;".")))))</f>
       </c>
       <c r="W50" s="47"/>
       <c r="X50" s="47"/>
@@ -14400,16 +14400,16 @@
         <v>115</v>
       </c>
       <c r="S51" s="74">
-        <f>IF($R51="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M51,$M51+SUMIFS($M$13:$M$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"Fermer")*$I51/SUMIFS($I$13:$I$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M51,$M51+SUMIFS($M$13:$M$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"Fermer")*$I51/SUMIFS($I$13:$I$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T51" s="75">
-        <f>IF($R51="Fermer","",$J51-$K51-$S51)</f>
+        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",$J51-$K51-$S51))</f>
       </c>
       <c r="U51" s="74">
-        <f>IF($R51="Fermer",-$L51,0)</f>
+        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer",-$L51,0))</f>
       </c>
       <c r="V51" s="76">
-        <f>IF($R51="Fermer","Fermer = perdre "&amp;TEXT($L51,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O51&gt;=0,$T51&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O51&lt;0,$L51&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O51&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P51,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q51,"0%")&amp;"."))))</f>
+        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","Fermer = perdre "&amp;TEXT($L51,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O51&gt;=0,$T51&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O51&lt;0,$L51&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O51&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P51,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q51,"0%")&amp;".")))))</f>
       </c>
       <c r="W51" s="47"/>
       <c r="X51" s="47"/>
@@ -14472,16 +14472,16 @@
         <v>112</v>
       </c>
       <c r="S52" s="74">
-        <f>IF($R52="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M52,$M52+SUMIFS($M$13:$M$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"Fermer")*$I52/SUMIFS($I$13:$I$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M52,$M52+SUMIFS($M$13:$M$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"Fermer")*$I52/SUMIFS($I$13:$I$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T52" s="75">
-        <f>IF($R52="Fermer","",$J52-$K52-$S52)</f>
+        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",$J52-$K52-$S52))</f>
       </c>
       <c r="U52" s="74">
-        <f>IF($R52="Fermer",-$L52,0)</f>
+        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer",-$L52,0))</f>
       </c>
       <c r="V52" s="76">
-        <f>IF($R52="Fermer","Fermer = perdre "&amp;TEXT($L52,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O52&gt;=0,$T52&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O52&lt;0,$L52&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O52&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P52,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q52,"0%")&amp;"."))))</f>
+        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","Fermer = perdre "&amp;TEXT($L52,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O52&gt;=0,$T52&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O52&lt;0,$L52&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O52&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P52,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q52,"0%")&amp;".")))))</f>
       </c>
       <c r="W52" s="47"/>
       <c r="X52" s="47"/>
@@ -14544,16 +14544,16 @@
         <v>115</v>
       </c>
       <c r="S53" s="74">
-        <f>IF($R53="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M53,$M53+SUMIFS($M$13:$M$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"Fermer")*$I53/SUMIFS($I$13:$I$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M53,$M53+SUMIFS($M$13:$M$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"Fermer")*$I53/SUMIFS($I$13:$I$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T53" s="75">
-        <f>IF($R53="Fermer","",$J53-$K53-$S53)</f>
+        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",$J53-$K53-$S53))</f>
       </c>
       <c r="U53" s="74">
-        <f>IF($R53="Fermer",-$L53,0)</f>
+        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer",-$L53,0))</f>
       </c>
       <c r="V53" s="76">
-        <f>IF($R53="Fermer","Fermer = perdre "&amp;TEXT($L53,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O53&gt;=0,$T53&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O53&lt;0,$L53&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O53&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P53,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q53,"0%")&amp;"."))))</f>
+        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","Fermer = perdre "&amp;TEXT($L53,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O53&gt;=0,$T53&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O53&lt;0,$L53&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O53&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P53,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q53,"0%")&amp;".")))))</f>
       </c>
       <c r="W53" s="47"/>
       <c r="X53" s="47"/>
@@ -14616,16 +14616,16 @@
         <v>115</v>
       </c>
       <c r="S54" s="74">
-        <f>IF($R54="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M54,$M54+SUMIFS($M$13:$M$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"Fermer")*$I54/SUMIFS($I$13:$I$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M54,$M54+SUMIFS($M$13:$M$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"Fermer")*$I54/SUMIFS($I$13:$I$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T54" s="75">
-        <f>IF($R54="Fermer","",$J54-$K54-$S54)</f>
+        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",$J54-$K54-$S54))</f>
       </c>
       <c r="U54" s="74">
-        <f>IF($R54="Fermer",-$L54,0)</f>
+        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer",-$L54,0))</f>
       </c>
       <c r="V54" s="76">
-        <f>IF($R54="Fermer","Fermer = perdre "&amp;TEXT($L54,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O54&gt;=0,$T54&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O54&lt;0,$L54&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O54&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P54,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q54,"0%")&amp;"."))))</f>
+        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","Fermer = perdre "&amp;TEXT($L54,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O54&gt;=0,$T54&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O54&lt;0,$L54&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O54&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P54,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q54,"0%")&amp;".")))))</f>
       </c>
       <c r="W54" s="47"/>
       <c r="X54" s="47"/>
@@ -14688,16 +14688,16 @@
         <v>112</v>
       </c>
       <c r="S55" s="74">
-        <f>IF($R55="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M55,$M55+SUMIFS($M$13:$M$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"Fermer")*$I55/SUMIFS($I$13:$I$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M55,$M55+SUMIFS($M$13:$M$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"Fermer")*$I55/SUMIFS($I$13:$I$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T55" s="75">
-        <f>IF($R55="Fermer","",$J55-$K55-$S55)</f>
+        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",$J55-$K55-$S55))</f>
       </c>
       <c r="U55" s="74">
-        <f>IF($R55="Fermer",-$L55,0)</f>
+        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer",-$L55,0))</f>
       </c>
       <c r="V55" s="76">
-        <f>IF($R55="Fermer","Fermer = perdre "&amp;TEXT($L55,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O55&gt;=0,$T55&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O55&lt;0,$L55&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O55&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P55,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q55,"0%")&amp;"."))))</f>
+        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","Fermer = perdre "&amp;TEXT($L55,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O55&gt;=0,$T55&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O55&lt;0,$L55&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O55&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P55,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q55,"0%")&amp;".")))))</f>
       </c>
       <c r="W55" s="47"/>
       <c r="X55" s="47"/>
@@ -14760,16 +14760,16 @@
         <v>115</v>
       </c>
       <c r="S56" s="74">
-        <f>IF($R56="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M56,$M56+SUMIFS($M$13:$M$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"Fermer")*$I56/SUMIFS($I$13:$I$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M56,$M56+SUMIFS($M$13:$M$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"Fermer")*$I56/SUMIFS($I$13:$I$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T56" s="75">
-        <f>IF($R56="Fermer","",$J56-$K56-$S56)</f>
+        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",$J56-$K56-$S56))</f>
       </c>
       <c r="U56" s="74">
-        <f>IF($R56="Fermer",-$L56,0)</f>
+        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer",-$L56,0))</f>
       </c>
       <c r="V56" s="76">
-        <f>IF($R56="Fermer","Fermer = perdre "&amp;TEXT($L56,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O56&gt;=0,$T56&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O56&lt;0,$L56&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O56&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P56,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q56,"0%")&amp;"."))))</f>
+        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","Fermer = perdre "&amp;TEXT($L56,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O56&gt;=0,$T56&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O56&lt;0,$L56&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O56&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P56,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q56,"0%")&amp;".")))))</f>
       </c>
       <c r="W56" s="47"/>
       <c r="X56" s="47"/>
@@ -14832,16 +14832,16 @@
         <v>112</v>
       </c>
       <c r="S57" s="74">
-        <f>IF($R57="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M57,$M57+SUMIFS($M$13:$M$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"Fermer")*$I57/SUMIFS($I$13:$I$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M57,$M57+SUMIFS($M$13:$M$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"Fermer")*$I57/SUMIFS($I$13:$I$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T57" s="75">
-        <f>IF($R57="Fermer","",$J57-$K57-$S57)</f>
+        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",$J57-$K57-$S57))</f>
       </c>
       <c r="U57" s="74">
-        <f>IF($R57="Fermer",-$L57,0)</f>
+        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer",-$L57,0))</f>
       </c>
       <c r="V57" s="76">
-        <f>IF($R57="Fermer","Fermer = perdre "&amp;TEXT($L57,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O57&gt;=0,$T57&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O57&lt;0,$L57&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O57&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P57,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q57,"0%")&amp;"."))))</f>
+        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","Fermer = perdre "&amp;TEXT($L57,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O57&gt;=0,$T57&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O57&lt;0,$L57&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O57&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P57,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q57,"0%")&amp;".")))))</f>
       </c>
       <c r="W57" s="47"/>
       <c r="X57" s="47"/>
@@ -14904,16 +14904,16 @@
         <v>115</v>
       </c>
       <c r="S58" s="74">
-        <f>IF($R58="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M58,$M58+SUMIFS($M$13:$M$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"Fermer")*$I58/SUMIFS($I$13:$I$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M58,$M58+SUMIFS($M$13:$M$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"Fermer")*$I58/SUMIFS($I$13:$I$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T58" s="75">
-        <f>IF($R58="Fermer","",$J58-$K58-$S58)</f>
+        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",$J58-$K58-$S58))</f>
       </c>
       <c r="U58" s="74">
-        <f>IF($R58="Fermer",-$L58,0)</f>
+        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer",-$L58,0))</f>
       </c>
       <c r="V58" s="76">
-        <f>IF($R58="Fermer","Fermer = perdre "&amp;TEXT($L58,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O58&gt;=0,$T58&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O58&lt;0,$L58&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O58&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P58,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q58,"0%")&amp;"."))))</f>
+        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","Fermer = perdre "&amp;TEXT($L58,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O58&gt;=0,$T58&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O58&lt;0,$L58&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O58&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P58,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q58,"0%")&amp;".")))))</f>
       </c>
       <c r="W58" s="47"/>
       <c r="X58" s="47"/>
@@ -14976,16 +14976,16 @@
         <v>112</v>
       </c>
       <c r="S59" s="74">
-        <f>IF($R59="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M59,$M59+SUMIFS($M$13:$M$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"Fermer")*$I59/SUMIFS($I$13:$I$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M59,$M59+SUMIFS($M$13:$M$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"Fermer")*$I59/SUMIFS($I$13:$I$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T59" s="75">
-        <f>IF($R59="Fermer","",$J59-$K59-$S59)</f>
+        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",$J59-$K59-$S59))</f>
       </c>
       <c r="U59" s="74">
-        <f>IF($R59="Fermer",-$L59,0)</f>
+        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer",-$L59,0))</f>
       </c>
       <c r="V59" s="76">
-        <f>IF($R59="Fermer","Fermer = perdre "&amp;TEXT($L59,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O59&gt;=0,$T59&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O59&lt;0,$L59&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O59&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P59,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q59,"0%")&amp;"."))))</f>
+        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","Fermer = perdre "&amp;TEXT($L59,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O59&gt;=0,$T59&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O59&lt;0,$L59&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O59&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P59,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q59,"0%")&amp;".")))))</f>
       </c>
       <c r="W59" s="47"/>
       <c r="X59" s="47"/>
@@ -15048,16 +15048,16 @@
         <v>115</v>
       </c>
       <c r="S60" s="74">
-        <f>IF($R60="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M60,$M60+SUMIFS($M$13:$M$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"Fermer")*$I60/SUMIFS($I$13:$I$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M60,$M60+SUMIFS($M$13:$M$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"Fermer")*$I60/SUMIFS($I$13:$I$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T60" s="75">
-        <f>IF($R60="Fermer","",$J60-$K60-$S60)</f>
+        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",$J60-$K60-$S60))</f>
       </c>
       <c r="U60" s="74">
-        <f>IF($R60="Fermer",-$L60,0)</f>
+        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer",-$L60,0))</f>
       </c>
       <c r="V60" s="76">
-        <f>IF($R60="Fermer","Fermer = perdre "&amp;TEXT($L60,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O60&gt;=0,$T60&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O60&lt;0,$L60&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O60&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P60,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q60,"0%")&amp;"."))))</f>
+        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","Fermer = perdre "&amp;TEXT($L60,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O60&gt;=0,$T60&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O60&lt;0,$L60&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O60&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P60,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q60,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -15111,16 +15111,16 @@
         <v>115</v>
       </c>
       <c r="S61" s="74">
-        <f>IF($R61="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M61,$M61+SUMIFS($M$13:$M$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"Fermer")*$I61/SUMIFS($I$13:$I$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M61,$M61+SUMIFS($M$13:$M$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"Fermer")*$I61/SUMIFS($I$13:$I$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T61" s="75">
-        <f>IF($R61="Fermer","",$J61-$K61-$S61)</f>
+        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",$J61-$K61-$S61))</f>
       </c>
       <c r="U61" s="74">
-        <f>IF($R61="Fermer",-$L61,0)</f>
+        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer",-$L61,0))</f>
       </c>
       <c r="V61" s="76">
-        <f>IF($R61="Fermer","Fermer = perdre "&amp;TEXT($L61,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O61&gt;=0,$T61&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O61&lt;0,$L61&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O61&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P61,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q61,"0%")&amp;"."))))</f>
+        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","Fermer = perdre "&amp;TEXT($L61,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O61&gt;=0,$T61&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O61&lt;0,$L61&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O61&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P61,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q61,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -15174,16 +15174,16 @@
         <v>115</v>
       </c>
       <c r="S62" s="74">
-        <f>IF($R62="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M62,$M62+SUMIFS($M$13:$M$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"Fermer")*$I62/SUMIFS($I$13:$I$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M62,$M62+SUMIFS($M$13:$M$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"Fermer")*$I62/SUMIFS($I$13:$I$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T62" s="75">
-        <f>IF($R62="Fermer","",$J62-$K62-$S62)</f>
+        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",$J62-$K62-$S62))</f>
       </c>
       <c r="U62" s="74">
-        <f>IF($R62="Fermer",-$L62,0)</f>
+        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer",-$L62,0))</f>
       </c>
       <c r="V62" s="76">
-        <f>IF($R62="Fermer","Fermer = perdre "&amp;TEXT($L62,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O62&gt;=0,$T62&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O62&lt;0,$L62&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O62&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P62,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q62,"0%")&amp;"."))))</f>
+        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","Fermer = perdre "&amp;TEXT($L62,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O62&gt;=0,$T62&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O62&lt;0,$L62&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O62&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P62,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q62,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -15237,16 +15237,16 @@
         <v>115</v>
       </c>
       <c r="S63" s="74">
-        <f>IF($R63="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M63,$M63+SUMIFS($M$13:$M$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"Fermer")*$I63/SUMIFS($I$13:$I$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M63,$M63+SUMIFS($M$13:$M$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"Fermer")*$I63/SUMIFS($I$13:$I$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T63" s="75">
-        <f>IF($R63="Fermer","",$J63-$K63-$S63)</f>
+        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",$J63-$K63-$S63))</f>
       </c>
       <c r="U63" s="74">
-        <f>IF($R63="Fermer",-$L63,0)</f>
+        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer",-$L63,0))</f>
       </c>
       <c r="V63" s="76">
-        <f>IF($R63="Fermer","Fermer = perdre "&amp;TEXT($L63,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O63&gt;=0,$T63&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O63&lt;0,$L63&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O63&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P63,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q63,"0%")&amp;"."))))</f>
+        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","Fermer = perdre "&amp;TEXT($L63,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O63&gt;=0,$T63&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O63&lt;0,$L63&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O63&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P63,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q63,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -15300,16 +15300,16 @@
         <v>112</v>
       </c>
       <c r="S64" s="74">
-        <f>IF($R64="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M64,$M64+SUMIFS($M$13:$M$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"Fermer")*$I64/SUMIFS($I$13:$I$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M64,$M64+SUMIFS($M$13:$M$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"Fermer")*$I64/SUMIFS($I$13:$I$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T64" s="75">
-        <f>IF($R64="Fermer","",$J64-$K64-$S64)</f>
+        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",$J64-$K64-$S64))</f>
       </c>
       <c r="U64" s="74">
-        <f>IF($R64="Fermer",-$L64,0)</f>
+        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer",-$L64,0))</f>
       </c>
       <c r="V64" s="76">
-        <f>IF($R64="Fermer","Fermer = perdre "&amp;TEXT($L64,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O64&gt;=0,$T64&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O64&lt;0,$L64&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O64&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P64,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q64,"0%")&amp;"."))))</f>
+        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","Fermer = perdre "&amp;TEXT($L64,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O64&gt;=0,$T64&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O64&lt;0,$L64&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O64&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P64,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q64,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
@@ -15363,16 +15363,16 @@
         <v>115</v>
       </c>
       <c r="S65" s="74">
-        <f>IF($R65="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M65,$M65+SUMIFS($M$13:$M$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"Fermer")*$I65/SUMIFS($I$13:$I$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M65,$M65+SUMIFS($M$13:$M$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"Fermer")*$I65/SUMIFS($I$13:$I$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T65" s="75">
-        <f>IF($R65="Fermer","",$J65-$K65-$S65)</f>
+        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",$J65-$K65-$S65))</f>
       </c>
       <c r="U65" s="74">
-        <f>IF($R65="Fermer",-$L65,0)</f>
+        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer",-$L65,0))</f>
       </c>
       <c r="V65" s="76">
-        <f>IF($R65="Fermer","Fermer = perdre "&amp;TEXT($L65,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O65&gt;=0,$T65&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O65&lt;0,$L65&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O65&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P65,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q65,"0%")&amp;"."))))</f>
+        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","Fermer = perdre "&amp;TEXT($L65,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O65&gt;=0,$T65&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O65&lt;0,$L65&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O65&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P65,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q65,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -15426,16 +15426,16 @@
         <v>112</v>
       </c>
       <c r="S66" s="74">
-        <f>IF($R66="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M66,$M66+SUMIFS($M$13:$M$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"Fermer")*$I66/SUMIFS($I$13:$I$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M66,$M66+SUMIFS($M$13:$M$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"Fermer")*$I66/SUMIFS($I$13:$I$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T66" s="75">
-        <f>IF($R66="Fermer","",$J66-$K66-$S66)</f>
+        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",$J66-$K66-$S66))</f>
       </c>
       <c r="U66" s="74">
-        <f>IF($R66="Fermer",-$L66,0)</f>
+        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer",-$L66,0))</f>
       </c>
       <c r="V66" s="76">
-        <f>IF($R66="Fermer","Fermer = perdre "&amp;TEXT($L66,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O66&gt;=0,$T66&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O66&lt;0,$L66&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O66&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P66,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q66,"0%")&amp;"."))))</f>
+        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","Fermer = perdre "&amp;TEXT($L66,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O66&gt;=0,$T66&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O66&lt;0,$L66&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O66&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P66,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q66,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -15489,16 +15489,16 @@
         <v>112</v>
       </c>
       <c r="S67" s="74">
-        <f>IF($R67="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M67,$M67+SUMIFS($M$13:$M$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"Fermer")*$I67/SUMIFS($I$13:$I$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M67,$M67+SUMIFS($M$13:$M$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"Fermer")*$I67/SUMIFS($I$13:$I$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T67" s="75">
-        <f>IF($R67="Fermer","",$J67-$K67-$S67)</f>
+        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",$J67-$K67-$S67))</f>
       </c>
       <c r="U67" s="74">
-        <f>IF($R67="Fermer",-$L67,0)</f>
+        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer",-$L67,0))</f>
       </c>
       <c r="V67" s="76">
-        <f>IF($R67="Fermer","Fermer = perdre "&amp;TEXT($L67,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O67&gt;=0,$T67&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O67&lt;0,$L67&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O67&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P67,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q67,"0%")&amp;"."))))</f>
+        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","Fermer = perdre "&amp;TEXT($L67,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O67&gt;=0,$T67&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O67&lt;0,$L67&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O67&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P67,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q67,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -15552,16 +15552,16 @@
         <v>115</v>
       </c>
       <c r="S68" s="74">
-        <f>IF($R68="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M68,$M68+SUMIFS($M$13:$M$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"Fermer")*$I68/SUMIFS($I$13:$I$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M68,$M68+SUMIFS($M$13:$M$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"Fermer")*$I68/SUMIFS($I$13:$I$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T68" s="75">
-        <f>IF($R68="Fermer","",$J68-$K68-$S68)</f>
+        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",$J68-$K68-$S68))</f>
       </c>
       <c r="U68" s="74">
-        <f>IF($R68="Fermer",-$L68,0)</f>
+        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer",-$L68,0))</f>
       </c>
       <c r="V68" s="76">
-        <f>IF($R68="Fermer","Fermer = perdre "&amp;TEXT($L68,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O68&gt;=0,$T68&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O68&lt;0,$L68&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O68&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P68,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q68,"0%")&amp;"."))))</f>
+        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","Fermer = perdre "&amp;TEXT($L68,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O68&gt;=0,$T68&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O68&lt;0,$L68&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O68&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P68,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q68,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -15615,16 +15615,16 @@
         <v>115</v>
       </c>
       <c r="S69" s="74">
-        <f>IF($R69="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M69,$M69+SUMIFS($M$13:$M$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"Fermer")*$I69/SUMIFS($I$13:$I$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M69,$M69+SUMIFS($M$13:$M$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"Fermer")*$I69/SUMIFS($I$13:$I$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T69" s="75">
-        <f>IF($R69="Fermer","",$J69-$K69-$S69)</f>
+        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",$J69-$K69-$S69))</f>
       </c>
       <c r="U69" s="74">
-        <f>IF($R69="Fermer",-$L69,0)</f>
+        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer",-$L69,0))</f>
       </c>
       <c r="V69" s="76">
-        <f>IF($R69="Fermer","Fermer = perdre "&amp;TEXT($L69,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O69&gt;=0,$T69&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O69&lt;0,$L69&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O69&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P69,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q69,"0%")&amp;"."))))</f>
+        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","Fermer = perdre "&amp;TEXT($L69,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O69&gt;=0,$T69&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O69&lt;0,$L69&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O69&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P69,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q69,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
@@ -15678,16 +15678,16 @@
         <v>112</v>
       </c>
       <c r="S70" s="74">
-        <f>IF($R70="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M70,$M70+SUMIFS($M$13:$M$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"Fermer")*$I70/SUMIFS($I$13:$I$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M70,$M70+SUMIFS($M$13:$M$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"Fermer")*$I70/SUMIFS($I$13:$I$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T70" s="75">
-        <f>IF($R70="Fermer","",$J70-$K70-$S70)</f>
+        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",$J70-$K70-$S70))</f>
       </c>
       <c r="U70" s="74">
-        <f>IF($R70="Fermer",-$L70,0)</f>
+        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer",-$L70,0))</f>
       </c>
       <c r="V70" s="76">
-        <f>IF($R70="Fermer","Fermer = perdre "&amp;TEXT($L70,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O70&gt;=0,$T70&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O70&lt;0,$L70&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O70&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P70,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q70,"0%")&amp;"."))))</f>
+        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","Fermer = perdre "&amp;TEXT($L70,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O70&gt;=0,$T70&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O70&lt;0,$L70&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O70&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P70,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q70,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -15741,16 +15741,16 @@
         <v>115</v>
       </c>
       <c r="S71" s="74">
-        <f>IF($R71="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M71,$M71+SUMIFS($M$13:$M$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"Fermer")*$I71/SUMIFS($I$13:$I$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M71,$M71+SUMIFS($M$13:$M$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"Fermer")*$I71/SUMIFS($I$13:$I$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T71" s="75">
-        <f>IF($R71="Fermer","",$J71-$K71-$S71)</f>
+        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",$J71-$K71-$S71))</f>
       </c>
       <c r="U71" s="74">
-        <f>IF($R71="Fermer",-$L71,0)</f>
+        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer",-$L71,0))</f>
       </c>
       <c r="V71" s="76">
-        <f>IF($R71="Fermer","Fermer = perdre "&amp;TEXT($L71,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O71&gt;=0,$T71&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O71&lt;0,$L71&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O71&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P71,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q71,"0%")&amp;"."))))</f>
+        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","Fermer = perdre "&amp;TEXT($L71,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O71&gt;=0,$T71&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O71&lt;0,$L71&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O71&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P71,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q71,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -15804,16 +15804,16 @@
         <v>115</v>
       </c>
       <c r="S72" s="74">
-        <f>IF($R72="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M72,$M72+SUMIFS($M$13:$M$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"Fermer")*$I72/SUMIFS($I$13:$I$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"&lt;&gt;Fermer")))</f>
+        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M72,$M72+SUMIFS($M$13:$M$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"Fermer")*$I72/SUMIFS($I$13:$I$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
       </c>
       <c r="T72" s="75">
-        <f>IF($R72="Fermer","",$J72-$K72-$S72)</f>
+        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",$J72-$K72-$S72))</f>
       </c>
       <c r="U72" s="74">
-        <f>IF($R72="Fermer",-$L72,0)</f>
+        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer",-$L72,0))</f>
       </c>
       <c r="V72" s="76">
-        <f>IF($R72="Fermer","Fermer = perdre "&amp;TEXT($L72,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O72&gt;=0,$T72&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O72&lt;0,$L72&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O72&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P72,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q72,"0%")&amp;"."))))</f>
+        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","Fermer = perdre "&amp;TEXT($L72,"#,##0")&amp;" € de contribution. Le fixe, lui, reste.",IF(AND($O72&gt;=0,$T72&lt;0),"BASCULE : saine avant, en déficit à cause d'une fermeture voisine.",IF(AND($O72&lt;0,$L72&gt;0),"Déficit au coût complet mais contribution positive : ne pas fermer, c'est un artefact d'allocation.",IF($O72&lt;0,"Contribution négative : vrai point dur.","Rentable. Point mort "&amp;TEXT($P72,"#,##0")&amp;" étudiants, marge de sécurité "&amp;TEXT($Q72,"0%")&amp;".")))))</f>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">

--- a/eduservices/SIMULATION_CORRIGE.xlsx
+++ b/eduservices/SIMULATION_CORRIGE.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t>Template00</t>
   </si>
@@ -365,7 +365,7 @@
     <t>Garder</t>
   </si>
   <si>
-    <t>Rentable — point mort 45 étud., marge sécu 2%</t>
+    <t>Rentable. Point mort 35 étudiants, marge de sécurité 23%.</t>
   </si>
   <si>
     <t>B2</t>
@@ -374,15 +374,27 @@
     <t>cohorte</t>
   </si>
   <si>
-    <t>Rentable — point mort 0 étud., marge sécu 0%</t>
+    <t>Rentable. Point mort 34 étudiants, marge de sécurité 15%.</t>
   </si>
   <si>
     <t>B3</t>
   </si>
   <si>
+    <t>Rentable. Point mort 34 étudiants, marge de sécurité 12%.</t>
+  </si>
+  <si>
     <t>Nantes</t>
   </si>
   <si>
+    <t>Rentable. Point mort 43 étudiants, marge de sécurité 23%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 41 étudiants, marge de sécurité 15%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 42 étudiants, marge de sécurité 13%.</t>
+  </si>
+  <si>
     <t>Rennes</t>
   </si>
   <si>
@@ -395,21 +407,66 @@
     <t>INIT</t>
   </si>
   <si>
+    <t>Rentable. Point mort 44 étudiants, marge de sécurité 21%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 43 étudiants, marge de sécurité 11%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 43 étudiants, marge de sécurité 9%.</t>
+  </si>
+  <si>
     <t>Mastère Communication</t>
   </si>
   <si>
     <t>M1</t>
   </si>
   <si>
+    <t>Rentable. Point mort 39 étudiants, marge de sécurité 31%.</t>
+  </si>
+  <si>
     <t>M2</t>
   </si>
   <si>
+    <t>Rentable. Point mort 39 étudiants, marge de sécurité 23%.</t>
+  </si>
+  <si>
     <t>Paris</t>
   </si>
   <si>
+    <t>Rentable. Point mort 63 étudiants, marge de sécurité 20%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 61 étudiants, marge de sécurité 14%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 61 étudiants, marge de sécurité 13%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 56 étudiants, marge de sécurité 30%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 54 étudiants, marge de sécurité 25%.</t>
+  </si>
+  <si>
     <t>Toulouse</t>
   </si>
   <si>
+    <t>Rentable. Point mort 42 étudiants, marge de sécurité 20%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 41 étudiants, marge de sécurité 12%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 41 étudiants, marge de sécurité 10%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 37 étudiants, marge de sécurité 30%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 37 étudiants, marge de sécurité 22%.</t>
+  </si>
+  <si>
     <t>MBWAY</t>
   </si>
   <si>
@@ -419,12 +476,66 @@
     <t>Bachelor Management</t>
   </si>
   <si>
+    <t>Rentable. Point mort 44 étudiants, marge de sécurité 12%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 44 étudiants, marge de sécurité 10%.</t>
+  </si>
+  <si>
     <t>Mastère Management</t>
   </si>
   <si>
+    <t>Rentable. Point mort 40 étudiants, marge de sécurité 31%.</t>
+  </si>
+  <si>
     <t>Lyon</t>
   </si>
   <si>
+    <t>Rentable. Point mort 67 étudiants, marge de sécurité 8%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 42 étudiants, marge de sécurité 35%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 42 étudiants, marge de sécurité 34%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 59 étudiants, marge de sécurité 20%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 58 étudiants, marge de sécurité 12%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 43 étudiants, marge de sécurité 35%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 42 étudiants, marge de sécurité 28%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 43 étudiants, marge de sécurité 27%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 59 étudiants, marge de sécurité 13%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 58 étudiants, marge de sécurité 3%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 67 étudiants, marge de sécurité 22%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 65 étudiants, marge de sécurité 16%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 65 étudiants, marge de sécurité 14%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 60 étudiants, marge de sécurité 31%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 58 étudiants, marge de sécurité 25%.</t>
+  </si>
+  <si>
     <t>PIGIER</t>
   </si>
   <si>
@@ -434,16 +545,64 @@
     <t>BTS1</t>
   </si>
   <si>
+    <t>Rentable. Point mort 35 étudiants, marge de sécurité 15%.</t>
+  </si>
+  <si>
     <t>BTS2</t>
   </si>
   <si>
+    <t>Rentable. Point mort 34 étudiants, marge de sécurité 5%.</t>
+  </si>
+  <si>
     <t>Bachelor Ressources humaines</t>
   </si>
   <si>
+    <t>Rentable. Point mort 25 étudiants, marge de sécurité 38%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 25 étudiants, marge de sécurité 31%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 25 étudiants, marge de sécurité 29%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 32 étudiants, marge de sécurité 30%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 32 étudiants, marge de sécurité 31%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 44 étudiants, marge de sécurité 15%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 42 étudiants, marge de sécurité 8%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 33 étudiants, marge de sécurité 37%.</t>
+  </si>
+  <si>
     <t>TUNON</t>
   </si>
   <si>
     <t>Bachelor Tourisme</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 40 étudiants, marge de sécurité 10%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 39 étudiants, marge de sécurité 3%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 39 étudiants, marge de sécurité 0%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 48 étudiants, marge de sécurité 9%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 45 étudiants, marge de sécurité 4%.</t>
+  </si>
+  <si>
+    <t>Rentable. Point mort 45 étudiants, marge de sécurité 2%.</t>
   </si>
   <si>
     <t>POURQUOI L'EBITDA A BOUGÉ</t>
@@ -658,35 +817,35 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="29">
-    <numFmt numFmtId="171" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00,"/>
-    <numFmt numFmtId="173" formatCode="#,##0,"/>
-    <numFmt numFmtId="176" formatCode="mm/dd/yy;@"/>
-    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="182" formatCode="&quot;▲ &quot;0.0%;&quot;▼ &quot;0.0%;&quot;&quot;"/>
-    <numFmt numFmtId="184" formatCode="&quot;▲ &quot;0.00;&quot;▼ &quot;0.00;&quot;&quot;"/>
-    <numFmt numFmtId="185" formatCode="0.0,,&quot; M€&quot;"/>
-    <numFmt numFmtId="189" formatCode="#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="193" formatCode="&quot;▲ &quot;0.0%;&quot;▼ &quot;0.0%;&quot;—&quot;"/>
-    <numFmt numFmtId="194" formatCode="&quot;+&quot;0.0%;&quot;-&quot;0.0%;&quot;—&quot;"/>
-    <numFmt numFmtId="195" formatCode="&quot;▲ &quot;0.00&quot; pt&quot;;&quot;▼ &quot;0.00&quot; pt&quot;;&quot;—&quot;"/>
-    <numFmt numFmtId="196" formatCode="&quot;+&quot;0.00&quot; pt&quot;;&quot;-&quot;0.00&quot; pt&quot;;&quot;—&quot;"/>
-    <numFmt numFmtId="197" formatCode="#,##0&quot; places libres&quot;;\-#,##0&quot; places libres&quot;;&quot;—&quot;"/>
-    <numFmt numFmtId="198" formatCode="#,##0&quot; places libres&quot;"/>
-    <numFmt numFmtId="203" formatCode="0.00&quot; €&quot;"/>
-    <numFmt numFmtId="205" formatCode="&quot;▲ &quot;#,##0;&quot;▼ &quot;#,##0;&quot;—&quot;"/>
-    <numFmt numFmtId="208" formatCode="\+#,##0&quot; €&quot;;\-#,##0&quot; €&quot;;&quot;0 €&quot;"/>
-    <numFmt numFmtId="209" formatCode="\+0.00%;\-0.00%;&quot;0,00 %&quot;"/>
-    <numFmt numFmtId="210" formatCode="\+#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="211" formatCode="\-#,##0&quot; €&quot;"/>
-    <numFmt numFmtId="215" formatCode="&quot;+&quot;0.0%;&quot;-&quot;0.0%;&quot;&quot;"/>
-    <numFmt numFmtId="222" formatCode="#,##0&quot; €&quot;;\(#,##0\)&quot; €&quot;;&quot;-&quot;"/>
-    <numFmt numFmtId="224" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="225" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="226" formatCode="_(&quot;€&quot;* #,##0.00_);_(&quot;€&quot;* \(#,##0.00\);_(&quot;€&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="227" formatCode="_(&quot;€&quot;* #,##0_);_(&quot;€&quot;* \(#,##0\);_(&quot;€&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="228" formatCode="#.###."/>
+    <numFmt numFmtId="1277" formatCode="0.0%"/>
+    <numFmt numFmtId="1278" formatCode="#,##0.00,"/>
+    <numFmt numFmtId="1279" formatCode="#,##0,"/>
+    <numFmt numFmtId="1282" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="1284" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="1285" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="1288" formatCode="&quot;▲ &quot;0.0%;&quot;▼ &quot;0.0%;&quot;&quot;"/>
+    <numFmt numFmtId="1290" formatCode="&quot;▲ &quot;0.00;&quot;▼ &quot;0.00;&quot;&quot;"/>
+    <numFmt numFmtId="1291" formatCode="0.0,,&quot; M€&quot;"/>
+    <numFmt numFmtId="1295" formatCode="#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="1299" formatCode="&quot;▲ &quot;0.0%;&quot;▼ &quot;0.0%;&quot;—&quot;"/>
+    <numFmt numFmtId="1300" formatCode="&quot;+&quot;0.0%;&quot;-&quot;0.0%;&quot;—&quot;"/>
+    <numFmt numFmtId="1301" formatCode="&quot;▲ &quot;0.00&quot; pt&quot;;&quot;▼ &quot;0.00&quot; pt&quot;;&quot;—&quot;"/>
+    <numFmt numFmtId="1302" formatCode="&quot;+&quot;0.00&quot; pt&quot;;&quot;-&quot;0.00&quot; pt&quot;;&quot;—&quot;"/>
+    <numFmt numFmtId="1303" formatCode="#,##0&quot; places libres&quot;;\-#,##0&quot; places libres&quot;;&quot;—&quot;"/>
+    <numFmt numFmtId="1304" formatCode="#,##0&quot; places libres&quot;"/>
+    <numFmt numFmtId="1309" formatCode="0.00&quot; €&quot;"/>
+    <numFmt numFmtId="1311" formatCode="&quot;▲ &quot;#,##0;&quot;▼ &quot;#,##0;&quot;—&quot;"/>
+    <numFmt numFmtId="1314" formatCode="\+#,##0&quot; €&quot;;\-#,##0&quot; €&quot;;&quot;0 €&quot;"/>
+    <numFmt numFmtId="1315" formatCode="\+0.00%;\-0.00%;&quot;0,00 %&quot;"/>
+    <numFmt numFmtId="1316" formatCode="\+#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="1317" formatCode="\-#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="1321" formatCode="&quot;+&quot;0.0%;&quot;-&quot;0.0%;&quot;&quot;"/>
+    <numFmt numFmtId="1327" formatCode="#,##0&quot; €&quot;;\(#,##0\)&quot; €&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="1329" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="1330" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="1331" formatCode="_(&quot;€&quot;* #,##0.00_);_(&quot;€&quot;* \(#,##0.00\);_(&quot;€&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="1332" formatCode="_(&quot;€&quot;* #,##0_);_(&quot;€&quot;* \(#,##0\);_(&quot;€&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="1333" formatCode="#.###."/>
   </numFmts>
   <fonts count="70">
     <font>
@@ -1853,7 +2012,7 @@
   <cellStyleXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="1277" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
@@ -1863,7 +2022,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="8" borderId="2" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="1278" fontId="2" fillId="8" borderId="2" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -1879,20 +2038,20 @@
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" applyFont="0" applyFill="0" applyNumberFormat="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="4" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="1279" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="1278" fontId="2" fillId="0" borderId="4" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyFill="0" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="0" fillId="9" borderId="5" applyFont="0" applyNumberFormat="0" applyAlignment="0"/>
+    <xf numFmtId="1278" fontId="0" fillId="9" borderId="5" applyFont="0" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="1282" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="9" fontId="0" fillId="10" borderId="1" applyFont="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="1278" fontId="5" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyFill="0" applyNumberFormat="0">
@@ -1902,8 +2061,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyNumberFormat="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1"/>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" applyBorder="0">
+    <xf numFmtId="1284" fontId="2" fillId="0" borderId="1"/>
+    <xf numFmtId="1285" fontId="8" fillId="0" borderId="1" applyBorder="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1917,7 +2076,7 @@
     <xf numFmtId="37" fontId="12" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="1278" fontId="2" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -1932,7 +2091,7 @@
     <xf numFmtId="9" fontId="5" fillId="13" borderId="1" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="13" borderId="9" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0"/>
+    <xf numFmtId="1278" fontId="5" fillId="13" borderId="9" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -1990,10 +2149,10 @@
     <xf numFmtId="0" fontId="54" fillId="40" borderId="1" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="55" fillId="41" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="56" fillId="42" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="224" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="225" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="226" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="227" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="1329" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="1330" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="1331" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="1332" fontId="0" fillId="0" borderId="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="43" borderId="1" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="29" applyFill="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -2006,7 +2165,7 @@
     <xf numFmtId="0" fontId="0" fillId="45" borderId="33" applyFont="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="65" fillId="41" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyFill="0" applyNumberFormat="0"/>
-    <xf numFmtId="228" fontId="5" fillId="13" borderId="35" applyFill="0" applyBorder="0" applyNumberFormat="0">
+    <xf numFmtId="1333" fontId="5" fillId="13" borderId="35" applyFill="0" applyBorder="0" applyNumberFormat="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="13" borderId="7" applyFill="0" applyNumberFormat="0">
@@ -2020,7 +2179,7 @@
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="36" applyFill="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="5" fillId="13" borderId="37" applyNumberFormat="0">
+    <xf numFmtId="1278" fontId="5" fillId="13" borderId="37" applyNumberFormat="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="13" borderId="3" applyBorder="0" applyNumberFormat="0">
@@ -2040,7 +2199,7 @@
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -2086,19 +2245,19 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="14" xfId="0"/>
-    <xf numFmtId="185" fontId="27" fillId="14" borderId="15" xfId="32">
+    <xf numFmtId="1291" fontId="27" fillId="14" borderId="15" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="185" fontId="27" fillId="14" borderId="1" xfId="32">
+    <xf numFmtId="1291" fontId="27" fillId="14" borderId="1" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="185" fontId="27" fillId="14" borderId="16" xfId="32">
+    <xf numFmtId="1291" fontId="27" fillId="14" borderId="16" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="14" borderId="15" xfId="32">
+    <xf numFmtId="1277" fontId="27" fillId="14" borderId="15" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="14" borderId="16" xfId="32">
+    <xf numFmtId="1277" fontId="27" fillId="14" borderId="16" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="27" fillId="14" borderId="15" xfId="32">
@@ -2107,41 +2266,41 @@
     <xf numFmtId="3" fontId="27" fillId="14" borderId="16" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="27" fillId="14" borderId="15" xfId="32">
+    <xf numFmtId="1295" fontId="27" fillId="14" borderId="15" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="27" fillId="14" borderId="16" xfId="32">
+    <xf numFmtId="1295" fontId="27" fillId="14" borderId="16" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="14" borderId="15" xfId="0">
+    <xf numFmtId="1277" fontId="27" fillId="14" borderId="15" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="14" borderId="16" xfId="0">
+    <xf numFmtId="1277" fontId="27" fillId="14" borderId="16" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="16" xfId="0"/>
-    <xf numFmtId="193" fontId="28" fillId="14" borderId="17" xfId="32">
+    <xf numFmtId="1299" fontId="28" fillId="14" borderId="17" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="193" fontId="28" fillId="14" borderId="20" xfId="32">
+    <xf numFmtId="1299" fontId="28" fillId="14" borderId="20" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="194" fontId="29" fillId="14" borderId="18" xfId="32">
+    <xf numFmtId="1300" fontId="29" fillId="14" borderId="18" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="195" fontId="28" fillId="14" borderId="17" xfId="32">
+    <xf numFmtId="1301" fontId="28" fillId="14" borderId="17" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="196" fontId="29" fillId="14" borderId="18" xfId="32">
+    <xf numFmtId="1302" fontId="29" fillId="14" borderId="18" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="197" fontId="28" fillId="14" borderId="17" xfId="0">
+    <xf numFmtId="1303" fontId="28" fillId="14" borderId="17" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="198" fontId="29" fillId="14" borderId="18" xfId="0">
+    <xf numFmtId="1304" fontId="29" fillId="14" borderId="18" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="198" fontId="29" fillId="14" borderId="17" xfId="0">
+    <xf numFmtId="1304" fontId="29" fillId="14" borderId="17" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="18" xfId="0"/>
@@ -2180,28 +2339,28 @@
     <xf numFmtId="3" fontId="50" fillId="14" borderId="1" xfId="0" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="215" fontId="50" fillId="14" borderId="1" xfId="0" quotePrefix="1">
+    <xf numFmtId="1321" fontId="50" fillId="14" borderId="1" xfId="0" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="19" fillId="14" borderId="1" xfId="0">
+    <xf numFmtId="1288" fontId="19" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="14" borderId="1" xfId="0">
+    <xf numFmtId="1277" fontId="19" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="19" fillId="14" borderId="1" xfId="0">
+    <xf numFmtId="1290" fontId="19" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="14" borderId="1" xfId="36">
+    <xf numFmtId="1277" fontId="19" fillId="14" borderId="1" xfId="36">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="48" fillId="0" borderId="3" xfId="36">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="48" fillId="0" borderId="3" xfId="2">
+    <xf numFmtId="1277" fontId="48" fillId="0" borderId="3" xfId="2">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0">
@@ -2213,16 +2372,16 @@
     <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="14" borderId="1" xfId="32">
+    <xf numFmtId="1277" fontId="27" fillId="14" borderId="1" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="27" fillId="14" borderId="1" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="27" fillId="14" borderId="1" xfId="32">
+    <xf numFmtId="1295" fontId="27" fillId="14" borderId="1" xfId="32">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="14" borderId="1" xfId="0">
+    <xf numFmtId="1277" fontId="27" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" quotePrefix="1">
@@ -2235,10 +2394,10 @@
     <xf numFmtId="3" fontId="2" fillId="14" borderId="3" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="51" fillId="0" borderId="26" xfId="0">
+    <xf numFmtId="1327" fontId="51" fillId="0" borderId="26" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="52" fillId="0" borderId="26" xfId="0">
+    <xf numFmtId="1327" fontId="52" fillId="0" borderId="26" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="0">
@@ -2247,12 +2406,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="32">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="50" fillId="14" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="215" fontId="50" fillId="14" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="17" borderId="1" xfId="0">
@@ -2290,32 +2443,32 @@
     <xf numFmtId="0" fontId="23" fillId="18" borderId="20" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="23" fillId="18" borderId="20" xfId="0">
+    <xf numFmtId="1295" fontId="23" fillId="18" borderId="20" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="20" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="16" borderId="20" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="39" fillId="16" borderId="20" xfId="0">
+    <xf numFmtId="1295" fontId="39" fillId="16" borderId="20" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="34" fillId="16" borderId="20" xfId="0">
+    <xf numFmtId="1277" fontId="34" fillId="16" borderId="20" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="20" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="210" fontId="46" fillId="20" borderId="20" xfId="0">
+    <xf numFmtId="1316" fontId="46" fillId="20" borderId="20" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="211" fontId="47" fillId="20" borderId="20" xfId="0">
+    <xf numFmtId="1317" fontId="47" fillId="20" borderId="20" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="19" borderId="22" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="203" fontId="40" fillId="19" borderId="22" xfId="0">
+    <xf numFmtId="1309" fontId="40" fillId="19" borderId="22" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="19" borderId="22" xfId="0">
@@ -2354,31 +2507,31 @@
     <xf numFmtId="0" fontId="34" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="19" fillId="14" borderId="1" xfId="0">
+    <xf numFmtId="1295" fontId="19" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="205" fontId="19" fillId="14" borderId="1" xfId="0">
+    <xf numFmtId="1311" fontId="19" fillId="14" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="22" xfId="0"/>
-    <xf numFmtId="189" fontId="44" fillId="19" borderId="22" xfId="0">
+    <xf numFmtId="1295" fontId="44" fillId="19" borderId="22" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="20" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="20" xfId="0"/>
-    <xf numFmtId="189" fontId="19" fillId="16" borderId="20" xfId="0">
+    <xf numFmtId="1295" fontId="19" fillId="16" borderId="20" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="19" borderId="24" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="24" xfId="0"/>
-    <xf numFmtId="208" fontId="45" fillId="19" borderId="24" xfId="0">
+    <xf numFmtId="1314" fontId="45" fillId="19" borderId="24" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="209" fontId="34" fillId="19" borderId="24" xfId="0">
+    <xf numFmtId="1315" fontId="34" fillId="19" borderId="24" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2757,8 +2910,8 @@
           <c:extLst/>
           <c:spPr/>
         </c:ser>
-        <c:axId val="51217427"/>
-        <c:axId val="15046042"/>
+        <c:axId val="83540091"/>
+        <c:axId val="55622102"/>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:gapWidth val="60"/>
@@ -2766,7 +2919,7 @@
         <c:overlap val="-10"/>
       </c:barChart>
       <c:catAx axisType="0">
-        <c:axId val="51217427"/>
+        <c:axId val="83540091"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2776,7 +2929,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="15046042"/>
+        <c:crossAx val="55622102"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2810,7 +2963,7 @@
         <c:tickMarkSkip val="1"/>
       </c:catAx>
       <c:valAx axisType="3">
-        <c:axId val="15046042"/>
+        <c:axId val="55622102"/>
         <c:delete val="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2857,7 +3010,7 @@
         </c:majorGridlines>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:crossAx val="51217427"/>
+        <c:crossAx val="83540091"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3036,15 +3189,15 @@
             <a:ln w="19050"/>
           </c:spPr>
         </c:ser>
-        <c:axId val="87441254"/>
-        <c:axId val="16253614"/>
+        <c:axId val="37927784"/>
+        <c:axId val="95150954"/>
         <c:grouping val="standard"/>
         <c:varyColors val="1"/>
         <c:smooth val="0"/>
         <c:marker val="1"/>
       </c:lineChart>
       <c:catAx axisType="0">
-        <c:axId val="87441254"/>
+        <c:axId val="37927784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3054,7 +3207,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="16253614"/>
+        <c:crossAx val="95150954"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3088,7 +3241,7 @@
         <c:tickMarkSkip val="1"/>
       </c:catAx>
       <c:valAx axisType="3">
-        <c:axId val="16253614"/>
+        <c:axId val="95150954"/>
         <c:delete val="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3138,7 +3291,7 @@
         <c:majorUnit val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:crossAx val="87441254"/>
+        <c:crossAx val="37927784"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3399,8 +3552,8 @@
           <c:extLst/>
           <c:spPr/>
         </c:ser>
-        <c:axId val="33797582"/>
-        <c:axId val="58998765"/>
+        <c:axId val="51723296"/>
+        <c:axId val="39741988"/>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
         <c:gapWidth val="55"/>
@@ -3408,7 +3561,7 @@
         <c:overlap val="100"/>
       </c:barChart>
       <c:catAx axisType="0">
-        <c:axId val="33797582"/>
+        <c:axId val="51723296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3418,7 +3571,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="58998765"/>
+        <c:crossAx val="39741988"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3452,7 +3605,7 @@
         <c:tickMarkSkip val="1"/>
       </c:catAx>
       <c:valAx axisType="3">
-        <c:axId val="58998765"/>
+        <c:axId val="39741988"/>
         <c:delete val="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3499,7 +3652,7 @@
         </c:majorGridlines>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:crossAx val="33797582"/>
+        <c:crossAx val="51723296"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3706,8 +3859,8 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:axId val="82525312"/>
-        <c:axId val="37035994"/>
+        <c:axId val="98123738"/>
+        <c:axId val="43886086"/>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
         <c:gapWidth val="45"/>
@@ -3715,7 +3868,7 @@
         <c:overlap val="100"/>
       </c:barChart>
       <c:catAx axisType="0">
-        <c:axId val="82525312"/>
+        <c:axId val="98123738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3735,7 +3888,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37035994"/>
+        <c:crossAx val="43886086"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3756,7 +3909,7 @@
         <c:tickMarkSkip val="1"/>
       </c:catAx>
       <c:valAx axisType="3">
-        <c:axId val="37035994"/>
+        <c:axId val="43886086"/>
         <c:delete val="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3803,7 +3956,7 @@
         </c:majorGridlines>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:crossAx val="82525312"/>
+        <c:crossAx val="98123738"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3954,8 +4107,8 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:axId val="92800452"/>
-        <c:axId val="18007135"/>
+        <c:axId val="67013452"/>
+        <c:axId val="60008424"/>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:gapWidth val="45"/>
@@ -3963,7 +4116,7 @@
         <c:overlap val="-15"/>
       </c:barChart>
       <c:catAx axisType="0">
-        <c:axId val="92800452"/>
+        <c:axId val="67013452"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3973,7 +4126,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="18007135"/>
+        <c:crossAx val="60008424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4007,7 +4160,7 @@
         <c:tickMarkSkip val="1"/>
       </c:catAx>
       <c:valAx axisType="3">
-        <c:axId val="18007135"/>
+        <c:axId val="60008424"/>
         <c:delete val="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4054,7 +4207,7 @@
         </c:majorGridlines>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:crossAx val="92800452"/>
+        <c:crossAx val="67013452"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -8248,7 +8401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{ACA24448-A947-B3D5-A458-957B2754ED83}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{024E9CD8-E5B8-7118-C0B8-0583418814A8}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:X34"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="9.140625" customHeight="1"/>
   <sheetData>
@@ -8301,7 +8454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8AE737E8-2578-E958-6009-32D314D17F8A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2B44170B-28E6-3DE8-FD98-CB0AB2284E08}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:BK106"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -11503,7 +11656,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7d60e042-2620-449a-98a1-787c2c16d265}</x14:id>
+          <x14:id>{e9c7ee95-9e17-48b9-9079-01b5e5b06e60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11574,7 +11727,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7d60e042-2620-449a-98a1-787c2c16d265}">
+          <x14:cfRule type="dataBar" id="{e9c7ee95-9e17-48b9-9079-01b5e5b06e60}">
             <x14:dataBar minLength="0" maxLength="100" direction="leftToRight">
               <x14:color rgb="FFB8CFEC"/>
               <x14:cfvo type="num">
@@ -11597,7 +11750,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4FD16048-7218-26BF-7382-81E4C51DD638}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FA2C4AD7-EC34-E088-CEA8-B67A84D6799A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:BK145"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -11789,9 +11942,8 @@
       <c r="O11" s="69"/>
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
-      <c r="R11" s="10"/>
-    </row>
-    <row r="12" ht="40.5" customHeight="1">
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
       <c r="C12" s="70" t="s">
         <v>88</v>
       </c>
@@ -11908,7 +12060,7 @@
         <v>112</v>
       </c>
       <c r="S13" s="74">
-        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M13,$M13+SUMIFS($M$13:$M$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"Fermer")*$I13/SUMIFS($I$13:$I$72,$C$13:$C$72,$C13,$D$13:$D$72,$D13,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M13,$M13+SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I13/SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T13" s="75">
         <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",$J13-$K13-$S13))</f>
@@ -11975,7 +12127,7 @@
         <v>115</v>
       </c>
       <c r="S14" s="74">
-        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M14,$M14+SUMIFS($M$13:$M$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"Fermer")*$I14/SUMIFS($I$13:$I$72,$C$13:$C$72,$C14,$D$13:$D$72,$D14,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M14,$M14+SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I14/SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T14" s="75">
         <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",$J14-$K14-$S14))</f>
@@ -12037,7 +12189,7 @@
         <v>115</v>
       </c>
       <c r="S15" s="74">
-        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M15,$M15+SUMIFS($M$13:$M$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"Fermer")*$I15/SUMIFS($I$13:$I$72,$C$13:$C$72,$C15,$D$13:$D$72,$D15,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M15,$M15+SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I15/SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T15" s="75">
         <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",$J15-$K15-$S15))</f>
@@ -12054,7 +12206,7 @@
         <v>107</v>
       </c>
       <c r="D16" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" s="73" t="s">
         <v>109</v>
@@ -12099,7 +12251,7 @@
         <v>112</v>
       </c>
       <c r="S16" s="74">
-        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M16,$M16+SUMIFS($M$13:$M$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"Fermer")*$I16/SUMIFS($I$13:$I$72,$C$13:$C$72,$C16,$D$13:$D$72,$D16,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M16,$M16+SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I16/SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T16" s="75">
         <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",$J16-$K16-$S16))</f>
@@ -12116,7 +12268,7 @@
         <v>107</v>
       </c>
       <c r="D17" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E17" s="73" t="s">
         <v>109</v>
@@ -12161,7 +12313,7 @@
         <v>115</v>
       </c>
       <c r="S17" s="74">
-        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M17,$M17+SUMIFS($M$13:$M$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"Fermer")*$I17/SUMIFS($I$13:$I$72,$C$13:$C$72,$C17,$D$13:$D$72,$D17,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M17,$M17+SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I17/SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T17" s="75">
         <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",$J17-$K17-$S17))</f>
@@ -12178,7 +12330,7 @@
         <v>107</v>
       </c>
       <c r="D18" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E18" s="73" t="s">
         <v>109</v>
@@ -12223,7 +12375,7 @@
         <v>115</v>
       </c>
       <c r="S18" s="74">
-        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M18,$M18+SUMIFS($M$13:$M$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"Fermer")*$I18/SUMIFS($I$13:$I$72,$C$13:$C$72,$C18,$D$13:$D$72,$D18,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M18,$M18+SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I18/SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T18" s="75">
         <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",$J18-$K18-$S18))</f>
@@ -12240,7 +12392,7 @@
         <v>107</v>
       </c>
       <c r="D19" s="73" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E19" s="73" t="s">
         <v>109</v>
@@ -12285,7 +12437,7 @@
         <v>112</v>
       </c>
       <c r="S19" s="74">
-        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M19,$M19+SUMIFS($M$13:$M$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"Fermer")*$I19/SUMIFS($I$13:$I$72,$C$13:$C$72,$C19,$D$13:$D$72,$D19,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M19,$M19+SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I19/SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T19" s="75">
         <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",$J19-$K19-$S19))</f>
@@ -12302,7 +12454,7 @@
         <v>107</v>
       </c>
       <c r="D20" s="73" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E20" s="73" t="s">
         <v>109</v>
@@ -12347,7 +12499,7 @@
         <v>115</v>
       </c>
       <c r="S20" s="74">
-        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M20,$M20+SUMIFS($M$13:$M$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"Fermer")*$I20/SUMIFS($I$13:$I$72,$C$13:$C$72,$C20,$D$13:$D$72,$D20,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M20,$M20+SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I20/SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T20" s="75">
         <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",$J20-$K20-$S20))</f>
@@ -12364,7 +12516,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="73" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E21" s="73" t="s">
         <v>109</v>
@@ -12409,7 +12561,7 @@
         <v>115</v>
       </c>
       <c r="S21" s="74">
-        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M21,$M21+SUMIFS($M$13:$M$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"Fermer")*$I21/SUMIFS($I$13:$I$72,$C$13:$C$72,$C21,$D$13:$D$72,$D21,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M21,$M21+SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I21/SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T21" s="75">
         <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",$J21-$K21-$S21))</f>
@@ -12426,16 +12578,16 @@
         <v>35</v>
       </c>
       <c r="D22" s="73" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E22" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F22" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G22" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H22" s="73">
         <v>54.601406</v>
@@ -12471,7 +12623,7 @@
         <v>112</v>
       </c>
       <c r="S22" s="74">
-        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M22,$M22+SUMIFS($M$13:$M$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"Fermer")*$I22/SUMIFS($I$13:$I$72,$C$13:$C$72,$C22,$D$13:$D$72,$D22,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M22,$M22+SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I22/SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T22" s="75">
         <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",$J22-$K22-$S22))</f>
@@ -12488,10 +12640,10 @@
         <v>35</v>
       </c>
       <c r="D23" s="73" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E23" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F23" s="73" t="s">
         <v>114</v>
@@ -12533,7 +12685,7 @@
         <v>115</v>
       </c>
       <c r="S23" s="74">
-        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M23,$M23+SUMIFS($M$13:$M$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"Fermer")*$I23/SUMIFS($I$13:$I$72,$C$13:$C$72,$C23,$D$13:$D$72,$D23,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M23,$M23+SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I23/SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T23" s="75">
         <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",$J23-$K23-$S23))</f>
@@ -12550,10 +12702,10 @@
         <v>35</v>
       </c>
       <c r="D24" s="73" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E24" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F24" s="73" t="s">
         <v>117</v>
@@ -12595,7 +12747,7 @@
         <v>115</v>
       </c>
       <c r="S24" s="74">
-        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M24,$M24+SUMIFS($M$13:$M$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"Fermer")*$I24/SUMIFS($I$13:$I$72,$C$13:$C$72,$C24,$D$13:$D$72,$D24,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M24,$M24+SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I24/SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T24" s="75">
         <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",$J24-$K24-$S24))</f>
@@ -12612,13 +12764,13 @@
         <v>35</v>
       </c>
       <c r="D25" s="73" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E25" s="73" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F25" s="73" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G25" s="73" t="s">
         <v>111</v>
@@ -12657,7 +12809,7 @@
         <v>112</v>
       </c>
       <c r="S25" s="74">
-        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M25,$M25+SUMIFS($M$13:$M$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"Fermer")*$I25/SUMIFS($I$13:$I$72,$C$13:$C$72,$C25,$D$13:$D$72,$D25,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M25,$M25+SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I25/SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T25" s="75">
         <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",$J25-$K25-$S25))</f>
@@ -12674,13 +12826,13 @@
         <v>35</v>
       </c>
       <c r="D26" s="73" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E26" s="73" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F26" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G26" s="73" t="s">
         <v>111</v>
@@ -12719,7 +12871,7 @@
         <v>115</v>
       </c>
       <c r="S26" s="74">
-        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M26,$M26+SUMIFS($M$13:$M$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"Fermer")*$I26/SUMIFS($I$13:$I$72,$C$13:$C$72,$C26,$D$13:$D$72,$D26,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M26,$M26+SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I26/SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T26" s="75">
         <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",$J26-$K26-$S26))</f>
@@ -12736,16 +12888,16 @@
         <v>35</v>
       </c>
       <c r="D27" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E27" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F27" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G27" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H27" s="73">
         <v>78.323408</v>
@@ -12781,7 +12933,7 @@
         <v>112</v>
       </c>
       <c r="S27" s="74">
-        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M27,$M27+SUMIFS($M$13:$M$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"Fermer")*$I27/SUMIFS($I$13:$I$72,$C$13:$C$72,$C27,$D$13:$D$72,$D27,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M27,$M27+SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I27/SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T27" s="75">
         <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",$J27-$K27-$S27))</f>
@@ -12798,10 +12950,10 @@
         <v>35</v>
       </c>
       <c r="D28" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E28" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F28" s="73" t="s">
         <v>114</v>
@@ -12843,7 +12995,7 @@
         <v>115</v>
       </c>
       <c r="S28" s="74">
-        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M28,$M28+SUMIFS($M$13:$M$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"Fermer")*$I28/SUMIFS($I$13:$I$72,$C$13:$C$72,$C28,$D$13:$D$72,$D28,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M28,$M28+SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I28/SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T28" s="75">
         <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",$J28-$K28-$S28))</f>
@@ -12860,10 +13012,10 @@
         <v>35</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E29" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F29" s="73" t="s">
         <v>117</v>
@@ -12905,7 +13057,7 @@
         <v>115</v>
       </c>
       <c r="S29" s="74">
-        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M29,$M29+SUMIFS($M$13:$M$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"Fermer")*$I29/SUMIFS($I$13:$I$72,$C$13:$C$72,$C29,$D$13:$D$72,$D29,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M29,$M29+SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I29/SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T29" s="75">
         <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",$J29-$K29-$S29))</f>
@@ -12922,13 +13074,13 @@
         <v>35</v>
       </c>
       <c r="D30" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E30" s="73" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F30" s="73" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G30" s="73" t="s">
         <v>111</v>
@@ -12967,7 +13119,7 @@
         <v>112</v>
       </c>
       <c r="S30" s="74">
-        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M30,$M30+SUMIFS($M$13:$M$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"Fermer")*$I30/SUMIFS($I$13:$I$72,$C$13:$C$72,$C30,$D$13:$D$72,$D30,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M30,$M30+SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I30/SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T30" s="75">
         <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",$J30-$K30-$S30))</f>
@@ -12984,13 +13136,13 @@
         <v>35</v>
       </c>
       <c r="D31" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E31" s="73" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F31" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G31" s="73" t="s">
         <v>111</v>
@@ -13029,7 +13181,7 @@
         <v>115</v>
       </c>
       <c r="S31" s="74">
-        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M31,$M31+SUMIFS($M$13:$M$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"Fermer")*$I31/SUMIFS($I$13:$I$72,$C$13:$C$72,$C31,$D$13:$D$72,$D31,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M31,$M31+SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I31/SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T31" s="75">
         <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",$J31-$K31-$S31))</f>
@@ -13046,16 +13198,16 @@
         <v>35</v>
       </c>
       <c r="D32" s="73" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E32" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F32" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G32" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H32" s="73">
         <v>51.351967</v>
@@ -13091,7 +13243,7 @@
         <v>112</v>
       </c>
       <c r="S32" s="74">
-        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M32,$M32+SUMIFS($M$13:$M$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"Fermer")*$I32/SUMIFS($I$13:$I$72,$C$13:$C$72,$C32,$D$13:$D$72,$D32,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M32,$M32+SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I32/SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T32" s="75">
         <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",$J32-$K32-$S32))</f>
@@ -13108,10 +13260,10 @@
         <v>35</v>
       </c>
       <c r="D33" s="73" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E33" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F33" s="73" t="s">
         <v>114</v>
@@ -13153,7 +13305,7 @@
         <v>115</v>
       </c>
       <c r="S33" s="74">
-        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M33,$M33+SUMIFS($M$13:$M$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"Fermer")*$I33/SUMIFS($I$13:$I$72,$C$13:$C$72,$C33,$D$13:$D$72,$D33,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M33,$M33+SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I33/SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T33" s="75">
         <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",$J33-$K33-$S33))</f>
@@ -13170,10 +13322,10 @@
         <v>35</v>
       </c>
       <c r="D34" s="73" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E34" s="73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F34" s="73" t="s">
         <v>117</v>
@@ -13215,7 +13367,7 @@
         <v>115</v>
       </c>
       <c r="S34" s="74">
-        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M34,$M34+SUMIFS($M$13:$M$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"Fermer")*$I34/SUMIFS($I$13:$I$72,$C$13:$C$72,$C34,$D$13:$D$72,$D34,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M34,$M34+SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I34/SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T34" s="75">
         <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",$J34-$K34-$S34))</f>
@@ -13232,13 +13384,13 @@
         <v>35</v>
       </c>
       <c r="D35" s="73" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E35" s="73" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F35" s="73" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G35" s="73" t="s">
         <v>111</v>
@@ -13277,7 +13429,7 @@
         <v>112</v>
       </c>
       <c r="S35" s="74">
-        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M35,$M35+SUMIFS($M$13:$M$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"Fermer")*$I35/SUMIFS($I$13:$I$72,$C$13:$C$72,$C35,$D$13:$D$72,$D35,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M35,$M35+SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I35/SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T35" s="75">
         <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",$J35-$K35-$S35))</f>
@@ -13294,13 +13446,13 @@
         <v>35</v>
       </c>
       <c r="D36" s="73" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E36" s="73" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F36" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G36" s="73" t="s">
         <v>111</v>
@@ -13339,7 +13491,7 @@
         <v>115</v>
       </c>
       <c r="S36" s="74">
-        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M36,$M36+SUMIFS($M$13:$M$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"Fermer")*$I36/SUMIFS($I$13:$I$72,$C$13:$C$72,$C36,$D$13:$D$72,$D36,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M36,$M36+SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I36/SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T36" s="75">
         <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",$J36-$K36-$S36))</f>
@@ -13353,19 +13505,19 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="C37" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D37" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E37" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F37" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G37" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H37" s="73">
         <v>55.74675</v>
@@ -13401,7 +13553,7 @@
         <v>112</v>
       </c>
       <c r="S37" s="74">
-        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M37,$M37+SUMIFS($M$13:$M$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"Fermer")*$I37/SUMIFS($I$13:$I$72,$C$13:$C$72,$C37,$D$13:$D$72,$D37,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M37,$M37+SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I37/SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T37" s="75">
         <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",$J37-$K37-$S37))</f>
@@ -13416,13 +13568,13 @@
     <row r="38" ht="14.25" customHeight="1">
       <c r="B38" s="78"/>
       <c r="C38" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E38" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F38" s="73" t="s">
         <v>114</v>
@@ -13464,7 +13616,7 @@
         <v>115</v>
       </c>
       <c r="S38" s="74">
-        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M38,$M38+SUMIFS($M$13:$M$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"Fermer")*$I38/SUMIFS($I$13:$I$72,$C$13:$C$72,$C38,$D$13:$D$72,$D38,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M38,$M38+SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I38/SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T38" s="75">
         <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",$J38-$K38-$S38))</f>
@@ -13488,13 +13640,13 @@
     <row r="39" ht="14.25" customHeight="1">
       <c r="B39" s="78"/>
       <c r="C39" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D39" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E39" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F39" s="73" t="s">
         <v>117</v>
@@ -13536,7 +13688,7 @@
         <v>115</v>
       </c>
       <c r="S39" s="74">
-        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M39,$M39+SUMIFS($M$13:$M$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"Fermer")*$I39/SUMIFS($I$13:$I$72,$C$13:$C$72,$C39,$D$13:$D$72,$D39,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M39,$M39+SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I39/SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T39" s="75">
         <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",$J39-$K39-$S39))</f>
@@ -13560,16 +13712,16 @@
     <row r="40" ht="14.25" customHeight="1">
       <c r="B40" s="78"/>
       <c r="C40" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D40" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E40" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="73" t="s">
         <v>131</v>
-      </c>
-      <c r="F40" s="73" t="s">
-        <v>124</v>
       </c>
       <c r="G40" s="73" t="s">
         <v>111</v>
@@ -13608,7 +13760,7 @@
         <v>112</v>
       </c>
       <c r="S40" s="74">
-        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M40,$M40+SUMIFS($M$13:$M$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"Fermer")*$I40/SUMIFS($I$13:$I$72,$C$13:$C$72,$C40,$D$13:$D$72,$D40,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M40,$M40+SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I40/SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T40" s="75">
         <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",$J40-$K40-$S40))</f>
@@ -13632,16 +13784,16 @@
     <row r="41" ht="14.25" customHeight="1">
       <c r="B41" s="78"/>
       <c r="C41" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D41" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E41" s="73" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="F41" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G41" s="73" t="s">
         <v>111</v>
@@ -13680,7 +13832,7 @@
         <v>115</v>
       </c>
       <c r="S41" s="74">
-        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M41,$M41+SUMIFS($M$13:$M$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"Fermer")*$I41/SUMIFS($I$13:$I$72,$C$13:$C$72,$C41,$D$13:$D$72,$D41,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M41,$M41+SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I41/SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T41" s="75">
         <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",$J41-$K41-$S41))</f>
@@ -13704,19 +13856,19 @@
     <row r="42" ht="14.25" customHeight="1">
       <c r="B42" s="78"/>
       <c r="C42" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D42" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E42" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F42" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G42" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H42" s="73">
         <v>72.005855</v>
@@ -13752,7 +13904,7 @@
         <v>112</v>
       </c>
       <c r="S42" s="74">
-        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M42,$M42+SUMIFS($M$13:$M$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"Fermer")*$I42/SUMIFS($I$13:$I$72,$C$13:$C$72,$C42,$D$13:$D$72,$D42,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M42,$M42+SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I42/SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T42" s="75">
         <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",$J42-$K42-$S42))</f>
@@ -13776,13 +13928,13 @@
     <row r="43" ht="14.25" customHeight="1">
       <c r="B43" s="78"/>
       <c r="C43" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D43" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E43" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F43" s="73" t="s">
         <v>114</v>
@@ -13824,7 +13976,7 @@
         <v>115</v>
       </c>
       <c r="S43" s="74">
-        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M43,$M43+SUMIFS($M$13:$M$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"Fermer")*$I43/SUMIFS($I$13:$I$72,$C$13:$C$72,$C43,$D$13:$D$72,$D43,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M43,$M43+SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I43/SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T43" s="75">
         <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",$J43-$K43-$S43))</f>
@@ -13848,13 +14000,13 @@
     <row r="44" ht="14.25" customHeight="1">
       <c r="B44" s="78"/>
       <c r="C44" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D44" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E44" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F44" s="73" t="s">
         <v>117</v>
@@ -13896,7 +14048,7 @@
         <v>115</v>
       </c>
       <c r="S44" s="74">
-        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M44,$M44+SUMIFS($M$13:$M$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"Fermer")*$I44/SUMIFS($I$13:$I$72,$C$13:$C$72,$C44,$D$13:$D$72,$D44,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M44,$M44+SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I44/SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T44" s="75">
         <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",$J44-$K44-$S44))</f>
@@ -13920,16 +14072,16 @@
     <row r="45" ht="14.25" customHeight="1">
       <c r="B45" s="78"/>
       <c r="C45" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D45" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E45" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="F45" s="73" t="s">
         <v>131</v>
-      </c>
-      <c r="F45" s="73" t="s">
-        <v>124</v>
       </c>
       <c r="G45" s="73" t="s">
         <v>111</v>
@@ -13968,7 +14120,7 @@
         <v>112</v>
       </c>
       <c r="S45" s="74">
-        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M45,$M45+SUMIFS($M$13:$M$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"Fermer")*$I45/SUMIFS($I$13:$I$72,$C$13:$C$72,$C45,$D$13:$D$72,$D45,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M45,$M45+SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I45/SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T45" s="75">
         <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",$J45-$K45-$S45))</f>
@@ -13992,16 +14144,16 @@
     <row r="46" ht="14.25" customHeight="1">
       <c r="B46" s="78"/>
       <c r="C46" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D46" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E46" s="73" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="F46" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G46" s="73" t="s">
         <v>111</v>
@@ -14040,7 +14192,7 @@
         <v>115</v>
       </c>
       <c r="S46" s="74">
-        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M46,$M46+SUMIFS($M$13:$M$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"Fermer")*$I46/SUMIFS($I$13:$I$72,$C$13:$C$72,$C46,$D$13:$D$72,$D46,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M46,$M46+SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I46/SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T46" s="75">
         <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",$J46-$K46-$S46))</f>
@@ -14064,19 +14216,19 @@
     <row r="47" ht="14.25" customHeight="1">
       <c r="B47" s="78"/>
       <c r="C47" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D47" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E47" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F47" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G47" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H47" s="73">
         <v>65.539302</v>
@@ -14112,7 +14264,7 @@
         <v>112</v>
       </c>
       <c r="S47" s="74">
-        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M47,$M47+SUMIFS($M$13:$M$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"Fermer")*$I47/SUMIFS($I$13:$I$72,$C$13:$C$72,$C47,$D$13:$D$72,$D47,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M47,$M47+SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I47/SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T47" s="75">
         <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",$J47-$K47-$S47))</f>
@@ -14136,13 +14288,13 @@
     <row r="48" ht="14.25" customHeight="1">
       <c r="B48" s="78"/>
       <c r="C48" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D48" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E48" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F48" s="73" t="s">
         <v>114</v>
@@ -14184,7 +14336,7 @@
         <v>115</v>
       </c>
       <c r="S48" s="74">
-        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M48,$M48+SUMIFS($M$13:$M$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"Fermer")*$I48/SUMIFS($I$13:$I$72,$C$13:$C$72,$C48,$D$13:$D$72,$D48,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M48,$M48+SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I48/SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T48" s="75">
         <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",$J48-$K48-$S48))</f>
@@ -14208,13 +14360,13 @@
     <row r="49" ht="14.25" customHeight="1">
       <c r="B49" s="78"/>
       <c r="C49" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D49" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E49" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F49" s="73" t="s">
         <v>117</v>
@@ -14256,7 +14408,7 @@
         <v>115</v>
       </c>
       <c r="S49" s="74">
-        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M49,$M49+SUMIFS($M$13:$M$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"Fermer")*$I49/SUMIFS($I$13:$I$72,$C$13:$C$72,$C49,$D$13:$D$72,$D49,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M49,$M49+SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I49/SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T49" s="75">
         <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",$J49-$K49-$S49))</f>
@@ -14280,16 +14432,16 @@
     <row r="50" ht="14.25" customHeight="1">
       <c r="B50" s="78"/>
       <c r="C50" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D50" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E50" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="F50" s="73" t="s">
         <v>131</v>
-      </c>
-      <c r="F50" s="73" t="s">
-        <v>124</v>
       </c>
       <c r="G50" s="73" t="s">
         <v>111</v>
@@ -14328,7 +14480,7 @@
         <v>112</v>
       </c>
       <c r="S50" s="74">
-        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M50,$M50+SUMIFS($M$13:$M$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"Fermer")*$I50/SUMIFS($I$13:$I$72,$C$13:$C$72,$C50,$D$13:$D$72,$D50,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M50,$M50+SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I50/SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T50" s="75">
         <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",$J50-$K50-$S50))</f>
@@ -14352,16 +14504,16 @@
     <row r="51" ht="14.25" customHeight="1">
       <c r="B51" s="78"/>
       <c r="C51" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D51" s="73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E51" s="73" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="F51" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G51" s="73" t="s">
         <v>111</v>
@@ -14400,7 +14552,7 @@
         <v>115</v>
       </c>
       <c r="S51" s="74">
-        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M51,$M51+SUMIFS($M$13:$M$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"Fermer")*$I51/SUMIFS($I$13:$I$72,$C$13:$C$72,$C51,$D$13:$D$72,$D51,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M51,$M51+SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I51/SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T51" s="75">
         <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",$J51-$K51-$S51))</f>
@@ -14424,19 +14576,19 @@
     <row r="52" ht="14.25" customHeight="1">
       <c r="B52" s="78"/>
       <c r="C52" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D52" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E52" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F52" s="73" t="s">
         <v>110</v>
       </c>
       <c r="G52" s="73" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H52" s="73">
         <v>84.920597</v>
@@ -14472,7 +14624,7 @@
         <v>112</v>
       </c>
       <c r="S52" s="74">
-        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M52,$M52+SUMIFS($M$13:$M$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"Fermer")*$I52/SUMIFS($I$13:$I$72,$C$13:$C$72,$C52,$D$13:$D$72,$D52,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M52,$M52+SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I52/SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T52" s="75">
         <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",$J52-$K52-$S52))</f>
@@ -14496,13 +14648,13 @@
     <row r="53" ht="14.25" customHeight="1">
       <c r="B53" s="78"/>
       <c r="C53" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D53" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E53" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F53" s="73" t="s">
         <v>114</v>
@@ -14544,7 +14696,7 @@
         <v>115</v>
       </c>
       <c r="S53" s="74">
-        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M53,$M53+SUMIFS($M$13:$M$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"Fermer")*$I53/SUMIFS($I$13:$I$72,$C$13:$C$72,$C53,$D$13:$D$72,$D53,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M53,$M53+SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I53/SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T53" s="75">
         <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",$J53-$K53-$S53))</f>
@@ -14568,13 +14720,13 @@
     <row r="54" ht="14.25" customHeight="1">
       <c r="B54" s="78"/>
       <c r="C54" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D54" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E54" s="73" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F54" s="73" t="s">
         <v>117</v>
@@ -14616,7 +14768,7 @@
         <v>115</v>
       </c>
       <c r="S54" s="74">
-        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M54,$M54+SUMIFS($M$13:$M$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"Fermer")*$I54/SUMIFS($I$13:$I$72,$C$13:$C$72,$C54,$D$13:$D$72,$D54,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M54,$M54+SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I54/SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T54" s="75">
         <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",$J54-$K54-$S54))</f>
@@ -14640,16 +14792,16 @@
     <row r="55" ht="14.25" customHeight="1">
       <c r="B55" s="78"/>
       <c r="C55" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D55" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E55" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="F55" s="73" t="s">
         <v>131</v>
-      </c>
-      <c r="F55" s="73" t="s">
-        <v>124</v>
       </c>
       <c r="G55" s="73" t="s">
         <v>111</v>
@@ -14688,7 +14840,7 @@
         <v>112</v>
       </c>
       <c r="S55" s="74">
-        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M55,$M55+SUMIFS($M$13:$M$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"Fermer")*$I55/SUMIFS($I$13:$I$72,$C$13:$C$72,$C55,$D$13:$D$72,$D55,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M55,$M55+SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I55/SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T55" s="75">
         <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",$J55-$K55-$S55))</f>
@@ -14712,16 +14864,16 @@
     <row r="56" ht="14.25" customHeight="1">
       <c r="B56" s="78"/>
       <c r="C56" s="73" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D56" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E56" s="73" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="F56" s="73" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G56" s="73" t="s">
         <v>111</v>
@@ -14760,7 +14912,7 @@
         <v>115</v>
       </c>
       <c r="S56" s="74">
-        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M56,$M56+SUMIFS($M$13:$M$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"Fermer")*$I56/SUMIFS($I$13:$I$72,$C$13:$C$72,$C56,$D$13:$D$72,$D56,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M56,$M56+SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I56/SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T56" s="75">
         <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",$J56-$K56-$S56))</f>
@@ -14784,16 +14936,16 @@
     <row r="57" ht="14.25" customHeight="1">
       <c r="B57" s="63"/>
       <c r="C57" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D57" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="F57" s="73" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="G57" s="73" t="s">
         <v>111</v>
@@ -14832,7 +14984,7 @@
         <v>112</v>
       </c>
       <c r="S57" s="74">
-        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M57,$M57+SUMIFS($M$13:$M$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"Fermer")*$I57/SUMIFS($I$13:$I$72,$C$13:$C$72,$C57,$D$13:$D$72,$D57,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M57,$M57+SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I57/SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T57" s="75">
         <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",$J57-$K57-$S57))</f>
@@ -14856,16 +15008,16 @@
     <row r="58" ht="14.25" customHeight="1">
       <c r="B58" s="63"/>
       <c r="C58" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D58" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="F58" s="73" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="G58" s="73" t="s">
         <v>111</v>
@@ -14904,7 +15056,7 @@
         <v>115</v>
       </c>
       <c r="S58" s="74">
-        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M58,$M58+SUMIFS($M$13:$M$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"Fermer")*$I58/SUMIFS($I$13:$I$72,$C$13:$C$72,$C58,$D$13:$D$72,$D58,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M58,$M58+SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I58/SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T58" s="75">
         <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",$J58-$K58-$S58))</f>
@@ -14928,13 +15080,13 @@
     <row r="59" ht="14.25" customHeight="1">
       <c r="B59" s="63"/>
       <c r="C59" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D59" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F59" s="73" t="s">
         <v>110</v>
@@ -14976,7 +15128,7 @@
         <v>112</v>
       </c>
       <c r="S59" s="74">
-        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M59,$M59+SUMIFS($M$13:$M$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"Fermer")*$I59/SUMIFS($I$13:$I$72,$C$13:$C$72,$C59,$D$13:$D$72,$D59,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M59,$M59+SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I59/SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T59" s="75">
         <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",$J59-$K59-$S59))</f>
@@ -15000,13 +15152,13 @@
     <row r="60" ht="14.25" customHeight="1">
       <c r="B60" s="63"/>
       <c r="C60" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D60" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E60" s="73" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F60" s="73" t="s">
         <v>114</v>
@@ -15048,7 +15200,7 @@
         <v>115</v>
       </c>
       <c r="S60" s="74">
-        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M60,$M60+SUMIFS($M$13:$M$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"Fermer")*$I60/SUMIFS($I$13:$I$72,$C$13:$C$72,$C60,$D$13:$D$72,$D60,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M60,$M60+SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I60/SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T60" s="75">
         <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",$J60-$K60-$S60))</f>
@@ -15063,13 +15215,13 @@
     <row r="61" ht="14.25" customHeight="1">
       <c r="B61" s="63"/>
       <c r="C61" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D61" s="73" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F61" s="73" t="s">
         <v>117</v>
@@ -15111,7 +15263,7 @@
         <v>115</v>
       </c>
       <c r="S61" s="74">
-        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M61,$M61+SUMIFS($M$13:$M$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"Fermer")*$I61/SUMIFS($I$13:$I$72,$C$13:$C$72,$C61,$D$13:$D$72,$D61,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M61,$M61+SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I61/SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T61" s="75">
         <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",$J61-$K61-$S61))</f>
@@ -15126,13 +15278,13 @@
     <row r="62" ht="14.25" customHeight="1">
       <c r="B62" s="63"/>
       <c r="C62" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D62" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E62" s="73" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F62" s="73" t="s">
         <v>117</v>
@@ -15174,7 +15326,7 @@
         <v>115</v>
       </c>
       <c r="S62" s="74">
-        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M62,$M62+SUMIFS($M$13:$M$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"Fermer")*$I62/SUMIFS($I$13:$I$72,$C$13:$C$72,$C62,$D$13:$D$72,$D62,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M62,$M62+SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I62/SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T62" s="75">
         <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",$J62-$K62-$S62))</f>
@@ -15189,13 +15341,13 @@
     <row r="63" ht="14.25" customHeight="1">
       <c r="B63" s="63"/>
       <c r="C63" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D63" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E63" s="73" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F63" s="73" t="s">
         <v>114</v>
@@ -15237,7 +15389,7 @@
         <v>115</v>
       </c>
       <c r="S63" s="74">
-        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M63,$M63+SUMIFS($M$13:$M$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"Fermer")*$I63/SUMIFS($I$13:$I$72,$C$13:$C$72,$C63,$D$13:$D$72,$D63,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M63,$M63+SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I63/SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T63" s="75">
         <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",$J63-$K63-$S63))</f>
@@ -15252,16 +15404,16 @@
     <row r="64" ht="14.25" customHeight="1">
       <c r="B64" s="63"/>
       <c r="C64" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D64" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E64" s="73" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="F64" s="73" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="G64" s="73" t="s">
         <v>111</v>
@@ -15300,7 +15452,7 @@
         <v>112</v>
       </c>
       <c r="S64" s="74">
-        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M64,$M64+SUMIFS($M$13:$M$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"Fermer")*$I64/SUMIFS($I$13:$I$72,$C$13:$C$72,$C64,$D$13:$D$72,$D64,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M64,$M64+SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I64/SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T64" s="75">
         <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",$J64-$K64-$S64))</f>
@@ -15315,16 +15467,16 @@
     <row r="65" ht="14.25" customHeight="1">
       <c r="B65" s="63"/>
       <c r="C65" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D65" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E65" s="73" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="F65" s="73" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="G65" s="73" t="s">
         <v>111</v>
@@ -15363,7 +15515,7 @@
         <v>115</v>
       </c>
       <c r="S65" s="74">
-        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M65,$M65+SUMIFS($M$13:$M$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"Fermer")*$I65/SUMIFS($I$13:$I$72,$C$13:$C$72,$C65,$D$13:$D$72,$D65,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M65,$M65+SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I65/SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T65" s="75">
         <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",$J65-$K65-$S65))</f>
@@ -15378,13 +15530,13 @@
     <row r="66" ht="14.25" customHeight="1">
       <c r="B66" s="63"/>
       <c r="C66" s="73" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D66" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E66" s="73" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F66" s="73" t="s">
         <v>110</v>
@@ -15426,7 +15578,7 @@
         <v>112</v>
       </c>
       <c r="S66" s="74">
-        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M66,$M66+SUMIFS($M$13:$M$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"Fermer")*$I66/SUMIFS($I$13:$I$72,$C$13:$C$72,$C66,$D$13:$D$72,$D66,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M66,$M66+SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I66/SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T66" s="75">
         <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",$J66-$K66-$S66))</f>
@@ -15441,13 +15593,13 @@
     <row r="67" ht="14.25" customHeight="1">
       <c r="B67" s="63"/>
       <c r="C67" s="73" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D67" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E67" s="73" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="F67" s="73" t="s">
         <v>110</v>
@@ -15489,7 +15641,7 @@
         <v>112</v>
       </c>
       <c r="S67" s="74">
-        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M67,$M67+SUMIFS($M$13:$M$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"Fermer")*$I67/SUMIFS($I$13:$I$72,$C$13:$C$72,$C67,$D$13:$D$72,$D67,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M67,$M67+SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I67/SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T67" s="75">
         <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",$J67-$K67-$S67))</f>
@@ -15504,13 +15656,13 @@
     <row r="68" ht="14.25" customHeight="1">
       <c r="B68" s="63"/>
       <c r="C68" s="73" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D68" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E68" s="73" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="F68" s="73" t="s">
         <v>114</v>
@@ -15552,7 +15704,7 @@
         <v>115</v>
       </c>
       <c r="S68" s="74">
-        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M68,$M68+SUMIFS($M$13:$M$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"Fermer")*$I68/SUMIFS($I$13:$I$72,$C$13:$C$72,$C68,$D$13:$D$72,$D68,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M68,$M68+SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I68/SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T68" s="75">
         <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",$J68-$K68-$S68))</f>
@@ -15567,13 +15719,13 @@
     <row r="69" ht="14.25" customHeight="1">
       <c r="B69" s="63"/>
       <c r="C69" s="73" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D69" s="73" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E69" s="73" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="F69" s="73" t="s">
         <v>117</v>
@@ -15615,7 +15767,7 @@
         <v>115</v>
       </c>
       <c r="S69" s="74">
-        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M69,$M69+SUMIFS($M$13:$M$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"Fermer")*$I69/SUMIFS($I$13:$I$72,$C$13:$C$72,$C69,$D$13:$D$72,$D69,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M69,$M69+SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I69/SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T69" s="75">
         <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",$J69-$K69-$S69))</f>
@@ -15630,13 +15782,13 @@
     <row r="70" ht="14.25" customHeight="1">
       <c r="B70" s="63"/>
       <c r="C70" s="73" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D70" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E70" s="73" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="F70" s="73" t="s">
         <v>110</v>
@@ -15678,7 +15830,7 @@
         <v>112</v>
       </c>
       <c r="S70" s="74">
-        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M70,$M70+SUMIFS($M$13:$M$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"Fermer")*$I70/SUMIFS($I$13:$I$72,$C$13:$C$72,$C70,$D$13:$D$72,$D70,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M70,$M70+SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I70/SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T70" s="75">
         <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",$J70-$K70-$S70))</f>
@@ -15693,13 +15845,13 @@
     <row r="71" ht="14.25" customHeight="1">
       <c r="B71" s="63"/>
       <c r="C71" s="73" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D71" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E71" s="73" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="F71" s="73" t="s">
         <v>114</v>
@@ -15741,7 +15893,7 @@
         <v>115</v>
       </c>
       <c r="S71" s="74">
-        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M71,$M71+SUMIFS($M$13:$M$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"Fermer")*$I71/SUMIFS($I$13:$I$72,$C$13:$C$72,$C71,$D$13:$D$72,$D71,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M71,$M71+SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I71/SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T71" s="75">
         <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",$J71-$K71-$S71))</f>
@@ -15756,13 +15908,13 @@
     <row r="72" ht="14.25" customHeight="1">
       <c r="B72" s="63"/>
       <c r="C72" s="73" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="D72" s="73" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E72" s="73" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="F72" s="73" t="s">
         <v>117</v>
@@ -15804,7 +15956,7 @@
         <v>115</v>
       </c>
       <c r="S72" s="74">
-        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",IF(SUMIFS($I$13:$I$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"&lt;&gt;Fermer")=0,$M72,$M72+SUMIFS($M$13:$M$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"Fermer")*$I72/SUMIFS($I$13:$I$72,$C$13:$C$72,$C72,$D$13:$D$72,$D72,$R$13:$R$72,"&lt;&gt;Fermer"))))</f>
+        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M72,$M72+SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I72/SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
       </c>
       <c r="T72" s="75">
         <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",$J72-$K72-$S72))</f>
@@ -15818,1331 +15970,269 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="B73" s="63"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="43"/>
-      <c r="H73" s="43"/>
-      <c r="I73" s="43"/>
-      <c r="J73" s="43"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="43"/>
-      <c r="M73" s="43"/>
-      <c r="N73" s="43"/>
-      <c r="O73" s="43"/>
-      <c r="P73" s="43"/>
-      <c r="Q73" s="43"/>
-      <c r="R73" s="43"/>
+      <c r="C73" s="64"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
+      <c r="F73" s="56"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="56"/>
+      <c r="I73" s="57"/>
+      <c r="J73" s="58"/>
+      <c r="K73" s="58"/>
+      <c r="L73" s="59"/>
+      <c r="M73" s="56"/>
+      <c r="N73" s="58"/>
+      <c r="O73" s="58"/>
+      <c r="P73" s="56"/>
+      <c r="Q73" s="56"/>
+      <c r="R73" s="56"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="B74" s="63"/>
-      <c r="C74" s="44"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="10"/>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
-      <c r="Q74" s="10"/>
-      <c r="R74" s="10"/>
+      <c r="C74" s="64"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="65"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="57"/>
+      <c r="J74" s="58"/>
+      <c r="K74" s="58"/>
+      <c r="L74" s="59"/>
+      <c r="M74" s="56"/>
+      <c r="N74" s="58"/>
+      <c r="O74" s="58"/>
+      <c r="P74" s="56"/>
+      <c r="Q74" s="56"/>
+      <c r="R74" s="56"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="B75" s="63"/>
-      <c r="C75" s="44"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
-      <c r="N75" s="10"/>
-      <c r="O75" s="10"/>
-      <c r="P75" s="10"/>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
+      <c r="C75" s="64"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="65"/>
+      <c r="F75" s="56"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="58"/>
+      <c r="K75" s="58"/>
+      <c r="L75" s="59"/>
+      <c r="M75" s="56"/>
+      <c r="N75" s="58"/>
+      <c r="O75" s="58"/>
+      <c r="P75" s="56"/>
+      <c r="Q75" s="56"/>
+      <c r="R75" s="56"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="B76" s="63"/>
-      <c r="C76" s="44"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
-      <c r="N76" s="10"/>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-      <c r="Q76" s="10"/>
-      <c r="R76" s="10"/>
+      <c r="C76" s="64"/>
+      <c r="D76" s="65"/>
+      <c r="E76" s="65"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="57"/>
+      <c r="J76" s="58"/>
+      <c r="K76" s="58"/>
+      <c r="L76" s="59"/>
+      <c r="M76" s="56"/>
+      <c r="N76" s="58"/>
+      <c r="O76" s="58"/>
+      <c r="P76" s="56"/>
+      <c r="Q76" s="56"/>
+      <c r="R76" s="56"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="B77" s="63"/>
-      <c r="C77" s="44"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
-      <c r="N77" s="10"/>
-      <c r="O77" s="10"/>
-      <c r="P77" s="10"/>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
+      <c r="C77" s="64"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="65"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="57"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="57"/>
+      <c r="J77" s="58"/>
+      <c r="K77" s="58"/>
+      <c r="L77" s="59"/>
+      <c r="M77" s="56"/>
+      <c r="N77" s="58"/>
+      <c r="O77" s="58"/>
+      <c r="P77" s="56"/>
+      <c r="Q77" s="56"/>
+      <c r="R77" s="56"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="B78" s="63"/>
-      <c r="C78" s="44"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
-      <c r="N78" s="10"/>
-      <c r="O78" s="10"/>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="10"/>
-      <c r="R78" s="10"/>
+      <c r="C78" s="64"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="56"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="56"/>
+      <c r="I78" s="57"/>
+      <c r="J78" s="58"/>
+      <c r="K78" s="58"/>
+      <c r="L78" s="59"/>
+      <c r="M78" s="56"/>
+      <c r="N78" s="58"/>
+      <c r="O78" s="58"/>
+      <c r="P78" s="56"/>
+      <c r="Q78" s="56"/>
+      <c r="R78" s="56"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="B79" s="63"/>
-      <c r="C79" s="44"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
+      <c r="C79" s="64"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="65"/>
+      <c r="F79" s="56"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="56"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="58"/>
+      <c r="K79" s="58"/>
+      <c r="L79" s="59"/>
+      <c r="M79" s="56"/>
+      <c r="N79" s="58"/>
+      <c r="O79" s="58"/>
+      <c r="P79" s="56"/>
+      <c r="Q79" s="56"/>
+      <c r="R79" s="56"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="B80" s="63"/>
-      <c r="C80" s="44"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="10"/>
-      <c r="N80" s="10"/>
-      <c r="O80" s="10"/>
-      <c r="P80" s="10"/>
-      <c r="Q80" s="10"/>
-      <c r="R80" s="10"/>
+      <c r="C80" s="64"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="57"/>
+      <c r="J80" s="58"/>
+      <c r="K80" s="58"/>
+      <c r="L80" s="59"/>
+      <c r="M80" s="56"/>
+      <c r="N80" s="58"/>
+      <c r="O80" s="58"/>
+      <c r="P80" s="56"/>
+      <c r="Q80" s="56"/>
+      <c r="R80" s="56"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="B81" s="63"/>
-      <c r="C81" s="44"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
-      <c r="N81" s="10"/>
-      <c r="O81" s="10"/>
-      <c r="P81" s="10"/>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
+      <c r="C81" s="64"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="56"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="57"/>
+      <c r="J81" s="58"/>
+      <c r="K81" s="58"/>
+      <c r="L81" s="59"/>
+      <c r="M81" s="56"/>
+      <c r="N81" s="58"/>
+      <c r="O81" s="58"/>
+      <c r="P81" s="56"/>
+      <c r="Q81" s="56"/>
+      <c r="R81" s="56"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="B82" s="63"/>
-      <c r="C82" s="44"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
-      <c r="N82" s="10"/>
-      <c r="O82" s="10"/>
-      <c r="P82" s="10"/>
-      <c r="Q82" s="10"/>
-      <c r="R82" s="10"/>
+      <c r="C82" s="64"/>
+      <c r="D82" s="65"/>
+      <c r="E82" s="65"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="57"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="57"/>
+      <c r="J82" s="58"/>
+      <c r="K82" s="58"/>
+      <c r="L82" s="59"/>
+      <c r="M82" s="56"/>
+      <c r="N82" s="58"/>
+      <c r="O82" s="58"/>
+      <c r="P82" s="56"/>
+      <c r="Q82" s="56"/>
+      <c r="R82" s="56"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="B83" s="63"/>
-      <c r="C83" s="44"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
-      <c r="N83" s="10"/>
-      <c r="O83" s="10"/>
-      <c r="P83" s="10"/>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
+      <c r="C83" s="64"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="56"/>
+      <c r="G83" s="57"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="57"/>
+      <c r="J83" s="58"/>
+      <c r="K83" s="58"/>
+      <c r="L83" s="59"/>
+      <c r="M83" s="56"/>
+      <c r="N83" s="58"/>
+      <c r="O83" s="58"/>
+      <c r="P83" s="56"/>
+      <c r="Q83" s="56"/>
+      <c r="R83" s="56"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="B84" s="63"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="10"/>
-      <c r="N84" s="10"/>
-      <c r="O84" s="10"/>
-      <c r="P84" s="10"/>
-      <c r="Q84" s="10"/>
-      <c r="R84" s="10"/>
+      <c r="C84" s="64"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="65"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="57"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="57"/>
+      <c r="J84" s="58"/>
+      <c r="K84" s="58"/>
+      <c r="L84" s="59"/>
+      <c r="M84" s="56"/>
+      <c r="N84" s="58"/>
+      <c r="O84" s="58"/>
+      <c r="P84" s="56"/>
+      <c r="Q84" s="56"/>
+      <c r="R84" s="56"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="B85" s="63"/>
-      <c r="C85" s="44"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
-      <c r="N85" s="10"/>
-      <c r="O85" s="10"/>
-      <c r="P85" s="10"/>
-      <c r="Q85" s="10"/>
-      <c r="R85" s="10"/>
+      <c r="C85" s="64"/>
+      <c r="D85" s="65"/>
+      <c r="E85" s="65"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="57"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="57"/>
+      <c r="J85" s="58"/>
+      <c r="K85" s="58"/>
+      <c r="L85" s="59"/>
+      <c r="M85" s="56"/>
+      <c r="N85" s="58"/>
+      <c r="O85" s="58"/>
+      <c r="P85" s="56"/>
+      <c r="Q85" s="56"/>
+      <c r="R85" s="56"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="B86" s="63"/>
-      <c r="C86" s="44"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
-      <c r="N86" s="10"/>
-      <c r="O86" s="10"/>
-      <c r="P86" s="10"/>
-      <c r="Q86" s="10"/>
-      <c r="R86" s="10"/>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
-      <c r="C87" s="44"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
-      <c r="N87" s="10"/>
-      <c r="O87" s="10"/>
-      <c r="P87" s="10"/>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="C88" s="44"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
-      <c r="N88" s="10"/>
-      <c r="O88" s="10"/>
-      <c r="P88" s="10"/>
-      <c r="Q88" s="10"/>
-      <c r="R88" s="10"/>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
-      <c r="C89" s="44"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="10"/>
-      <c r="N89" s="10"/>
-      <c r="O89" s="10"/>
-      <c r="P89" s="10"/>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
-      <c r="C90" s="44"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="10"/>
-      <c r="N90" s="10"/>
-      <c r="O90" s="10"/>
-      <c r="P90" s="10"/>
-      <c r="Q90" s="10"/>
-      <c r="R90" s="10"/>
-    </row>
-    <row r="91" ht="14.25" customHeight="1">
-      <c r="C91" s="44"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
-      <c r="N91" s="10"/>
-      <c r="O91" s="10"/>
-      <c r="P91" s="10"/>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="C92" s="44"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
-      <c r="N92" s="10"/>
-      <c r="O92" s="10"/>
-      <c r="P92" s="10"/>
-      <c r="Q92" s="10"/>
-      <c r="R92" s="10"/>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
-      <c r="C93" s="45"/>
-      <c r="D93" s="46"/>
-      <c r="E93" s="46"/>
-      <c r="F93" s="46"/>
-      <c r="G93" s="46"/>
-      <c r="H93" s="46"/>
-      <c r="I93" s="46"/>
-      <c r="J93" s="46"/>
-      <c r="K93" s="46"/>
-      <c r="L93" s="46"/>
-      <c r="M93" s="46"/>
-      <c r="N93" s="46"/>
-      <c r="O93" s="46"/>
-      <c r="P93" s="46"/>
-      <c r="Q93" s="46"/>
-      <c r="R93" s="46"/>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
-      <c r="N94" s="10"/>
-      <c r="O94" s="10"/>
-      <c r="P94" s="10"/>
-      <c r="Q94" s="10"/>
-      <c r="R94" s="10"/>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
-      <c r="N95" s="10"/>
-      <c r="O95" s="10"/>
-      <c r="P95" s="10"/>
-      <c r="Q95" s="10"/>
-      <c r="R95" s="10"/>
-    </row>
-    <row r="96" ht="14.25" customHeight="1">
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
-      <c r="N96" s="10"/>
-      <c r="O96" s="10"/>
-      <c r="P96" s="10"/>
-      <c r="Q96" s="10"/>
-      <c r="R96" s="10"/>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
-      <c r="C97" s="53"/>
-      <c r="D97" s="54"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="56"/>
-      <c r="I97" s="57"/>
-      <c r="J97" s="58"/>
-      <c r="K97" s="58"/>
-      <c r="L97" s="59"/>
-      <c r="M97" s="56"/>
-      <c r="N97" s="58"/>
-      <c r="O97" s="58"/>
-      <c r="P97" s="56"/>
-      <c r="Q97" s="56"/>
-      <c r="R97" s="56"/>
-    </row>
-    <row r="98" ht="14.25" customHeight="1">
-      <c r="C98" s="53"/>
-      <c r="D98" s="54"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="57"/>
-      <c r="H98" s="56"/>
-      <c r="I98" s="57"/>
-      <c r="J98" s="58"/>
-      <c r="K98" s="58"/>
-      <c r="L98" s="59"/>
-      <c r="M98" s="56"/>
-      <c r="N98" s="58"/>
-      <c r="O98" s="58"/>
-      <c r="P98" s="56"/>
-      <c r="Q98" s="56"/>
-      <c r="R98" s="56"/>
-    </row>
-    <row r="99" ht="14.25" customHeight="1">
-      <c r="C99" s="53"/>
-      <c r="D99" s="54"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="56"/>
-      <c r="G99" s="57"/>
-      <c r="H99" s="56"/>
-      <c r="I99" s="57"/>
-      <c r="J99" s="58"/>
-      <c r="K99" s="58"/>
-      <c r="L99" s="59"/>
-      <c r="M99" s="56"/>
-      <c r="N99" s="58"/>
-      <c r="O99" s="58"/>
-      <c r="P99" s="56"/>
-      <c r="Q99" s="56"/>
-      <c r="R99" s="56"/>
-    </row>
-    <row r="100" ht="14.25" customHeight="1">
-      <c r="C100" s="53"/>
-      <c r="D100" s="54"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="56"/>
-      <c r="G100" s="57"/>
-      <c r="H100" s="56"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="58"/>
-      <c r="K100" s="58"/>
-      <c r="L100" s="59"/>
-      <c r="M100" s="56"/>
-      <c r="N100" s="58"/>
-      <c r="O100" s="58"/>
-      <c r="P100" s="56"/>
-      <c r="Q100" s="56"/>
-      <c r="R100" s="56"/>
-    </row>
-    <row r="101" ht="14.25" customHeight="1">
-      <c r="C101" s="53"/>
-      <c r="D101" s="79"/>
-      <c r="E101" s="80"/>
-      <c r="F101" s="56"/>
-      <c r="G101" s="57"/>
-      <c r="H101" s="56"/>
-      <c r="I101" s="57"/>
-      <c r="J101" s="58"/>
-      <c r="K101" s="58"/>
-      <c r="L101" s="59"/>
-      <c r="M101" s="56"/>
-      <c r="N101" s="58"/>
-      <c r="O101" s="58"/>
-      <c r="P101" s="56"/>
-      <c r="Q101" s="56"/>
-      <c r="R101" s="56"/>
-    </row>
-    <row r="102" ht="14.25" customHeight="1">
-      <c r="C102" s="53"/>
-      <c r="D102" s="79"/>
-      <c r="E102" s="80"/>
-      <c r="F102" s="56"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="56"/>
-      <c r="I102" s="57"/>
-      <c r="J102" s="58"/>
-      <c r="K102" s="58"/>
-      <c r="L102" s="59"/>
-      <c r="M102" s="56"/>
-      <c r="N102" s="58"/>
-      <c r="O102" s="58"/>
-      <c r="P102" s="56"/>
-      <c r="Q102" s="56"/>
-      <c r="R102" s="56"/>
-    </row>
-    <row r="103" ht="14.25" customHeight="1">
-      <c r="C103" s="53"/>
-      <c r="D103" s="79"/>
-      <c r="E103" s="80"/>
-      <c r="F103" s="56"/>
-      <c r="G103" s="57"/>
-      <c r="H103" s="56"/>
-      <c r="I103" s="57"/>
-      <c r="J103" s="58"/>
-      <c r="K103" s="58"/>
-      <c r="L103" s="59"/>
-      <c r="M103" s="56"/>
-      <c r="N103" s="58"/>
-      <c r="O103" s="58"/>
-      <c r="P103" s="56"/>
-      <c r="Q103" s="56"/>
-      <c r="R103" s="56"/>
-    </row>
-    <row r="104" ht="14.25" customHeight="1">
-      <c r="C104" s="53"/>
-      <c r="D104" s="79"/>
-      <c r="E104" s="80"/>
-      <c r="F104" s="56"/>
-      <c r="G104" s="57"/>
-      <c r="H104" s="56"/>
-      <c r="I104" s="57"/>
-      <c r="J104" s="58"/>
-      <c r="K104" s="58"/>
-      <c r="L104" s="59"/>
-      <c r="M104" s="56"/>
-      <c r="N104" s="58"/>
-      <c r="O104" s="58"/>
-      <c r="P104" s="56"/>
-      <c r="Q104" s="56"/>
-      <c r="R104" s="56"/>
-    </row>
-    <row r="105" ht="14.25" customHeight="1">
-      <c r="C105" s="53"/>
-      <c r="D105" s="79"/>
-      <c r="E105" s="80"/>
-      <c r="F105" s="56"/>
-      <c r="G105" s="57"/>
-      <c r="H105" s="56"/>
-      <c r="I105" s="57"/>
-      <c r="J105" s="58"/>
-      <c r="K105" s="58"/>
-      <c r="L105" s="59"/>
-      <c r="M105" s="56"/>
-      <c r="N105" s="58"/>
-      <c r="O105" s="58"/>
-      <c r="P105" s="56"/>
-      <c r="Q105" s="56"/>
-      <c r="R105" s="56"/>
-    </row>
-    <row r="106" ht="14.25" customHeight="1">
-      <c r="C106" s="53"/>
-      <c r="D106" s="79"/>
-      <c r="E106" s="80"/>
-      <c r="F106" s="56"/>
-      <c r="G106" s="57"/>
-      <c r="H106" s="56"/>
-      <c r="I106" s="57"/>
-      <c r="J106" s="58"/>
-      <c r="K106" s="58"/>
-      <c r="L106" s="59"/>
-      <c r="M106" s="56"/>
-      <c r="N106" s="58"/>
-      <c r="O106" s="58"/>
-      <c r="P106" s="56"/>
-      <c r="Q106" s="56"/>
-      <c r="R106" s="56"/>
-    </row>
-    <row r="107" ht="14.25" customHeight="1">
-      <c r="C107" s="53"/>
-      <c r="D107" s="79"/>
-      <c r="E107" s="80"/>
-      <c r="F107" s="56"/>
-      <c r="G107" s="57"/>
-      <c r="H107" s="56"/>
-      <c r="I107" s="57"/>
-      <c r="J107" s="58"/>
-      <c r="K107" s="58"/>
-      <c r="L107" s="59"/>
-      <c r="M107" s="56"/>
-      <c r="N107" s="58"/>
-      <c r="O107" s="58"/>
-      <c r="P107" s="56"/>
-      <c r="Q107" s="56"/>
-      <c r="R107" s="56"/>
-    </row>
-    <row r="108" ht="14.25" customHeight="1">
-      <c r="C108" s="53"/>
-      <c r="D108" s="79"/>
-      <c r="E108" s="80"/>
-      <c r="F108" s="56"/>
-      <c r="G108" s="57"/>
-      <c r="H108" s="56"/>
-      <c r="I108" s="57"/>
-      <c r="J108" s="58"/>
-      <c r="K108" s="58"/>
-      <c r="L108" s="59"/>
-      <c r="M108" s="56"/>
-      <c r="N108" s="58"/>
-      <c r="O108" s="58"/>
-      <c r="P108" s="56"/>
-      <c r="Q108" s="56"/>
-      <c r="R108" s="56"/>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
-      <c r="C109" s="53"/>
-      <c r="D109" s="79"/>
-      <c r="E109" s="80"/>
-      <c r="F109" s="56"/>
-      <c r="G109" s="57"/>
-      <c r="H109" s="56"/>
-      <c r="I109" s="57"/>
-      <c r="J109" s="58"/>
-      <c r="K109" s="58"/>
-      <c r="L109" s="59"/>
-      <c r="M109" s="56"/>
-      <c r="N109" s="58"/>
-      <c r="O109" s="58"/>
-      <c r="P109" s="56"/>
-      <c r="Q109" s="56"/>
-      <c r="R109" s="56"/>
-    </row>
-    <row r="110" ht="14.25" customHeight="1">
-      <c r="C110" s="53"/>
-      <c r="D110" s="79"/>
-      <c r="E110" s="80"/>
-      <c r="F110" s="56"/>
-      <c r="G110" s="57"/>
-      <c r="H110" s="56"/>
-      <c r="I110" s="57"/>
-      <c r="J110" s="58"/>
-      <c r="K110" s="58"/>
-      <c r="L110" s="59"/>
-      <c r="M110" s="56"/>
-      <c r="N110" s="58"/>
-      <c r="O110" s="58"/>
-      <c r="P110" s="56"/>
-      <c r="Q110" s="56"/>
-      <c r="R110" s="56"/>
-    </row>
-    <row r="111" ht="14.25" customHeight="1">
-      <c r="C111" s="53"/>
-      <c r="D111" s="79"/>
-      <c r="E111" s="80"/>
-      <c r="F111" s="56"/>
-      <c r="G111" s="57"/>
-      <c r="H111" s="56"/>
-      <c r="I111" s="57"/>
-      <c r="J111" s="58"/>
-      <c r="K111" s="58"/>
-      <c r="L111" s="59"/>
-      <c r="M111" s="56"/>
-      <c r="N111" s="58"/>
-      <c r="O111" s="58"/>
-      <c r="P111" s="56"/>
-      <c r="Q111" s="56"/>
-      <c r="R111" s="56"/>
-    </row>
-    <row r="112" ht="14.25" customHeight="1">
-      <c r="C112" s="53"/>
-      <c r="D112" s="79"/>
-      <c r="E112" s="80"/>
-      <c r="F112" s="56"/>
-      <c r="G112" s="57"/>
-      <c r="H112" s="56"/>
-      <c r="I112" s="57"/>
-      <c r="J112" s="58"/>
-      <c r="K112" s="58"/>
-      <c r="L112" s="59"/>
-      <c r="M112" s="56"/>
-      <c r="N112" s="58"/>
-      <c r="O112" s="58"/>
-      <c r="P112" s="56"/>
-      <c r="Q112" s="56"/>
-      <c r="R112" s="56"/>
-    </row>
-    <row r="113" ht="14.25" customHeight="1">
-      <c r="C113" s="53"/>
-      <c r="D113" s="79"/>
-      <c r="E113" s="80"/>
-      <c r="F113" s="56"/>
-      <c r="G113" s="57"/>
-      <c r="H113" s="56"/>
-      <c r="I113" s="57"/>
-      <c r="J113" s="58"/>
-      <c r="K113" s="58"/>
-      <c r="L113" s="59"/>
-      <c r="M113" s="56"/>
-      <c r="N113" s="58"/>
-      <c r="O113" s="58"/>
-      <c r="P113" s="56"/>
-      <c r="Q113" s="56"/>
-      <c r="R113" s="56"/>
-    </row>
-    <row r="114" ht="14.25" customHeight="1">
-      <c r="C114" s="53"/>
-      <c r="D114" s="79"/>
-      <c r="E114" s="80"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="57"/>
-      <c r="H114" s="56"/>
-      <c r="I114" s="57"/>
-      <c r="J114" s="58"/>
-      <c r="K114" s="58"/>
-      <c r="L114" s="59"/>
-      <c r="M114" s="56"/>
-      <c r="N114" s="58"/>
-      <c r="O114" s="58"/>
-      <c r="P114" s="56"/>
-      <c r="Q114" s="56"/>
-      <c r="R114" s="56"/>
-    </row>
-    <row r="115" ht="14.25" customHeight="1">
-      <c r="C115" s="53"/>
-      <c r="D115" s="79"/>
-      <c r="E115" s="80"/>
-      <c r="F115" s="56"/>
-      <c r="G115" s="57"/>
-      <c r="H115" s="56"/>
-      <c r="I115" s="57"/>
-      <c r="J115" s="58"/>
-      <c r="K115" s="58"/>
-      <c r="L115" s="59"/>
-      <c r="M115" s="56"/>
-      <c r="N115" s="58"/>
-      <c r="O115" s="58"/>
-      <c r="P115" s="56"/>
-      <c r="Q115" s="56"/>
-      <c r="R115" s="56"/>
-    </row>
-    <row r="116" ht="14.25" customHeight="1">
-      <c r="C116" s="64"/>
-      <c r="D116" s="65"/>
-      <c r="E116" s="65"/>
-      <c r="F116" s="56"/>
-      <c r="G116" s="57"/>
-      <c r="H116" s="56"/>
-      <c r="I116" s="57"/>
-      <c r="J116" s="58"/>
-      <c r="K116" s="58"/>
-      <c r="L116" s="59"/>
-      <c r="M116" s="56"/>
-      <c r="N116" s="58"/>
-      <c r="O116" s="58"/>
-      <c r="P116" s="56"/>
-      <c r="Q116" s="56"/>
-      <c r="R116" s="56"/>
-    </row>
-    <row r="117" ht="14.25" customHeight="1">
-      <c r="C117" s="64"/>
-      <c r="D117" s="65"/>
-      <c r="E117" s="65"/>
-      <c r="F117" s="56"/>
-      <c r="G117" s="57"/>
-      <c r="H117" s="56"/>
-      <c r="I117" s="57"/>
-      <c r="J117" s="58"/>
-      <c r="K117" s="58"/>
-      <c r="L117" s="59"/>
-      <c r="M117" s="56"/>
-      <c r="N117" s="58"/>
-      <c r="O117" s="58"/>
-      <c r="P117" s="56"/>
-      <c r="Q117" s="56"/>
-      <c r="R117" s="56"/>
-    </row>
-    <row r="118" ht="14.25" customHeight="1">
-      <c r="C118" s="64"/>
-      <c r="D118" s="65"/>
-      <c r="E118" s="65"/>
-      <c r="F118" s="56"/>
-      <c r="G118" s="57"/>
-      <c r="H118" s="56"/>
-      <c r="I118" s="57"/>
-      <c r="J118" s="58"/>
-      <c r="K118" s="58"/>
-      <c r="L118" s="59"/>
-      <c r="M118" s="56"/>
-      <c r="N118" s="58"/>
-      <c r="O118" s="58"/>
-      <c r="P118" s="56"/>
-      <c r="Q118" s="56"/>
-      <c r="R118" s="56"/>
-    </row>
-    <row r="119" ht="14.25" customHeight="1">
-      <c r="C119" s="64"/>
-      <c r="D119" s="65"/>
-      <c r="E119" s="65"/>
-      <c r="F119" s="56"/>
-      <c r="G119" s="57"/>
-      <c r="H119" s="56"/>
-      <c r="I119" s="57"/>
-      <c r="J119" s="58"/>
-      <c r="K119" s="58"/>
-      <c r="L119" s="59"/>
-      <c r="M119" s="56"/>
-      <c r="N119" s="58"/>
-      <c r="O119" s="58"/>
-      <c r="P119" s="56"/>
-      <c r="Q119" s="56"/>
-      <c r="R119" s="56"/>
-    </row>
-    <row r="120" ht="14.25" customHeight="1">
-      <c r="C120" s="64"/>
-      <c r="D120" s="65"/>
-      <c r="E120" s="65"/>
-      <c r="F120" s="56"/>
-      <c r="G120" s="57"/>
-      <c r="H120" s="56"/>
-      <c r="I120" s="57"/>
-      <c r="J120" s="58"/>
-      <c r="K120" s="58"/>
-      <c r="L120" s="59"/>
-      <c r="M120" s="56"/>
-      <c r="N120" s="58"/>
-      <c r="O120" s="58"/>
-      <c r="P120" s="56"/>
-      <c r="Q120" s="56"/>
-      <c r="R120" s="56"/>
-    </row>
-    <row r="121" ht="14.25" customHeight="1">
-      <c r="C121" s="64"/>
-      <c r="D121" s="65"/>
-      <c r="E121" s="65"/>
-      <c r="F121" s="56"/>
-      <c r="G121" s="57"/>
-      <c r="H121" s="56"/>
-      <c r="I121" s="57"/>
-      <c r="J121" s="58"/>
-      <c r="K121" s="58"/>
-      <c r="L121" s="59"/>
-      <c r="M121" s="56"/>
-      <c r="N121" s="58"/>
-      <c r="O121" s="58"/>
-      <c r="P121" s="56"/>
-      <c r="Q121" s="56"/>
-      <c r="R121" s="56"/>
-    </row>
-    <row r="122" ht="14.25" customHeight="1">
-      <c r="C122" s="64"/>
-      <c r="D122" s="65"/>
-      <c r="E122" s="65"/>
-      <c r="F122" s="56"/>
-      <c r="G122" s="57"/>
-      <c r="H122" s="56"/>
-      <c r="I122" s="57"/>
-      <c r="J122" s="58"/>
-      <c r="K122" s="58"/>
-      <c r="L122" s="59"/>
-      <c r="M122" s="56"/>
-      <c r="N122" s="58"/>
-      <c r="O122" s="58"/>
-      <c r="P122" s="56"/>
-      <c r="Q122" s="56"/>
-      <c r="R122" s="56"/>
-    </row>
-    <row r="123" ht="14.25" customHeight="1">
-      <c r="C123" s="64"/>
-      <c r="D123" s="65"/>
-      <c r="E123" s="65"/>
-      <c r="F123" s="56"/>
-      <c r="G123" s="57"/>
-      <c r="H123" s="56"/>
-      <c r="I123" s="57"/>
-      <c r="J123" s="58"/>
-      <c r="K123" s="58"/>
-      <c r="L123" s="59"/>
-      <c r="M123" s="56"/>
-      <c r="N123" s="58"/>
-      <c r="O123" s="58"/>
-      <c r="P123" s="56"/>
-      <c r="Q123" s="56"/>
-      <c r="R123" s="56"/>
-    </row>
-    <row r="124" ht="14.25" customHeight="1">
-      <c r="C124" s="64"/>
-      <c r="D124" s="65"/>
-      <c r="E124" s="65"/>
-      <c r="F124" s="56"/>
-      <c r="G124" s="57"/>
-      <c r="H124" s="56"/>
-      <c r="I124" s="57"/>
-      <c r="J124" s="58"/>
-      <c r="K124" s="58"/>
-      <c r="L124" s="59"/>
-      <c r="M124" s="56"/>
-      <c r="N124" s="58"/>
-      <c r="O124" s="58"/>
-      <c r="P124" s="56"/>
-      <c r="Q124" s="56"/>
-      <c r="R124" s="56"/>
-    </row>
-    <row r="125" ht="14.25" customHeight="1">
-      <c r="C125" s="64"/>
-      <c r="D125" s="65"/>
-      <c r="E125" s="65"/>
-      <c r="F125" s="56"/>
-      <c r="G125" s="57"/>
-      <c r="H125" s="56"/>
-      <c r="I125" s="57"/>
-      <c r="J125" s="58"/>
-      <c r="K125" s="58"/>
-      <c r="L125" s="59"/>
-      <c r="M125" s="56"/>
-      <c r="N125" s="58"/>
-      <c r="O125" s="58"/>
-      <c r="P125" s="56"/>
-      <c r="Q125" s="56"/>
-      <c r="R125" s="56"/>
-    </row>
-    <row r="126" ht="14.25" customHeight="1">
-      <c r="C126" s="64"/>
-      <c r="D126" s="65"/>
-      <c r="E126" s="65"/>
-      <c r="F126" s="56"/>
-      <c r="G126" s="57"/>
-      <c r="H126" s="56"/>
-      <c r="I126" s="57"/>
-      <c r="J126" s="58"/>
-      <c r="K126" s="58"/>
-      <c r="L126" s="59"/>
-      <c r="M126" s="56"/>
-      <c r="N126" s="58"/>
-      <c r="O126" s="58"/>
-      <c r="P126" s="56"/>
-      <c r="Q126" s="56"/>
-      <c r="R126" s="56"/>
-    </row>
-    <row r="127" ht="14.25" customHeight="1">
-      <c r="C127" s="64"/>
-      <c r="D127" s="65"/>
-      <c r="E127" s="65"/>
-      <c r="F127" s="56"/>
-      <c r="G127" s="57"/>
-      <c r="H127" s="56"/>
-      <c r="I127" s="57"/>
-      <c r="J127" s="58"/>
-      <c r="K127" s="58"/>
-      <c r="L127" s="59"/>
-      <c r="M127" s="56"/>
-      <c r="N127" s="58"/>
-      <c r="O127" s="58"/>
-      <c r="P127" s="56"/>
-      <c r="Q127" s="56"/>
-      <c r="R127" s="56"/>
-    </row>
-    <row r="128" ht="14.25" customHeight="1">
-      <c r="C128" s="64"/>
-      <c r="D128" s="65"/>
-      <c r="E128" s="65"/>
-      <c r="F128" s="56"/>
-      <c r="G128" s="57"/>
-      <c r="H128" s="56"/>
-      <c r="I128" s="57"/>
-      <c r="J128" s="58"/>
-      <c r="K128" s="58"/>
-      <c r="L128" s="59"/>
-      <c r="M128" s="56"/>
-      <c r="N128" s="58"/>
-      <c r="O128" s="58"/>
-      <c r="P128" s="56"/>
-      <c r="Q128" s="56"/>
-      <c r="R128" s="56"/>
-    </row>
-    <row r="129" ht="14.25" customHeight="1">
-      <c r="C129" s="64"/>
-      <c r="D129" s="65"/>
-      <c r="E129" s="65"/>
-      <c r="F129" s="56"/>
-      <c r="G129" s="57"/>
-      <c r="H129" s="56"/>
-      <c r="I129" s="57"/>
-      <c r="J129" s="58"/>
-      <c r="K129" s="58"/>
-      <c r="L129" s="59"/>
-      <c r="M129" s="56"/>
-      <c r="N129" s="58"/>
-      <c r="O129" s="58"/>
-      <c r="P129" s="56"/>
-      <c r="Q129" s="56"/>
-      <c r="R129" s="56"/>
-    </row>
-    <row r="130" ht="14.25" customHeight="1">
-      <c r="C130" s="64"/>
-      <c r="D130" s="65"/>
-      <c r="E130" s="65"/>
-      <c r="F130" s="56"/>
-      <c r="G130" s="57"/>
-      <c r="H130" s="56"/>
-      <c r="I130" s="57"/>
-      <c r="J130" s="58"/>
-      <c r="K130" s="58"/>
-      <c r="L130" s="59"/>
-      <c r="M130" s="56"/>
-      <c r="N130" s="58"/>
-      <c r="O130" s="58"/>
-      <c r="P130" s="56"/>
-      <c r="Q130" s="56"/>
-      <c r="R130" s="56"/>
-    </row>
-    <row r="131" ht="14.25" customHeight="1">
-      <c r="C131" s="64"/>
-      <c r="D131" s="65"/>
-      <c r="E131" s="65"/>
-      <c r="F131" s="56"/>
-      <c r="G131" s="57"/>
-      <c r="H131" s="56"/>
-      <c r="I131" s="57"/>
-      <c r="J131" s="58"/>
-      <c r="K131" s="58"/>
-      <c r="L131" s="59"/>
-      <c r="M131" s="56"/>
-      <c r="N131" s="58"/>
-      <c r="O131" s="58"/>
-      <c r="P131" s="56"/>
-      <c r="Q131" s="56"/>
-      <c r="R131" s="56"/>
-    </row>
-    <row r="132" ht="14.25" customHeight="1">
-      <c r="C132" s="64"/>
-      <c r="D132" s="65"/>
-      <c r="E132" s="65"/>
-      <c r="F132" s="56"/>
-      <c r="G132" s="57"/>
-      <c r="H132" s="56"/>
-      <c r="I132" s="57"/>
-      <c r="J132" s="58"/>
-      <c r="K132" s="58"/>
-      <c r="L132" s="59"/>
-      <c r="M132" s="56"/>
-      <c r="N132" s="58"/>
-      <c r="O132" s="58"/>
-      <c r="P132" s="56"/>
-      <c r="Q132" s="56"/>
-      <c r="R132" s="56"/>
-    </row>
-    <row r="133" ht="14.25" customHeight="1">
-      <c r="C133" s="64"/>
-      <c r="D133" s="65"/>
-      <c r="E133" s="65"/>
-      <c r="F133" s="56"/>
-      <c r="G133" s="57"/>
-      <c r="H133" s="56"/>
-      <c r="I133" s="57"/>
-      <c r="J133" s="58"/>
-      <c r="K133" s="58"/>
-      <c r="L133" s="59"/>
-      <c r="M133" s="56"/>
-      <c r="N133" s="58"/>
-      <c r="O133" s="58"/>
-      <c r="P133" s="56"/>
-      <c r="Q133" s="56"/>
-      <c r="R133" s="56"/>
-    </row>
-    <row r="134" ht="14.25" customHeight="1">
-      <c r="C134" s="64"/>
-      <c r="D134" s="65"/>
-      <c r="E134" s="65"/>
-      <c r="F134" s="56"/>
-      <c r="G134" s="57"/>
-      <c r="H134" s="56"/>
-      <c r="I134" s="57"/>
-      <c r="J134" s="58"/>
-      <c r="K134" s="58"/>
-      <c r="L134" s="59"/>
-      <c r="M134" s="56"/>
-      <c r="N134" s="58"/>
-      <c r="O134" s="58"/>
-      <c r="P134" s="56"/>
-      <c r="Q134" s="56"/>
-      <c r="R134" s="56"/>
-    </row>
-    <row r="135" ht="14.25" customHeight="1">
-      <c r="C135" s="64"/>
-      <c r="D135" s="65"/>
-      <c r="E135" s="65"/>
-      <c r="F135" s="56"/>
-      <c r="G135" s="57"/>
-      <c r="H135" s="56"/>
-      <c r="I135" s="57"/>
-      <c r="J135" s="58"/>
-      <c r="K135" s="58"/>
-      <c r="L135" s="59"/>
-      <c r="M135" s="56"/>
-      <c r="N135" s="58"/>
-      <c r="O135" s="58"/>
-      <c r="P135" s="56"/>
-      <c r="Q135" s="56"/>
-      <c r="R135" s="56"/>
-    </row>
-    <row r="136" ht="14.25" customHeight="1">
-      <c r="C136" s="64"/>
-      <c r="D136" s="65"/>
-      <c r="E136" s="65"/>
-      <c r="F136" s="56"/>
-      <c r="G136" s="57"/>
-      <c r="H136" s="56"/>
-      <c r="I136" s="57"/>
-      <c r="J136" s="58"/>
-      <c r="K136" s="58"/>
-      <c r="L136" s="59"/>
-      <c r="M136" s="56"/>
-      <c r="N136" s="58"/>
-      <c r="O136" s="58"/>
-      <c r="P136" s="56"/>
-      <c r="Q136" s="56"/>
-      <c r="R136" s="56"/>
-    </row>
-    <row r="137" ht="14.25" customHeight="1">
-      <c r="C137" s="64"/>
-      <c r="D137" s="65"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="56"/>
-      <c r="G137" s="57"/>
-      <c r="H137" s="56"/>
-      <c r="I137" s="57"/>
-      <c r="J137" s="58"/>
-      <c r="K137" s="58"/>
-      <c r="L137" s="59"/>
-      <c r="M137" s="56"/>
-      <c r="N137" s="58"/>
-      <c r="O137" s="58"/>
-      <c r="P137" s="56"/>
-      <c r="Q137" s="56"/>
-      <c r="R137" s="56"/>
-    </row>
-    <row r="138" ht="14.25" customHeight="1">
-      <c r="C138" s="64"/>
-      <c r="D138" s="65"/>
-      <c r="E138" s="65"/>
-      <c r="F138" s="56"/>
-      <c r="G138" s="57"/>
-      <c r="H138" s="56"/>
-      <c r="I138" s="57"/>
-      <c r="J138" s="58"/>
-      <c r="K138" s="58"/>
-      <c r="L138" s="59"/>
-      <c r="M138" s="56"/>
-      <c r="N138" s="58"/>
-      <c r="O138" s="58"/>
-      <c r="P138" s="56"/>
-      <c r="Q138" s="56"/>
-      <c r="R138" s="56"/>
-    </row>
-    <row r="139" ht="14.25" customHeight="1">
-      <c r="C139" s="64"/>
-      <c r="D139" s="65"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="56"/>
-      <c r="G139" s="57"/>
-      <c r="H139" s="56"/>
-      <c r="I139" s="57"/>
-      <c r="J139" s="58"/>
-      <c r="K139" s="58"/>
-      <c r="L139" s="59"/>
-      <c r="M139" s="56"/>
-      <c r="N139" s="58"/>
-      <c r="O139" s="58"/>
-      <c r="P139" s="56"/>
-      <c r="Q139" s="56"/>
-      <c r="R139" s="56"/>
-    </row>
-    <row r="140" ht="14.25" customHeight="1">
-      <c r="C140" s="64"/>
-      <c r="D140" s="65"/>
-      <c r="E140" s="65"/>
-      <c r="F140" s="56"/>
-      <c r="G140" s="57"/>
-      <c r="H140" s="56"/>
-      <c r="I140" s="57"/>
-      <c r="J140" s="58"/>
-      <c r="K140" s="58"/>
-      <c r="L140" s="59"/>
-      <c r="M140" s="56"/>
-      <c r="N140" s="58"/>
-      <c r="O140" s="58"/>
-      <c r="P140" s="56"/>
-      <c r="Q140" s="56"/>
-      <c r="R140" s="56"/>
-    </row>
-    <row r="141" ht="14.25" customHeight="1">
-      <c r="C141" s="64"/>
-      <c r="D141" s="65"/>
-      <c r="E141" s="65"/>
-      <c r="F141" s="56"/>
-      <c r="G141" s="57"/>
-      <c r="H141" s="56"/>
-      <c r="I141" s="57"/>
-      <c r="J141" s="58"/>
-      <c r="K141" s="58"/>
-      <c r="L141" s="59"/>
-      <c r="M141" s="56"/>
-      <c r="N141" s="58"/>
-      <c r="O141" s="58"/>
-      <c r="P141" s="56"/>
-      <c r="Q141" s="56"/>
-      <c r="R141" s="56"/>
-    </row>
-    <row r="142" ht="14.25" customHeight="1">
-      <c r="C142" s="64"/>
-      <c r="D142" s="65"/>
-      <c r="E142" s="65"/>
-      <c r="F142" s="56"/>
-      <c r="G142" s="57"/>
-      <c r="H142" s="56"/>
-      <c r="I142" s="57"/>
-      <c r="J142" s="58"/>
-      <c r="K142" s="58"/>
-      <c r="L142" s="59"/>
-      <c r="M142" s="56"/>
-      <c r="N142" s="58"/>
-      <c r="O142" s="58"/>
-      <c r="P142" s="56"/>
-      <c r="Q142" s="56"/>
-      <c r="R142" s="56"/>
-    </row>
-    <row r="143" ht="14.25" customHeight="1">
-      <c r="C143" s="64"/>
-      <c r="D143" s="65"/>
-      <c r="E143" s="65"/>
-      <c r="F143" s="56"/>
-      <c r="G143" s="57"/>
-      <c r="H143" s="56"/>
-      <c r="I143" s="57"/>
-      <c r="J143" s="58"/>
-      <c r="K143" s="58"/>
-      <c r="L143" s="59"/>
-      <c r="M143" s="56"/>
-      <c r="N143" s="58"/>
-      <c r="O143" s="58"/>
-      <c r="P143" s="56"/>
-      <c r="Q143" s="56"/>
-      <c r="R143" s="56"/>
-    </row>
-    <row r="144" ht="14.25" customHeight="1">
-      <c r="C144" s="64"/>
-      <c r="D144" s="65"/>
-      <c r="E144" s="65"/>
-      <c r="F144" s="56"/>
-      <c r="G144" s="57"/>
-      <c r="H144" s="56"/>
-      <c r="I144" s="57"/>
-      <c r="J144" s="58"/>
-      <c r="K144" s="58"/>
-      <c r="L144" s="59"/>
-      <c r="M144" s="56"/>
-      <c r="N144" s="58"/>
-      <c r="O144" s="58"/>
-      <c r="P144" s="56"/>
-      <c r="Q144" s="56"/>
-      <c r="R144" s="56"/>
-    </row>
-    <row r="145" ht="14.25" customHeight="1">
-      <c r="C145" s="64"/>
-      <c r="D145" s="65"/>
-      <c r="E145" s="65"/>
-      <c r="F145" s="56"/>
-      <c r="G145" s="57"/>
-      <c r="H145" s="56"/>
-      <c r="I145" s="57"/>
-      <c r="J145" s="58"/>
-      <c r="K145" s="58"/>
-      <c r="L145" s="59"/>
-      <c r="M145" s="56"/>
-      <c r="N145" s="58"/>
-      <c r="O145" s="58"/>
-      <c r="P145" s="56"/>
-      <c r="Q145" s="56"/>
-      <c r="R145" s="56"/>
+      <c r="C86" s="64"/>
+      <c r="D86" s="65"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="56"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="58"/>
+      <c r="K86" s="58"/>
+      <c r="L86" s="59"/>
+      <c r="M86" s="56"/>
+      <c r="N86" s="58"/>
+      <c r="O86" s="58"/>
+      <c r="P86" s="56"/>
+      <c r="Q86" s="56"/>
+      <c r="R86" s="56"/>
     </row>
   </sheetData>
   <sheetProtection sort="1" autoFilter="0"/>
@@ -17171,7 +16261,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FDFFA778-3BB8-BCFB-5D2E-57BF8B9188CC}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{ACFE5413-7818-E732-F7E9-209BE4300A8A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:CE82"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="9.00390625" customHeight="1"/>
   <cols>
@@ -17190,344 +16280,344 @@
   </cols>
   <sheetData>
     <row r="1" ht="8.25" customHeight="1">
-      <c r="A1" s="81"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="81"/>
-      <c r="AU1" s="81"/>
-      <c r="AV1" s="81"/>
-      <c r="AW1" s="81"/>
-      <c r="AX1" s="81"/>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="81"/>
-      <c r="BI1" s="81"/>
-      <c r="BJ1" s="81"/>
-      <c r="BK1" s="81"/>
-      <c r="BL1" s="81"/>
-      <c r="BM1" s="81"/>
-      <c r="BN1" s="81"/>
-      <c r="BO1" s="81"/>
-      <c r="BP1" s="81"/>
-      <c r="BQ1" s="81"/>
-      <c r="BR1" s="81"/>
-      <c r="BS1" s="81"/>
-      <c r="BT1" s="81"/>
-      <c r="BU1" s="81"/>
-      <c r="BV1" s="81"/>
-      <c r="BW1" s="81"/>
-      <c r="BX1" s="81"/>
-      <c r="BY1" s="81"/>
-      <c r="BZ1" s="81"/>
-      <c r="CA1" s="81"/>
-      <c r="CB1" s="81"/>
-      <c r="CC1" s="81"/>
-      <c r="CD1" s="81"/>
+      <c r="A1" s="79"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="79"/>
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
+      <c r="BA1" s="79"/>
+      <c r="BB1" s="79"/>
+      <c r="BC1" s="79"/>
+      <c r="BD1" s="79"/>
+      <c r="BE1" s="79"/>
+      <c r="BF1" s="79"/>
+      <c r="BG1" s="79"/>
+      <c r="BH1" s="79"/>
+      <c r="BI1" s="79"/>
+      <c r="BJ1" s="79"/>
+      <c r="BK1" s="79"/>
+      <c r="BL1" s="79"/>
+      <c r="BM1" s="79"/>
+      <c r="BN1" s="79"/>
+      <c r="BO1" s="79"/>
+      <c r="BP1" s="79"/>
+      <c r="BQ1" s="79"/>
+      <c r="BR1" s="79"/>
+      <c r="BS1" s="79"/>
+      <c r="BT1" s="79"/>
+      <c r="BU1" s="79"/>
+      <c r="BV1" s="79"/>
+      <c r="BW1" s="79"/>
+      <c r="BX1" s="79"/>
+      <c r="BY1" s="79"/>
+      <c r="BZ1" s="79"/>
+      <c r="CA1" s="79"/>
+      <c r="CB1" s="79"/>
+      <c r="CC1" s="79"/>
+      <c r="CD1" s="79"/>
     </row>
     <row r="2" ht="8.25" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
-      <c r="AB2" s="81"/>
-      <c r="AC2" s="81"/>
-      <c r="AD2" s="81"/>
-      <c r="AE2" s="81"/>
-      <c r="AF2" s="81"/>
-      <c r="AG2" s="81"/>
-      <c r="AH2" s="81"/>
-      <c r="AI2" s="81"/>
-      <c r="AJ2" s="81"/>
-      <c r="AK2" s="81"/>
-      <c r="AL2" s="81"/>
-      <c r="AM2" s="81"/>
-      <c r="AN2" s="81"/>
-      <c r="AO2" s="81"/>
-      <c r="AP2" s="81"/>
-      <c r="AQ2" s="81"/>
-      <c r="AR2" s="81"/>
-      <c r="AS2" s="81"/>
-      <c r="AT2" s="81"/>
-      <c r="AU2" s="81"/>
-      <c r="AV2" s="81"/>
-      <c r="AW2" s="81"/>
-      <c r="AX2" s="81"/>
-      <c r="AY2" s="81"/>
-      <c r="AZ2" s="81"/>
-      <c r="BA2" s="81"/>
-      <c r="BB2" s="81"/>
-      <c r="BC2" s="81"/>
-      <c r="BD2" s="81"/>
-      <c r="BE2" s="81"/>
-      <c r="BF2" s="81"/>
-      <c r="BG2" s="81"/>
-      <c r="BH2" s="81"/>
-      <c r="BI2" s="81"/>
-      <c r="BJ2" s="81"/>
-      <c r="BK2" s="81"/>
-      <c r="BL2" s="81"/>
-      <c r="BM2" s="81"/>
-      <c r="BN2" s="81"/>
-      <c r="BO2" s="81"/>
-      <c r="BP2" s="81"/>
-      <c r="BQ2" s="81"/>
-      <c r="BR2" s="81"/>
-      <c r="BS2" s="81"/>
-      <c r="BT2" s="81"/>
-      <c r="BU2" s="81"/>
-      <c r="BV2" s="81"/>
-      <c r="BW2" s="81"/>
-      <c r="BX2" s="81"/>
-      <c r="BY2" s="81"/>
-      <c r="BZ2" s="81"/>
-      <c r="CA2" s="81"/>
-      <c r="CB2" s="81"/>
-      <c r="CC2" s="81"/>
-      <c r="CD2" s="81"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="79"/>
+      <c r="AG2" s="79"/>
+      <c r="AH2" s="79"/>
+      <c r="AI2" s="79"/>
+      <c r="AJ2" s="79"/>
+      <c r="AK2" s="79"/>
+      <c r="AL2" s="79"/>
+      <c r="AM2" s="79"/>
+      <c r="AN2" s="79"/>
+      <c r="AO2" s="79"/>
+      <c r="AP2" s="79"/>
+      <c r="AQ2" s="79"/>
+      <c r="AR2" s="79"/>
+      <c r="AS2" s="79"/>
+      <c r="AT2" s="79"/>
+      <c r="AU2" s="79"/>
+      <c r="AV2" s="79"/>
+      <c r="AW2" s="79"/>
+      <c r="AX2" s="79"/>
+      <c r="AY2" s="79"/>
+      <c r="AZ2" s="79"/>
+      <c r="BA2" s="79"/>
+      <c r="BB2" s="79"/>
+      <c r="BC2" s="79"/>
+      <c r="BD2" s="79"/>
+      <c r="BE2" s="79"/>
+      <c r="BF2" s="79"/>
+      <c r="BG2" s="79"/>
+      <c r="BH2" s="79"/>
+      <c r="BI2" s="79"/>
+      <c r="BJ2" s="79"/>
+      <c r="BK2" s="79"/>
+      <c r="BL2" s="79"/>
+      <c r="BM2" s="79"/>
+      <c r="BN2" s="79"/>
+      <c r="BO2" s="79"/>
+      <c r="BP2" s="79"/>
+      <c r="BQ2" s="79"/>
+      <c r="BR2" s="79"/>
+      <c r="BS2" s="79"/>
+      <c r="BT2" s="79"/>
+      <c r="BU2" s="79"/>
+      <c r="BV2" s="79"/>
+      <c r="BW2" s="79"/>
+      <c r="BX2" s="79"/>
+      <c r="BY2" s="79"/>
+      <c r="BZ2" s="79"/>
+      <c r="CA2" s="79"/>
+      <c r="CB2" s="79"/>
+      <c r="CC2" s="79"/>
+      <c r="CD2" s="79"/>
     </row>
     <row r="3" ht="26.25" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="83"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="81"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="81"/>
-      <c r="AR3" s="81"/>
-      <c r="AS3" s="81"/>
-      <c r="AT3" s="81"/>
-      <c r="AU3" s="81"/>
-      <c r="AV3" s="81"/>
-      <c r="AW3" s="81"/>
-      <c r="AX3" s="81"/>
-      <c r="AY3" s="81"/>
-      <c r="AZ3" s="81"/>
-      <c r="BA3" s="81"/>
-      <c r="BB3" s="81"/>
-      <c r="BC3" s="81"/>
-      <c r="BD3" s="81"/>
-      <c r="BE3" s="81"/>
-      <c r="BF3" s="81"/>
-      <c r="BG3" s="81"/>
-      <c r="BH3" s="81"/>
-      <c r="BI3" s="81"/>
-      <c r="BJ3" s="81"/>
-      <c r="BK3" s="81"/>
-      <c r="BL3" s="81"/>
-      <c r="BM3" s="81"/>
-      <c r="BN3" s="81"/>
-      <c r="BO3" s="81"/>
-      <c r="BP3" s="81"/>
-      <c r="BQ3" s="81"/>
-      <c r="BR3" s="81"/>
-      <c r="BS3" s="81"/>
-      <c r="BT3" s="81"/>
-      <c r="BU3" s="81"/>
-      <c r="BV3" s="81"/>
-      <c r="BW3" s="81"/>
-      <c r="BX3" s="81"/>
-      <c r="BY3" s="81"/>
-      <c r="BZ3" s="81"/>
-      <c r="CA3" s="81"/>
-      <c r="CB3" s="81"/>
-      <c r="CC3" s="81"/>
-      <c r="CD3" s="81"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="84" customFormat="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="86"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="87"/>
-      <c r="U4" s="87"/>
-      <c r="V4" s="87"/>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="87"/>
-      <c r="AB4" s="87"/>
-      <c r="AC4" s="87"/>
-      <c r="AD4" s="87"/>
-      <c r="AE4" s="87"/>
-      <c r="AF4" s="87"/>
-      <c r="AG4" s="87"/>
-      <c r="AH4" s="87"/>
-      <c r="AI4" s="87"/>
-      <c r="AJ4" s="87"/>
-      <c r="AK4" s="87"/>
-      <c r="AL4" s="87"/>
-      <c r="AM4" s="87"/>
-      <c r="AN4" s="87"/>
-      <c r="AO4" s="87"/>
-      <c r="AP4" s="87"/>
-      <c r="AQ4" s="87"/>
-      <c r="AR4" s="87"/>
-      <c r="AS4" s="87"/>
-      <c r="AT4" s="87"/>
-      <c r="AU4" s="87"/>
-      <c r="AV4" s="87"/>
-      <c r="AW4" s="87"/>
-      <c r="AX4" s="87"/>
-      <c r="AY4" s="87"/>
-      <c r="AZ4" s="87"/>
-      <c r="BA4" s="87"/>
-      <c r="BB4" s="87"/>
-      <c r="BC4" s="87"/>
-      <c r="BD4" s="87"/>
-      <c r="BE4" s="87"/>
-      <c r="BF4" s="87"/>
-      <c r="BG4" s="87"/>
-      <c r="BH4" s="87"/>
-      <c r="BI4" s="87"/>
-      <c r="BJ4" s="87"/>
-      <c r="BK4" s="87"/>
-      <c r="BL4" s="87"/>
-      <c r="BM4" s="87"/>
-      <c r="BN4" s="87"/>
-      <c r="BO4" s="87"/>
-      <c r="BP4" s="87"/>
-      <c r="BQ4" s="87"/>
-      <c r="BR4" s="87"/>
-      <c r="BS4" s="87"/>
-      <c r="BT4" s="87"/>
-      <c r="BU4" s="87"/>
-      <c r="BV4" s="87"/>
-      <c r="BW4" s="87"/>
-      <c r="BX4" s="87"/>
-      <c r="BY4" s="87"/>
-      <c r="BZ4" s="87"/>
-      <c r="CA4" s="87"/>
-      <c r="CB4" s="87"/>
-      <c r="CC4" s="87"/>
-      <c r="CD4" s="87"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="81"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="79"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
+      <c r="AF3" s="79"/>
+      <c r="AG3" s="79"/>
+      <c r="AH3" s="79"/>
+      <c r="AI3" s="79"/>
+      <c r="AJ3" s="79"/>
+      <c r="AK3" s="79"/>
+      <c r="AL3" s="79"/>
+      <c r="AM3" s="79"/>
+      <c r="AN3" s="79"/>
+      <c r="AO3" s="79"/>
+      <c r="AP3" s="79"/>
+      <c r="AQ3" s="79"/>
+      <c r="AR3" s="79"/>
+      <c r="AS3" s="79"/>
+      <c r="AT3" s="79"/>
+      <c r="AU3" s="79"/>
+      <c r="AV3" s="79"/>
+      <c r="AW3" s="79"/>
+      <c r="AX3" s="79"/>
+      <c r="AY3" s="79"/>
+      <c r="AZ3" s="79"/>
+      <c r="BA3" s="79"/>
+      <c r="BB3" s="79"/>
+      <c r="BC3" s="79"/>
+      <c r="BD3" s="79"/>
+      <c r="BE3" s="79"/>
+      <c r="BF3" s="79"/>
+      <c r="BG3" s="79"/>
+      <c r="BH3" s="79"/>
+      <c r="BI3" s="79"/>
+      <c r="BJ3" s="79"/>
+      <c r="BK3" s="79"/>
+      <c r="BL3" s="79"/>
+      <c r="BM3" s="79"/>
+      <c r="BN3" s="79"/>
+      <c r="BO3" s="79"/>
+      <c r="BP3" s="79"/>
+      <c r="BQ3" s="79"/>
+      <c r="BR3" s="79"/>
+      <c r="BS3" s="79"/>
+      <c r="BT3" s="79"/>
+      <c r="BU3" s="79"/>
+      <c r="BV3" s="79"/>
+      <c r="BW3" s="79"/>
+      <c r="BX3" s="79"/>
+      <c r="BY3" s="79"/>
+      <c r="BZ3" s="79"/>
+      <c r="CA3" s="79"/>
+      <c r="CB3" s="79"/>
+      <c r="CC3" s="79"/>
+      <c r="CD3" s="79"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="82" customFormat="1">
+      <c r="A4" s="83"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="84"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="85"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="85"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
+      <c r="AH4" s="85"/>
+      <c r="AI4" s="85"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="85"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
+      <c r="AR4" s="85"/>
+      <c r="AS4" s="85"/>
+      <c r="AT4" s="85"/>
+      <c r="AU4" s="85"/>
+      <c r="AV4" s="85"/>
+      <c r="AW4" s="85"/>
+      <c r="AX4" s="85"/>
+      <c r="AY4" s="85"/>
+      <c r="AZ4" s="85"/>
+      <c r="BA4" s="85"/>
+      <c r="BB4" s="85"/>
+      <c r="BC4" s="85"/>
+      <c r="BD4" s="85"/>
+      <c r="BE4" s="85"/>
+      <c r="BF4" s="85"/>
+      <c r="BG4" s="85"/>
+      <c r="BH4" s="85"/>
+      <c r="BI4" s="85"/>
+      <c r="BJ4" s="85"/>
+      <c r="BK4" s="85"/>
+      <c r="BL4" s="85"/>
+      <c r="BM4" s="85"/>
+      <c r="BN4" s="85"/>
+      <c r="BO4" s="85"/>
+      <c r="BP4" s="85"/>
+      <c r="BQ4" s="85"/>
+      <c r="BR4" s="85"/>
+      <c r="BS4" s="85"/>
+      <c r="BT4" s="85"/>
+      <c r="BU4" s="85"/>
+      <c r="BV4" s="85"/>
+      <c r="BW4" s="85"/>
+      <c r="BX4" s="85"/>
+      <c r="BY4" s="85"/>
+      <c r="BZ4" s="85"/>
+      <c r="CA4" s="85"/>
+      <c r="CB4" s="85"/>
+      <c r="CC4" s="85"/>
+      <c r="CD4" s="85"/>
     </row>
     <row r="5" ht="9.75" customHeight="1">
       <c r="A5" s="10"/>
@@ -17615,7 +16705,7 @@
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10"/>
-      <c r="B6" s="88" t="e">
+      <c r="B6" s="86" t="e">
         <f>"L'EBITDA passe de "&amp;TEXT(C12,"#,##0 €")&amp;" à "&amp;TEXT(C18,"#,##0 €")&amp;", soit "&amp;TEXT(C18-C12,"+#,##0 €;-#,##0 €")&amp;"  ("&amp;TEXT(C18/C12-1,"+0.0%;-0.0%")&amp;")"</f>
         <v>#DIV/0!</v>
       </c>
@@ -17702,8 +16792,8 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="10"/>
-      <c r="B7" s="89" t="s">
-        <v>142</v>
+      <c r="B7" s="87" t="s">
+        <v>195</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -17956,12 +17046,12 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="10"/>
-      <c r="B10" s="90" t="s">
-        <v>143</v>
+      <c r="B10" s="88" t="s">
+        <v>196</v>
       </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="91" t="s">
-        <v>144</v>
+      <c r="D10" s="89" t="s">
+        <v>197</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -18044,14 +17134,14 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="10"/>
-      <c r="B11" s="92" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="93" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="93" t="s">
-        <v>147</v>
+      <c r="B11" s="90" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="91" t="s">
+        <v>199</v>
+      </c>
+      <c r="D11" s="91" t="s">
+        <v>200</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -18134,14 +17224,14 @@
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="10"/>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="95">
+      <c r="C12" s="93">
         <f>O43</f>
         <v>0</v>
       </c>
-      <c r="D12" s="96"/>
+      <c r="D12" s="94"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -18223,14 +17313,14 @@
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="10"/>
-      <c r="B13" s="97" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="98">
+      <c r="B13" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="96">
         <f>S43</f>
         <v>0</v>
       </c>
-      <c r="D13" s="99" t="str">
+      <c r="D13" s="97" t="str">
         <f>_xlfn.IFERROR(IF(C13&gt;0,C13/SUMIF(C13:C17,"&gt;0"),C13/SUMIF(C13:C17,"&lt;0")),"")</f>
         <v/>
       </c>
@@ -18315,14 +17405,14 @@
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="97" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="98">
+      <c r="B14" s="95" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="96">
         <f>T43</f>
         <v>0</v>
       </c>
-      <c r="D14" s="99" t="str">
+      <c r="D14" s="97" t="str">
         <f>_xlfn.IFERROR(IF(C14&gt;0,C14/SUMIF(C13:C17,"&gt;0"),C14/SUMIF(C13:C17,"&lt;0")),"")</f>
         <v/>
       </c>
@@ -18407,14 +17497,14 @@
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="10"/>
-      <c r="B15" s="97" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="98">
+      <c r="B15" s="95" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="96">
         <f>U43</f>
         <v>0</v>
       </c>
-      <c r="D15" s="99" t="str">
+      <c r="D15" s="97" t="str">
         <f>_xlfn.IFERROR(IF(C15&gt;0,C15/SUMIF(C13:C17,"&gt;0"),C15/SUMIF(C13:C17,"&lt;0")),"")</f>
         <v/>
       </c>
@@ -18499,14 +17589,14 @@
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="10"/>
-      <c r="B16" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="98">
+      <c r="B16" s="95" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="96">
         <f>V43</f>
         <v>0</v>
       </c>
-      <c r="D16" s="99" t="str">
+      <c r="D16" s="97" t="str">
         <f>_xlfn.IFERROR(IF(C16&gt;0,C16/SUMIF(C13:C17,"&gt;0"),C16/SUMIF(C13:C17,"&lt;0")),"")</f>
         <v/>
       </c>
@@ -18591,14 +17681,14 @@
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="10"/>
-      <c r="B17" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="98">
+      <c r="B17" s="95" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="96">
         <f>W43</f>
         <v>0</v>
       </c>
-      <c r="D17" s="99" t="str">
+      <c r="D17" s="97" t="str">
         <f>_xlfn.IFERROR(IF(C17&gt;0,C17/SUMIF(C13:C17,"&gt;0"),C17/SUMIF(C13:C17,"&lt;0")),"")</f>
         <v/>
       </c>
@@ -18683,14 +17773,14 @@
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="10"/>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="95">
+      <c r="C18" s="93">
         <f>P43</f>
         <v>0</v>
       </c>
-      <c r="D18" s="96"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -18772,14 +17862,14 @@
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="10"/>
-      <c r="B19" s="100" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="101">
+      <c r="B19" s="98" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="99">
         <f>SUMIF($C$13:$C$17,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="D19" s="102">
+      <c r="D19" s="100">
         <f>SUMIF(C13:C17,"&lt;0")</f>
         <v>0</v>
       </c>
@@ -18948,15 +18038,15 @@
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="10"/>
-      <c r="B21" s="103" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="104">
+      <c r="B21" s="101" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="102">
         <f>SUM(C13:C17)-(C18-C12)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="105" t="s">
-        <v>155</v>
+      <c r="D21" s="103" t="s">
+        <v>208</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -19830,7 +18920,7 @@
       <c r="W31" s="10"/>
       <c r="X31" s="10"/>
       <c r="Y31" s="10" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="Z31" s="10">
         <f>MIN(C12,C12+SUM(C13:C13))</f>
@@ -19927,7 +19017,7 @@
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
       <c r="Y32" s="10" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="Z32" s="10">
         <f>MIN(C12+SUM(C13:C13),C12+SUM(C13:C14))</f>
@@ -20024,7 +19114,7 @@
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
       <c r="Y33" s="10" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="Z33" s="10">
         <f>MIN(C12+SUM(C13:C14),C12+SUM(C13:C15))</f>
@@ -20121,7 +19211,7 @@
       <c r="W34" s="10"/>
       <c r="X34" s="10"/>
       <c r="Y34" s="10" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="Z34" s="10">
         <f>MIN(C12+SUM(C13:C15),C12+SUM(C13:C16))</f>
@@ -20218,7 +19308,7 @@
       <c r="W35" s="10"/>
       <c r="X35" s="10"/>
       <c r="Y35" s="10" t="s">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="Z35" s="10">
         <f>MIN(C12+SUM(C13:C16),C12+SUM(C13:C17))</f>
@@ -20722,8 +19812,8 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="B41" s="90" t="s">
-        <v>156</v>
+      <c r="B41" s="88" t="s">
+        <v>209</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -20738,19 +19828,19 @@
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
       <c r="O41" s="10"/>
-      <c r="P41" s="91" t="s">
-        <v>157</v>
+      <c r="P41" s="89" t="s">
+        <v>210</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
-      <c r="S41" s="90" t="s">
-        <v>158</v>
+      <c r="S41" s="88" t="s">
+        <v>211</v>
       </c>
       <c r="T41" s="10"/>
       <c r="U41" s="10"/>
       <c r="V41" s="10"/>
-      <c r="W41" s="91" t="s">
-        <v>159</v>
+      <c r="W41" s="89" t="s">
+        <v>212</v>
       </c>
       <c r="X41" s="10"/>
       <c r="Y41" s="10"/>
@@ -20814,67 +19904,67 @@
     </row>
     <row r="42" ht="20.25" customHeight="1">
       <c r="A42" s="10"/>
-      <c r="B42" s="92" t="s">
-        <v>160</v>
-      </c>
-      <c r="C42" s="93" t="s">
-        <v>161</v>
-      </c>
-      <c r="D42" s="93" t="s">
-        <v>162</v>
-      </c>
-      <c r="E42" s="93" t="s">
-        <v>163</v>
-      </c>
-      <c r="F42" s="93" t="s">
-        <v>164</v>
-      </c>
-      <c r="G42" s="93" t="s">
-        <v>165</v>
-      </c>
-      <c r="H42" s="93" t="s">
-        <v>166</v>
-      </c>
-      <c r="I42" s="93" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="93" t="s">
-        <v>168</v>
-      </c>
-      <c r="K42" s="93" t="s">
-        <v>169</v>
-      </c>
-      <c r="L42" s="93" t="s">
-        <v>170</v>
-      </c>
-      <c r="M42" s="93" t="s">
-        <v>171</v>
-      </c>
-      <c r="N42" s="93" t="s">
-        <v>172</v>
-      </c>
-      <c r="O42" s="93" t="s">
+      <c r="B42" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42" s="91" t="s">
+        <v>214</v>
+      </c>
+      <c r="D42" s="91" t="s">
+        <v>215</v>
+      </c>
+      <c r="E42" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="91" t="s">
+        <v>218</v>
+      </c>
+      <c r="H42" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="I42" s="91" t="s">
+        <v>220</v>
+      </c>
+      <c r="J42" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="K42" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="L42" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="M42" s="91" t="s">
+        <v>224</v>
+      </c>
+      <c r="N42" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="O42" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="P42" s="93" t="s">
+      <c r="P42" s="91" t="s">
         <v>42</v>
       </c>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
-      <c r="S42" s="92" t="s">
-        <v>148</v>
-      </c>
-      <c r="T42" s="93" t="s">
-        <v>149</v>
-      </c>
-      <c r="U42" s="93" t="s">
-        <v>150</v>
-      </c>
-      <c r="V42" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="W42" s="93" t="s">
-        <v>152</v>
+      <c r="S42" s="90" t="s">
+        <v>201</v>
+      </c>
+      <c r="T42" s="91" t="s">
+        <v>202</v>
+      </c>
+      <c r="U42" s="91" t="s">
+        <v>203</v>
+      </c>
+      <c r="V42" s="91" t="s">
+        <v>204</v>
+      </c>
+      <c r="W42" s="91" t="s">
+        <v>205</v>
       </c>
       <c r="X42" s="10"/>
       <c r="Y42" s="10"/>
@@ -20938,71 +20028,71 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="10"/>
-      <c r="B43" s="106" t="s">
-        <v>173</v>
-      </c>
-      <c r="C43" s="107">
+      <c r="B43" s="104" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" s="105">
         <f t="shared" si="3" ref="C43:W43">SUM(C44:C73)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="107">
+      <c r="D43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E43" s="107">
+      <c r="E43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F43" s="108" t="s">
-        <v>174</v>
-      </c>
-      <c r="G43" s="109"/>
-      <c r="H43" s="109"/>
-      <c r="I43" s="109"/>
-      <c r="J43" s="109"/>
-      <c r="K43" s="107">
+      <c r="F43" s="106" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" s="107"/>
+      <c r="H43" s="107"/>
+      <c r="I43" s="107"/>
+      <c r="J43" s="107"/>
+      <c r="K43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L43" s="107">
+      <c r="L43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M43" s="107">
+      <c r="M43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N43" s="107">
+      <c r="N43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O43" s="107">
+      <c r="O43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P43" s="107">
+      <c r="P43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
-      <c r="S43" s="107">
+      <c r="S43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T43" s="107">
+      <c r="T43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U43" s="107">
+      <c r="U43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V43" s="107">
+      <c r="V43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W43" s="107">
+      <c r="W43" s="105">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21068,15 +20158,15 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
-      <c r="B44" s="110"/>
+      <c r="B44" s="108"/>
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
       <c r="E44" s="56"/>
-      <c r="F44" s="111"/>
-      <c r="G44" s="111"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="111"/>
-      <c r="J44" s="111"/>
+      <c r="F44" s="109"/>
+      <c r="G44" s="109"/>
+      <c r="H44" s="109"/>
+      <c r="I44" s="109"/>
+      <c r="J44" s="109"/>
       <c r="K44" s="56"/>
       <c r="L44" s="56"/>
       <c r="M44" s="56"/>
@@ -21167,15 +20257,15 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
-      <c r="B45" s="110"/>
+      <c r="B45" s="108"/>
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="E45" s="56"/>
-      <c r="F45" s="111"/>
-      <c r="G45" s="111"/>
-      <c r="H45" s="111"/>
-      <c r="I45" s="111"/>
-      <c r="J45" s="111"/>
+      <c r="F45" s="109"/>
+      <c r="G45" s="109"/>
+      <c r="H45" s="109"/>
+      <c r="I45" s="109"/>
+      <c r="J45" s="109"/>
       <c r="K45" s="56"/>
       <c r="L45" s="56"/>
       <c r="M45" s="56"/>
@@ -21266,15 +20356,15 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
-      <c r="B46" s="110"/>
+      <c r="B46" s="108"/>
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="E46" s="56"/>
-      <c r="F46" s="111"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="111"/>
-      <c r="J46" s="111"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="109"/>
+      <c r="H46" s="109"/>
+      <c r="I46" s="109"/>
+      <c r="J46" s="109"/>
       <c r="K46" s="56"/>
       <c r="L46" s="56"/>
       <c r="M46" s="56"/>
@@ -21365,15 +20455,15 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
-      <c r="B47" s="110"/>
+      <c r="B47" s="108"/>
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="E47" s="56"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
+      <c r="F47" s="109"/>
+      <c r="G47" s="109"/>
+      <c r="H47" s="109"/>
+      <c r="I47" s="109"/>
+      <c r="J47" s="109"/>
       <c r="K47" s="56"/>
       <c r="L47" s="56"/>
       <c r="M47" s="56"/>
@@ -21464,15 +20554,15 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
-      <c r="B48" s="110"/>
+      <c r="B48" s="108"/>
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="E48" s="56"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
+      <c r="F48" s="109"/>
+      <c r="G48" s="109"/>
+      <c r="H48" s="109"/>
+      <c r="I48" s="109"/>
+      <c r="J48" s="109"/>
       <c r="K48" s="56"/>
       <c r="L48" s="56"/>
       <c r="M48" s="56"/>
@@ -21563,15 +20653,15 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="110"/>
+      <c r="B49" s="108"/>
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="E49" s="56"/>
-      <c r="F49" s="111"/>
-      <c r="G49" s="111"/>
-      <c r="H49" s="111"/>
-      <c r="I49" s="111"/>
-      <c r="J49" s="111"/>
+      <c r="F49" s="109"/>
+      <c r="G49" s="109"/>
+      <c r="H49" s="109"/>
+      <c r="I49" s="109"/>
+      <c r="J49" s="109"/>
       <c r="K49" s="56"/>
       <c r="L49" s="56"/>
       <c r="M49" s="56"/>
@@ -21662,15 +20752,15 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="110"/>
+      <c r="B50" s="108"/>
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="E50" s="56"/>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="111"/>
+      <c r="F50" s="109"/>
+      <c r="G50" s="109"/>
+      <c r="H50" s="109"/>
+      <c r="I50" s="109"/>
+      <c r="J50" s="109"/>
       <c r="K50" s="56"/>
       <c r="L50" s="56"/>
       <c r="M50" s="56"/>
@@ -21761,15 +20851,15 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="110"/>
+      <c r="B51" s="108"/>
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="E51" s="56"/>
-      <c r="F51" s="111"/>
-      <c r="G51" s="111"/>
-      <c r="H51" s="111"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="111"/>
+      <c r="F51" s="109"/>
+      <c r="G51" s="109"/>
+      <c r="H51" s="109"/>
+      <c r="I51" s="109"/>
+      <c r="J51" s="109"/>
       <c r="K51" s="56"/>
       <c r="L51" s="56"/>
       <c r="M51" s="56"/>
@@ -21860,15 +20950,15 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="110"/>
+      <c r="B52" s="108"/>
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="E52" s="56"/>
-      <c r="F52" s="111"/>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="111"/>
+      <c r="F52" s="109"/>
+      <c r="G52" s="109"/>
+      <c r="H52" s="109"/>
+      <c r="I52" s="109"/>
+      <c r="J52" s="109"/>
       <c r="K52" s="56"/>
       <c r="L52" s="56"/>
       <c r="M52" s="56"/>
@@ -21959,15 +21049,15 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
-      <c r="B53" s="110"/>
+      <c r="B53" s="108"/>
       <c r="C53" s="56"/>
       <c r="D53" s="56"/>
       <c r="E53" s="56"/>
-      <c r="F53" s="111"/>
-      <c r="G53" s="111"/>
-      <c r="H53" s="111"/>
-      <c r="I53" s="111"/>
-      <c r="J53" s="111"/>
+      <c r="F53" s="109"/>
+      <c r="G53" s="109"/>
+      <c r="H53" s="109"/>
+      <c r="I53" s="109"/>
+      <c r="J53" s="109"/>
       <c r="K53" s="56"/>
       <c r="L53" s="56"/>
       <c r="M53" s="56"/>
@@ -22058,15 +21148,15 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
-      <c r="B54" s="110"/>
+      <c r="B54" s="108"/>
       <c r="C54" s="56"/>
       <c r="D54" s="56"/>
       <c r="E54" s="56"/>
-      <c r="F54" s="111"/>
-      <c r="G54" s="111"/>
-      <c r="H54" s="111"/>
-      <c r="I54" s="111"/>
-      <c r="J54" s="111"/>
+      <c r="F54" s="109"/>
+      <c r="G54" s="109"/>
+      <c r="H54" s="109"/>
+      <c r="I54" s="109"/>
+      <c r="J54" s="109"/>
       <c r="K54" s="56"/>
       <c r="L54" s="56"/>
       <c r="M54" s="56"/>
@@ -22157,15 +21247,15 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
-      <c r="B55" s="110"/>
+      <c r="B55" s="108"/>
       <c r="C55" s="56"/>
       <c r="D55" s="56"/>
       <c r="E55" s="56"/>
-      <c r="F55" s="111"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111"/>
-      <c r="I55" s="111"/>
-      <c r="J55" s="111"/>
+      <c r="F55" s="109"/>
+      <c r="G55" s="109"/>
+      <c r="H55" s="109"/>
+      <c r="I55" s="109"/>
+      <c r="J55" s="109"/>
       <c r="K55" s="56"/>
       <c r="L55" s="56"/>
       <c r="M55" s="56"/>
@@ -22256,15 +21346,15 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="B56" s="110"/>
+      <c r="B56" s="108"/>
       <c r="C56" s="56"/>
       <c r="D56" s="56"/>
       <c r="E56" s="56"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
+      <c r="F56" s="109"/>
+      <c r="G56" s="109"/>
+      <c r="H56" s="109"/>
+      <c r="I56" s="109"/>
+      <c r="J56" s="109"/>
       <c r="K56" s="56"/>
       <c r="L56" s="56"/>
       <c r="M56" s="56"/>
@@ -22355,15 +21445,15 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
-      <c r="B57" s="110"/>
+      <c r="B57" s="108"/>
       <c r="C57" s="56"/>
       <c r="D57" s="56"/>
       <c r="E57" s="56"/>
-      <c r="F57" s="111"/>
-      <c r="G57" s="111"/>
-      <c r="H57" s="111"/>
-      <c r="I57" s="111"/>
-      <c r="J57" s="111"/>
+      <c r="F57" s="109"/>
+      <c r="G57" s="109"/>
+      <c r="H57" s="109"/>
+      <c r="I57" s="109"/>
+      <c r="J57" s="109"/>
       <c r="K57" s="56"/>
       <c r="L57" s="56"/>
       <c r="M57" s="56"/>
@@ -22454,15 +21544,15 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
-      <c r="B58" s="110"/>
+      <c r="B58" s="108"/>
       <c r="C58" s="56"/>
       <c r="D58" s="56"/>
       <c r="E58" s="56"/>
-      <c r="F58" s="111"/>
-      <c r="G58" s="111"/>
-      <c r="H58" s="111"/>
-      <c r="I58" s="111"/>
-      <c r="J58" s="111"/>
+      <c r="F58" s="109"/>
+      <c r="G58" s="109"/>
+      <c r="H58" s="109"/>
+      <c r="I58" s="109"/>
+      <c r="J58" s="109"/>
       <c r="K58" s="56"/>
       <c r="L58" s="56"/>
       <c r="M58" s="56"/>
@@ -22538,15 +21628,15 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
-      <c r="B59" s="110"/>
+      <c r="B59" s="108"/>
       <c r="C59" s="56"/>
       <c r="D59" s="56"/>
       <c r="E59" s="56"/>
-      <c r="F59" s="111"/>
-      <c r="G59" s="111"/>
-      <c r="H59" s="111"/>
-      <c r="I59" s="111"/>
-      <c r="J59" s="111"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="109"/>
+      <c r="J59" s="109"/>
       <c r="K59" s="56"/>
       <c r="L59" s="56"/>
       <c r="M59" s="56"/>
@@ -22622,15 +21712,15 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
-      <c r="B60" s="110"/>
+      <c r="B60" s="108"/>
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
       <c r="E60" s="56"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
       <c r="K60" s="56"/>
       <c r="L60" s="56"/>
       <c r="M60" s="56"/>
@@ -22706,15 +21796,15 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
-      <c r="B61" s="110"/>
+      <c r="B61" s="108"/>
       <c r="C61" s="56"/>
       <c r="D61" s="56"/>
       <c r="E61" s="56"/>
-      <c r="F61" s="111"/>
-      <c r="G61" s="111"/>
-      <c r="H61" s="111"/>
-      <c r="I61" s="111"/>
-      <c r="J61" s="111"/>
+      <c r="F61" s="109"/>
+      <c r="G61" s="109"/>
+      <c r="H61" s="109"/>
+      <c r="I61" s="109"/>
+      <c r="J61" s="109"/>
       <c r="K61" s="56"/>
       <c r="L61" s="56"/>
       <c r="M61" s="56"/>
@@ -22790,15 +21880,15 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
-      <c r="B62" s="110"/>
+      <c r="B62" s="108"/>
       <c r="C62" s="56"/>
       <c r="D62" s="56"/>
       <c r="E62" s="56"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="111"/>
-      <c r="I62" s="111"/>
-      <c r="J62" s="111"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="109"/>
+      <c r="I62" s="109"/>
+      <c r="J62" s="109"/>
       <c r="K62" s="56"/>
       <c r="L62" s="56"/>
       <c r="M62" s="56"/>
@@ -22874,15 +21964,15 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
-      <c r="B63" s="110"/>
+      <c r="B63" s="108"/>
       <c r="C63" s="56"/>
       <c r="D63" s="56"/>
       <c r="E63" s="56"/>
-      <c r="F63" s="111"/>
-      <c r="G63" s="111"/>
-      <c r="H63" s="111"/>
-      <c r="I63" s="111"/>
-      <c r="J63" s="111"/>
+      <c r="F63" s="109"/>
+      <c r="G63" s="109"/>
+      <c r="H63" s="109"/>
+      <c r="I63" s="109"/>
+      <c r="J63" s="109"/>
       <c r="K63" s="56"/>
       <c r="L63" s="56"/>
       <c r="M63" s="56"/>
@@ -22958,15 +22048,15 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="B64" s="110"/>
+      <c r="B64" s="108"/>
       <c r="C64" s="56"/>
       <c r="D64" s="56"/>
       <c r="E64" s="56"/>
-      <c r="F64" s="111"/>
-      <c r="G64" s="111"/>
-      <c r="H64" s="111"/>
-      <c r="I64" s="111"/>
-      <c r="J64" s="111"/>
+      <c r="F64" s="109"/>
+      <c r="G64" s="109"/>
+      <c r="H64" s="109"/>
+      <c r="I64" s="109"/>
+      <c r="J64" s="109"/>
       <c r="K64" s="56"/>
       <c r="L64" s="56"/>
       <c r="M64" s="56"/>
@@ -23042,15 +22132,15 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
-      <c r="B65" s="110"/>
+      <c r="B65" s="108"/>
       <c r="C65" s="56"/>
       <c r="D65" s="56"/>
       <c r="E65" s="56"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="109"/>
+      <c r="H65" s="109"/>
+      <c r="I65" s="109"/>
+      <c r="J65" s="109"/>
       <c r="K65" s="56"/>
       <c r="L65" s="56"/>
       <c r="M65" s="56"/>
@@ -23126,15 +22216,15 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
-      <c r="B66" s="110"/>
+      <c r="B66" s="108"/>
       <c r="C66" s="56"/>
       <c r="D66" s="56"/>
       <c r="E66" s="56"/>
-      <c r="F66" s="111"/>
-      <c r="G66" s="111"/>
-      <c r="H66" s="111"/>
-      <c r="I66" s="111"/>
-      <c r="J66" s="111"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="109"/>
+      <c r="H66" s="109"/>
+      <c r="I66" s="109"/>
+      <c r="J66" s="109"/>
       <c r="K66" s="56"/>
       <c r="L66" s="56"/>
       <c r="M66" s="56"/>
@@ -23210,15 +22300,15 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
-      <c r="B67" s="110"/>
+      <c r="B67" s="108"/>
       <c r="C67" s="56"/>
       <c r="D67" s="56"/>
       <c r="E67" s="56"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="111"/>
-      <c r="I67" s="111"/>
-      <c r="J67" s="111"/>
+      <c r="F67" s="109"/>
+      <c r="G67" s="109"/>
+      <c r="H67" s="109"/>
+      <c r="I67" s="109"/>
+      <c r="J67" s="109"/>
       <c r="K67" s="56"/>
       <c r="L67" s="56"/>
       <c r="M67" s="56"/>
@@ -23294,15 +22384,15 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
-      <c r="B68" s="110"/>
+      <c r="B68" s="108"/>
       <c r="C68" s="56"/>
       <c r="D68" s="56"/>
       <c r="E68" s="56"/>
-      <c r="F68" s="111"/>
-      <c r="G68" s="111"/>
-      <c r="H68" s="111"/>
-      <c r="I68" s="111"/>
-      <c r="J68" s="111"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="109"/>
+      <c r="H68" s="109"/>
+      <c r="I68" s="109"/>
+      <c r="J68" s="109"/>
       <c r="K68" s="56"/>
       <c r="L68" s="56"/>
       <c r="M68" s="56"/>
@@ -23378,15 +22468,15 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
-      <c r="B69" s="110"/>
+      <c r="B69" s="108"/>
       <c r="C69" s="56"/>
       <c r="D69" s="56"/>
       <c r="E69" s="56"/>
-      <c r="F69" s="111"/>
-      <c r="G69" s="111"/>
-      <c r="H69" s="111"/>
-      <c r="I69" s="111"/>
-      <c r="J69" s="111"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="109"/>
+      <c r="I69" s="109"/>
+      <c r="J69" s="109"/>
       <c r="K69" s="56"/>
       <c r="L69" s="56"/>
       <c r="M69" s="56"/>
@@ -23462,15 +22552,15 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
-      <c r="B70" s="110"/>
+      <c r="B70" s="108"/>
       <c r="C70" s="56"/>
       <c r="D70" s="56"/>
       <c r="E70" s="56"/>
-      <c r="F70" s="111"/>
-      <c r="G70" s="111"/>
-      <c r="H70" s="111"/>
-      <c r="I70" s="111"/>
-      <c r="J70" s="111"/>
+      <c r="F70" s="109"/>
+      <c r="G70" s="109"/>
+      <c r="H70" s="109"/>
+      <c r="I70" s="109"/>
+      <c r="J70" s="109"/>
       <c r="K70" s="56"/>
       <c r="L70" s="56"/>
       <c r="M70" s="56"/>
@@ -23546,15 +22636,15 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
-      <c r="B71" s="110"/>
+      <c r="B71" s="108"/>
       <c r="C71" s="56"/>
       <c r="D71" s="56"/>
       <c r="E71" s="56"/>
-      <c r="F71" s="111"/>
-      <c r="G71" s="111"/>
-      <c r="H71" s="111"/>
-      <c r="I71" s="111"/>
-      <c r="J71" s="111"/>
+      <c r="F71" s="109"/>
+      <c r="G71" s="109"/>
+      <c r="H71" s="109"/>
+      <c r="I71" s="109"/>
+      <c r="J71" s="109"/>
       <c r="K71" s="56"/>
       <c r="L71" s="56"/>
       <c r="M71" s="56"/>
@@ -23630,15 +22720,15 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
-      <c r="B72" s="110"/>
+      <c r="B72" s="108"/>
       <c r="C72" s="56"/>
       <c r="D72" s="56"/>
       <c r="E72" s="56"/>
-      <c r="F72" s="111"/>
-      <c r="G72" s="111"/>
-      <c r="H72" s="111"/>
-      <c r="I72" s="111"/>
-      <c r="J72" s="111"/>
+      <c r="F72" s="109"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="109"/>
+      <c r="I72" s="109"/>
+      <c r="J72" s="109"/>
       <c r="K72" s="56"/>
       <c r="L72" s="56"/>
       <c r="M72" s="56"/>
@@ -23714,15 +22804,15 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
-      <c r="B73" s="110"/>
+      <c r="B73" s="108"/>
       <c r="C73" s="56"/>
       <c r="D73" s="56"/>
       <c r="E73" s="56"/>
-      <c r="F73" s="111"/>
-      <c r="G73" s="111"/>
-      <c r="H73" s="111"/>
-      <c r="I73" s="111"/>
-      <c r="J73" s="111"/>
+      <c r="F73" s="109"/>
+      <c r="G73" s="109"/>
+      <c r="H73" s="109"/>
+      <c r="I73" s="109"/>
+      <c r="J73" s="109"/>
       <c r="K73" s="56"/>
       <c r="L73" s="56"/>
       <c r="M73" s="56"/>
@@ -23798,15 +22888,15 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="10"/>
-      <c r="B74" s="110"/>
+      <c r="B74" s="108"/>
       <c r="C74" s="56"/>
       <c r="D74" s="56"/>
       <c r="E74" s="56"/>
-      <c r="F74" s="111"/>
-      <c r="G74" s="111"/>
-      <c r="H74" s="111"/>
-      <c r="I74" s="111"/>
-      <c r="J74" s="111"/>
+      <c r="F74" s="109"/>
+      <c r="G74" s="109"/>
+      <c r="H74" s="109"/>
+      <c r="I74" s="109"/>
+      <c r="J74" s="109"/>
       <c r="K74" s="56"/>
       <c r="L74" s="56"/>
       <c r="M74" s="56"/>
@@ -23882,15 +22972,15 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="10"/>
-      <c r="B75" s="110"/>
+      <c r="B75" s="108"/>
       <c r="C75" s="56"/>
       <c r="D75" s="56"/>
       <c r="E75" s="56"/>
-      <c r="F75" s="111"/>
-      <c r="G75" s="111"/>
-      <c r="H75" s="111"/>
-      <c r="I75" s="111"/>
-      <c r="J75" s="111"/>
+      <c r="F75" s="109"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="109"/>
+      <c r="I75" s="109"/>
+      <c r="J75" s="109"/>
       <c r="K75" s="56"/>
       <c r="L75" s="56"/>
       <c r="M75" s="56"/>
@@ -23966,15 +23056,15 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="10"/>
-      <c r="B76" s="110"/>
+      <c r="B76" s="108"/>
       <c r="C76" s="56"/>
       <c r="D76" s="56"/>
       <c r="E76" s="56"/>
-      <c r="F76" s="111"/>
-      <c r="G76" s="111"/>
-      <c r="H76" s="111"/>
-      <c r="I76" s="111"/>
-      <c r="J76" s="111"/>
+      <c r="F76" s="109"/>
+      <c r="G76" s="109"/>
+      <c r="H76" s="109"/>
+      <c r="I76" s="109"/>
+      <c r="J76" s="109"/>
       <c r="K76" s="56"/>
       <c r="L76" s="56"/>
       <c r="M76" s="56"/>
@@ -24125,7 +23215,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{AF99AC78-4CD8-7018-174C-8768B1409108}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7C25B498-9ECC-0D5F-C52D-E508D543029E}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Z56"/>
   <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="9.00390625" customHeight="1"/>
   <cols>
@@ -24143,53 +23233,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="81"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
+      <c r="A1" s="79"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
     </row>
     <row r="2" ht="26.25" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
     </row>
     <row r="3" ht="23.25" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
     </row>
     <row r="4" ht="9.75" customHeight="1">
       <c r="A4" s="10"/>
@@ -24208,7 +23298,7 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="10"/>
-      <c r="B5" s="113" t="e">
+      <c r="B5" s="111" t="e">
         <f>"Sur "&amp;TEXT(F34,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(F35:F47),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(F34:F47),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(F34:F47)/F34,"0.0%")&amp;" du chiffre d'affaires."</f>
         <v>#DIV/0!</v>
       </c>
@@ -24226,8 +23316,8 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="10"/>
-      <c r="B6" s="89" t="s">
-        <v>177</v>
+      <c r="B6" s="87" t="s">
+        <v>230</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -24240,23 +23330,23 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="114" t="s">
-        <v>178</v>
-      </c>
-      <c r="O6" s="114" t="s">
-        <v>179</v>
-      </c>
-      <c r="P6" s="114" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q6" s="114" t="s">
-        <v>181</v>
-      </c>
-      <c r="R6" s="114" t="s">
-        <v>182</v>
-      </c>
-      <c r="S6" s="114" t="s">
-        <v>183</v>
+      <c r="N6" s="112" t="s">
+        <v>231</v>
+      </c>
+      <c r="O6" s="112" t="s">
+        <v>232</v>
+      </c>
+      <c r="P6" s="112" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q6" s="112" t="s">
+        <v>234</v>
+      </c>
+      <c r="R6" s="112" t="s">
+        <v>235</v>
+      </c>
+      <c r="S6" s="112" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="7" ht="8.25" customHeight="1">
@@ -24363,10 +23453,10 @@
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
-      <c r="V13" s="115"/>
-      <c r="W13" s="116"/>
-      <c r="X13" s="116"/>
-      <c r="Y13" s="116"/>
+      <c r="V13" s="113"/>
+      <c r="W13" s="114"/>
+      <c r="X13" s="114"/>
+      <c r="Y13" s="114"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="10"/>
@@ -24382,10 +23472,10 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="V14" s="116"/>
-      <c r="W14" s="116"/>
-      <c r="X14" s="116"/>
-      <c r="Y14" s="116"/>
+      <c r="V14" s="114"/>
+      <c r="W14" s="114"/>
+      <c r="X14" s="114"/>
+      <c r="Y14" s="114"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="10"/>
@@ -24644,15 +23734,15 @@
     </row>
     <row r="32" ht="20.25" customHeight="1">
       <c r="A32" s="10"/>
-      <c r="B32" s="90" t="s">
-        <v>184</v>
+      <c r="B32" s="88" t="s">
+        <v>237</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="91"/>
+      <c r="H32" s="89"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
@@ -24661,26 +23751,26 @@
     </row>
     <row r="33" ht="26.25" customHeight="1">
       <c r="A33" s="10"/>
-      <c r="B33" s="92" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="92" t="s">
-        <v>179</v>
-      </c>
-      <c r="D33" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="93" t="s">
-        <v>182</v>
-      </c>
-      <c r="F33" s="93" t="s">
-        <v>183</v>
-      </c>
-      <c r="G33" s="93" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" s="93" t="s">
-        <v>186</v>
+      <c r="B33" s="90" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" s="90" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="90" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="91" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" s="91" t="s">
+        <v>236</v>
+      </c>
+      <c r="G33" s="91" t="s">
+        <v>238</v>
+      </c>
+      <c r="H33" s="91" t="s">
+        <v>239</v>
       </c>
       <c r="I33" s="10"/>
       <c r="K33" t="s">
@@ -24693,26 +23783,26 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
-      <c r="B34" s="117" t="s">
-        <v>187</v>
-      </c>
-      <c r="C34" s="118" t="str">
+      <c r="B34" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="116" t="str">
         <f t="shared" si="0" ref="C34:C49">_xlfn.IFERROR(VLOOKUP($B34,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D34" s="110" t="str">
+      <c r="D34" s="108" t="str">
         <f t="shared" si="1" ref="D34:D49">_xlfn.IFERROR(VLOOKUP($B34,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E34" s="119">
+      <c r="E34" s="117">
         <f t="shared" si="2" ref="E34:E49">_xlfn.IFERROR(VLOOKUP($B34,$N$7:$S$28,5,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="119">
+      <c r="F34" s="117">
         <f t="shared" si="3" ref="F34:F49">_xlfn.IFERROR(VLOOKUP($B34,$N$7:$S$28,6,FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="120">
+      <c r="G34" s="118">
         <f t="shared" si="4" ref="G34:G49">F34-E34</f>
         <v>0</v>
       </c>
@@ -24729,26 +23819,26 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
-      <c r="B35" s="117" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="118" t="str">
+      <c r="B35" s="115" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D35" s="110" t="str">
+      <c r="D35" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E35" s="119">
+      <c r="E35" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F35" s="119">
+      <c r="F35" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G35" s="120">
+      <c r="G35" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -24765,26 +23855,26 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="B36" s="117" t="s">
-        <v>189</v>
-      </c>
-      <c r="C36" s="118" t="str">
+      <c r="B36" s="115" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D36" s="110" t="str">
+      <c r="D36" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E36" s="119">
+      <c r="E36" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F36" s="119">
+      <c r="F36" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G36" s="120">
+      <c r="G36" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -24801,26 +23891,26 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
-      <c r="B37" s="117" t="s">
-        <v>190</v>
-      </c>
-      <c r="C37" s="118" t="str">
+      <c r="B37" s="115" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D37" s="110" t="str">
+      <c r="D37" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E37" s="119">
+      <c r="E37" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F37" s="119">
+      <c r="F37" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G37" s="120">
+      <c r="G37" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -24845,26 +23935,26 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
-      <c r="B38" s="117" t="s">
-        <v>191</v>
-      </c>
-      <c r="C38" s="118" t="str">
+      <c r="B38" s="115" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D38" s="110" t="str">
+      <c r="D38" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E38" s="119">
+      <c r="E38" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F38" s="119">
+      <c r="F38" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G38" s="120">
+      <c r="G38" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -24889,26 +23979,26 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
-      <c r="B39" s="117" t="s">
-        <v>192</v>
-      </c>
-      <c r="C39" s="118" t="str">
+      <c r="B39" s="115" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D39" s="110" t="str">
+      <c r="D39" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E39" s="119">
+      <c r="E39" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F39" s="119">
+      <c r="F39" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G39" s="120">
+      <c r="G39" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -24933,26 +24023,26 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
-      <c r="B40" s="117" t="s">
-        <v>193</v>
-      </c>
-      <c r="C40" s="118" t="str">
+      <c r="B40" s="115" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D40" s="110" t="str">
+      <c r="D40" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E40" s="119">
+      <c r="E40" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F40" s="119">
+      <c r="F40" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G40" s="120">
+      <c r="G40" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -24977,26 +24067,26 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="B41" s="117" t="s">
-        <v>194</v>
-      </c>
-      <c r="C41" s="118" t="str">
+      <c r="B41" s="115" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D41" s="110" t="str">
+      <c r="D41" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E41" s="119">
+      <c r="E41" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F41" s="119">
+      <c r="F41" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G41" s="120">
+      <c r="G41" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25021,26 +24111,26 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
-      <c r="B42" s="117" t="s">
-        <v>195</v>
-      </c>
-      <c r="C42" s="118" t="str">
+      <c r="B42" s="115" t="s">
+        <v>248</v>
+      </c>
+      <c r="C42" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D42" s="110" t="str">
+      <c r="D42" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E42" s="119">
+      <c r="E42" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F42" s="119">
+      <c r="F42" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G42" s="120">
+      <c r="G42" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25065,26 +24155,26 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
-      <c r="B43" s="117" t="s">
-        <v>196</v>
-      </c>
-      <c r="C43" s="118" t="str">
+      <c r="B43" s="115" t="s">
+        <v>249</v>
+      </c>
+      <c r="C43" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D43" s="110" t="str">
+      <c r="D43" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E43" s="119">
+      <c r="E43" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F43" s="119">
+      <c r="F43" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G43" s="120">
+      <c r="G43" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25109,26 +24199,26 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
-      <c r="B44" s="117" t="s">
-        <v>197</v>
-      </c>
-      <c r="C44" s="118" t="str">
+      <c r="B44" s="115" t="s">
+        <v>250</v>
+      </c>
+      <c r="C44" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D44" s="110" t="str">
+      <c r="D44" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E44" s="119">
+      <c r="E44" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F44" s="119">
+      <c r="F44" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G44" s="120">
+      <c r="G44" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25153,26 +24243,26 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
-      <c r="B45" s="117" t="s">
-        <v>198</v>
-      </c>
-      <c r="C45" s="118" t="str">
+      <c r="B45" s="115" t="s">
+        <v>251</v>
+      </c>
+      <c r="C45" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D45" s="110" t="str">
+      <c r="D45" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E45" s="119">
+      <c r="E45" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F45" s="119">
+      <c r="F45" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G45" s="120">
+      <c r="G45" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25197,26 +24287,26 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
-      <c r="B46" s="117" t="s">
-        <v>199</v>
-      </c>
-      <c r="C46" s="118" t="str">
+      <c r="B46" s="115" t="s">
+        <v>252</v>
+      </c>
+      <c r="C46" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D46" s="110" t="str">
+      <c r="D46" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E46" s="119">
+      <c r="E46" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F46" s="119">
+      <c r="F46" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G46" s="120">
+      <c r="G46" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25241,26 +24331,26 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
-      <c r="B47" s="117" t="s">
-        <v>200</v>
-      </c>
-      <c r="C47" s="118" t="str">
+      <c r="B47" s="115" t="s">
+        <v>253</v>
+      </c>
+      <c r="C47" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D47" s="110" t="str">
+      <c r="D47" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E47" s="119">
+      <c r="E47" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F47" s="119">
+      <c r="F47" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G47" s="120">
+      <c r="G47" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25285,26 +24375,26 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="10"/>
-      <c r="B48" s="117" t="s">
-        <v>201</v>
-      </c>
-      <c r="C48" s="118" t="str">
+      <c r="B48" s="115" t="s">
+        <v>254</v>
+      </c>
+      <c r="C48" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D48" s="110" t="str">
+      <c r="D48" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E48" s="119">
+      <c r="E48" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F48" s="119">
+      <c r="F48" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G48" s="120">
+      <c r="G48" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25329,26 +24419,26 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="117" t="s">
-        <v>202</v>
-      </c>
-      <c r="C49" s="118" t="str">
+      <c r="B49" s="115" t="s">
+        <v>255</v>
+      </c>
+      <c r="C49" s="116" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D49" s="110" t="str">
+      <c r="D49" s="108" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E49" s="119">
+      <c r="E49" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F49" s="119">
+      <c r="F49" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G49" s="120">
+      <c r="G49" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -25388,23 +24478,23 @@
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="103" t="s">
-        <v>203</v>
-      </c>
-      <c r="C51" s="121"/>
-      <c r="D51" s="103" t="s">
-        <v>204</v>
-      </c>
-      <c r="E51" s="122">
+      <c r="B51" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="101" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51" s="120">
         <f t="shared" si="7" ref="E51:F51">SUM(E34:E49)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="122">
+      <c r="F51" s="120">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G51" s="121"/>
-      <c r="H51" s="121"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="119"/>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
@@ -25427,8 +24517,8 @@
       <c r="M52" s="10"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="B53" s="90" t="s">
-        <v>205</v>
+      <c r="B53" s="88" t="s">
+        <v>258</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
@@ -25438,58 +24528,58 @@
       <c r="H53" s="10"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="B54" s="123" t="s">
-        <v>206</v>
-      </c>
-      <c r="C54" s="124"/>
-      <c r="D54" s="124"/>
-      <c r="E54" s="125">
+      <c r="B54" s="121" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54" s="122"/>
+      <c r="D54" s="122"/>
+      <c r="E54" s="123">
         <f t="shared" si="8" ref="E54:F54">SUM(E34:E36)</f>
         <v>0</v>
       </c>
-      <c r="F54" s="125">
+      <c r="F54" s="123">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G54" s="124"/>
-      <c r="H54" s="124"/>
+      <c r="G54" s="122"/>
+      <c r="H54" s="122"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="B55" s="123" t="s">
-        <v>207</v>
-      </c>
-      <c r="C55" s="124"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="125">
+      <c r="B55" s="121" t="s">
+        <v>260</v>
+      </c>
+      <c r="C55" s="122"/>
+      <c r="D55" s="122"/>
+      <c r="E55" s="123">
         <f>SUM($X$14:$X$16)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="125">
+      <c r="F55" s="123">
         <f>SUM($Y$14:$Y$16)</f>
         <v>0</v>
       </c>
-      <c r="G55" s="124"/>
-      <c r="H55" s="124"/>
+      <c r="G55" s="122"/>
+      <c r="H55" s="122"/>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="B56" s="126" t="s">
-        <v>208</v>
-      </c>
-      <c r="C56" s="127"/>
-      <c r="D56" s="127"/>
-      <c r="E56" s="128">
+      <c r="B56" s="124" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="125"/>
+      <c r="D56" s="125"/>
+      <c r="E56" s="126">
         <f t="shared" si="9" ref="E56:F56">E54-E55</f>
         <v>0</v>
       </c>
-      <c r="F56" s="128">
+      <c r="F56" s="126">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G56" s="129" t="e">
+      <c r="G56" s="127" t="e">
         <f t="shared" si="10" ref="G56:H56">E56/E55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H56" s="129" t="e">
+      <c r="H56" s="127" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
@@ -25530,7 +24620,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0fad0871-01bd-4ab1-a142-bca86c617910}</x14:id>
+          <x14:id>{e9231f15-8284-4a96-9507-256527c5f336}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25547,7 +24637,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0fad0871-01bd-4ab1-a142-bca86c617910}">
+          <x14:cfRule type="dataBar" id="{e9231f15-8284-4a96-9507-256527c5f336}">
             <x14:dataBar minLength="0" maxLength="100" direction="leftToRight">
               <x14:color rgb="FFB8CFEC"/>
               <x14:cfvo type="num">

--- a/eduservices/SIMULATION_CORRIGE.xlsx
+++ b/eduservices/SIMULATION_CORRIGE.xlsx
@@ -12060,7 +12060,7 @@
         <v>112</v>
       </c>
       <c r="S13" s="74">
-        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M13,$M13+SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I13/SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M13,$M13*SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C13)*($D$13:$D$72=$D13)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T13" s="75">
         <f>IF(OR($C13="",COUNT($H13:$Q13)=0),"",IF($R13="Fermer","",$J13-$K13-$S13))</f>
@@ -12127,7 +12127,7 @@
         <v>115</v>
       </c>
       <c r="S14" s="74">
-        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M14,$M14+SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I14/SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M14,$M14*SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C14)*($D$13:$D$72=$D14)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T14" s="75">
         <f>IF(OR($C14="",COUNT($H14:$Q14)=0),"",IF($R14="Fermer","",$J14-$K14-$S14))</f>
@@ -12189,7 +12189,7 @@
         <v>115</v>
       </c>
       <c r="S15" s="74">
-        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M15,$M15+SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I15/SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M15,$M15*SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C15)*($D$13:$D$72=$D15)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T15" s="75">
         <f>IF(OR($C15="",COUNT($H15:$Q15)=0),"",IF($R15="Fermer","",$J15-$K15-$S15))</f>
@@ -12251,7 +12251,7 @@
         <v>112</v>
       </c>
       <c r="S16" s="74">
-        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M16,$M16+SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I16/SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M16,$M16*SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C16)*($D$13:$D$72=$D16)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T16" s="75">
         <f>IF(OR($C16="",COUNT($H16:$Q16)=0),"",IF($R16="Fermer","",$J16-$K16-$S16))</f>
@@ -12313,7 +12313,7 @@
         <v>115</v>
       </c>
       <c r="S17" s="74">
-        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M17,$M17+SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I17/SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M17,$M17*SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C17)*($D$13:$D$72=$D17)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T17" s="75">
         <f>IF(OR($C17="",COUNT($H17:$Q17)=0),"",IF($R17="Fermer","",$J17-$K17-$S17))</f>
@@ -12375,7 +12375,7 @@
         <v>115</v>
       </c>
       <c r="S18" s="74">
-        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M18,$M18+SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I18/SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M18,$M18*SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C18)*($D$13:$D$72=$D18)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T18" s="75">
         <f>IF(OR($C18="",COUNT($H18:$Q18)=0),"",IF($R18="Fermer","",$J18-$K18-$S18))</f>
@@ -12437,7 +12437,7 @@
         <v>112</v>
       </c>
       <c r="S19" s="74">
-        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M19,$M19+SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I19/SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M19,$M19*SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C19)*($D$13:$D$72=$D19)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T19" s="75">
         <f>IF(OR($C19="",COUNT($H19:$Q19)=0),"",IF($R19="Fermer","",$J19-$K19-$S19))</f>
@@ -12499,7 +12499,7 @@
         <v>115</v>
       </c>
       <c r="S20" s="74">
-        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M20,$M20+SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I20/SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M20,$M20*SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C20)*($D$13:$D$72=$D20)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T20" s="75">
         <f>IF(OR($C20="",COUNT($H20:$Q20)=0),"",IF($R20="Fermer","",$J20-$K20-$S20))</f>
@@ -12561,7 +12561,7 @@
         <v>115</v>
       </c>
       <c r="S21" s="74">
-        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M21,$M21+SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I21/SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M21,$M21*SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C21)*($D$13:$D$72=$D21)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T21" s="75">
         <f>IF(OR($C21="",COUNT($H21:$Q21)=0),"",IF($R21="Fermer","",$J21-$K21-$S21))</f>
@@ -12623,7 +12623,7 @@
         <v>112</v>
       </c>
       <c r="S22" s="74">
-        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M22,$M22+SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I22/SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M22,$M22*SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C22)*($D$13:$D$72=$D22)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T22" s="75">
         <f>IF(OR($C22="",COUNT($H22:$Q22)=0),"",IF($R22="Fermer","",$J22-$K22-$S22))</f>
@@ -12685,7 +12685,7 @@
         <v>115</v>
       </c>
       <c r="S23" s="74">
-        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M23,$M23+SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I23/SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M23,$M23*SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C23)*($D$13:$D$72=$D23)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T23" s="75">
         <f>IF(OR($C23="",COUNT($H23:$Q23)=0),"",IF($R23="Fermer","",$J23-$K23-$S23))</f>
@@ -12747,7 +12747,7 @@
         <v>115</v>
       </c>
       <c r="S24" s="74">
-        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M24,$M24+SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I24/SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M24,$M24*SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C24)*($D$13:$D$72=$D24)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T24" s="75">
         <f>IF(OR($C24="",COUNT($H24:$Q24)=0),"",IF($R24="Fermer","",$J24-$K24-$S24))</f>
@@ -12809,7 +12809,7 @@
         <v>112</v>
       </c>
       <c r="S25" s="74">
-        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M25,$M25+SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I25/SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M25,$M25*SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C25)*($D$13:$D$72=$D25)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T25" s="75">
         <f>IF(OR($C25="",COUNT($H25:$Q25)=0),"",IF($R25="Fermer","",$J25-$K25-$S25))</f>
@@ -12871,7 +12871,7 @@
         <v>115</v>
       </c>
       <c r="S26" s="74">
-        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M26,$M26+SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I26/SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M26,$M26*SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C26)*($D$13:$D$72=$D26)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T26" s="75">
         <f>IF(OR($C26="",COUNT($H26:$Q26)=0),"",IF($R26="Fermer","",$J26-$K26-$S26))</f>
@@ -12933,7 +12933,7 @@
         <v>112</v>
       </c>
       <c r="S27" s="74">
-        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M27,$M27+SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I27/SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M27,$M27*SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C27)*($D$13:$D$72=$D27)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T27" s="75">
         <f>IF(OR($C27="",COUNT($H27:$Q27)=0),"",IF($R27="Fermer","",$J27-$K27-$S27))</f>
@@ -12995,7 +12995,7 @@
         <v>115</v>
       </c>
       <c r="S28" s="74">
-        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M28,$M28+SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I28/SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M28,$M28*SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C28)*($D$13:$D$72=$D28)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T28" s="75">
         <f>IF(OR($C28="",COUNT($H28:$Q28)=0),"",IF($R28="Fermer","",$J28-$K28-$S28))</f>
@@ -13057,7 +13057,7 @@
         <v>115</v>
       </c>
       <c r="S29" s="74">
-        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M29,$M29+SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I29/SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M29,$M29*SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C29)*($D$13:$D$72=$D29)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T29" s="75">
         <f>IF(OR($C29="",COUNT($H29:$Q29)=0),"",IF($R29="Fermer","",$J29-$K29-$S29))</f>
@@ -13119,7 +13119,7 @@
         <v>112</v>
       </c>
       <c r="S30" s="74">
-        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M30,$M30+SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I30/SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M30,$M30*SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C30)*($D$13:$D$72=$D30)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T30" s="75">
         <f>IF(OR($C30="",COUNT($H30:$Q30)=0),"",IF($R30="Fermer","",$J30-$K30-$S30))</f>
@@ -13181,7 +13181,7 @@
         <v>115</v>
       </c>
       <c r="S31" s="74">
-        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M31,$M31+SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I31/SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M31,$M31*SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C31)*($D$13:$D$72=$D31)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T31" s="75">
         <f>IF(OR($C31="",COUNT($H31:$Q31)=0),"",IF($R31="Fermer","",$J31-$K31-$S31))</f>
@@ -13243,7 +13243,7 @@
         <v>112</v>
       </c>
       <c r="S32" s="74">
-        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M32,$M32+SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I32/SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M32,$M32*SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C32)*($D$13:$D$72=$D32)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T32" s="75">
         <f>IF(OR($C32="",COUNT($H32:$Q32)=0),"",IF($R32="Fermer","",$J32-$K32-$S32))</f>
@@ -13305,7 +13305,7 @@
         <v>115</v>
       </c>
       <c r="S33" s="74">
-        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M33,$M33+SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I33/SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M33,$M33*SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C33)*($D$13:$D$72=$D33)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T33" s="75">
         <f>IF(OR($C33="",COUNT($H33:$Q33)=0),"",IF($R33="Fermer","",$J33-$K33-$S33))</f>
@@ -13367,7 +13367,7 @@
         <v>115</v>
       </c>
       <c r="S34" s="74">
-        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M34,$M34+SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I34/SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M34,$M34*SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C34)*($D$13:$D$72=$D34)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T34" s="75">
         <f>IF(OR($C34="",COUNT($H34:$Q34)=0),"",IF($R34="Fermer","",$J34-$K34-$S34))</f>
@@ -13429,7 +13429,7 @@
         <v>112</v>
       </c>
       <c r="S35" s="74">
-        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M35,$M35+SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I35/SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M35,$M35*SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C35)*($D$13:$D$72=$D35)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T35" s="75">
         <f>IF(OR($C35="",COUNT($H35:$Q35)=0),"",IF($R35="Fermer","",$J35-$K35-$S35))</f>
@@ -13491,7 +13491,7 @@
         <v>115</v>
       </c>
       <c r="S36" s="74">
-        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M36,$M36+SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I36/SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M36,$M36*SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C36)*($D$13:$D$72=$D36)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T36" s="75">
         <f>IF(OR($C36="",COUNT($H36:$Q36)=0),"",IF($R36="Fermer","",$J36-$K36-$S36))</f>
@@ -13553,7 +13553,7 @@
         <v>112</v>
       </c>
       <c r="S37" s="74">
-        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M37,$M37+SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I37/SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M37,$M37*SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C37)*($D$13:$D$72=$D37)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T37" s="75">
         <f>IF(OR($C37="",COUNT($H37:$Q37)=0),"",IF($R37="Fermer","",$J37-$K37-$S37))</f>
@@ -13616,7 +13616,7 @@
         <v>115</v>
       </c>
       <c r="S38" s="74">
-        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M38,$M38+SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I38/SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M38,$M38*SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C38)*($D$13:$D$72=$D38)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T38" s="75">
         <f>IF(OR($C38="",COUNT($H38:$Q38)=0),"",IF($R38="Fermer","",$J38-$K38-$S38))</f>
@@ -13688,7 +13688,7 @@
         <v>115</v>
       </c>
       <c r="S39" s="74">
-        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M39,$M39+SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I39/SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M39,$M39*SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C39)*($D$13:$D$72=$D39)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T39" s="75">
         <f>IF(OR($C39="",COUNT($H39:$Q39)=0),"",IF($R39="Fermer","",$J39-$K39-$S39))</f>
@@ -13760,7 +13760,7 @@
         <v>112</v>
       </c>
       <c r="S40" s="74">
-        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M40,$M40+SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I40/SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M40,$M40*SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C40)*($D$13:$D$72=$D40)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T40" s="75">
         <f>IF(OR($C40="",COUNT($H40:$Q40)=0),"",IF($R40="Fermer","",$J40-$K40-$S40))</f>
@@ -13832,7 +13832,7 @@
         <v>115</v>
       </c>
       <c r="S41" s="74">
-        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M41,$M41+SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I41/SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M41,$M41*SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C41)*($D$13:$D$72=$D41)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T41" s="75">
         <f>IF(OR($C41="",COUNT($H41:$Q41)=0),"",IF($R41="Fermer","",$J41-$K41-$S41))</f>
@@ -13904,7 +13904,7 @@
         <v>112</v>
       </c>
       <c r="S42" s="74">
-        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M42,$M42+SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I42/SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M42,$M42*SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C42)*($D$13:$D$72=$D42)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T42" s="75">
         <f>IF(OR($C42="",COUNT($H42:$Q42)=0),"",IF($R42="Fermer","",$J42-$K42-$S42))</f>
@@ -13976,7 +13976,7 @@
         <v>115</v>
       </c>
       <c r="S43" s="74">
-        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M43,$M43+SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I43/SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M43,$M43*SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C43)*($D$13:$D$72=$D43)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T43" s="75">
         <f>IF(OR($C43="",COUNT($H43:$Q43)=0),"",IF($R43="Fermer","",$J43-$K43-$S43))</f>
@@ -14048,7 +14048,7 @@
         <v>115</v>
       </c>
       <c r="S44" s="74">
-        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M44,$M44+SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I44/SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M44,$M44*SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C44)*($D$13:$D$72=$D44)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T44" s="75">
         <f>IF(OR($C44="",COUNT($H44:$Q44)=0),"",IF($R44="Fermer","",$J44-$K44-$S44))</f>
@@ -14120,7 +14120,7 @@
         <v>112</v>
       </c>
       <c r="S45" s="74">
-        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M45,$M45+SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I45/SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M45,$M45*SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C45)*($D$13:$D$72=$D45)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T45" s="75">
         <f>IF(OR($C45="",COUNT($H45:$Q45)=0),"",IF($R45="Fermer","",$J45-$K45-$S45))</f>
@@ -14192,7 +14192,7 @@
         <v>115</v>
       </c>
       <c r="S46" s="74">
-        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M46,$M46+SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I46/SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M46,$M46*SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C46)*($D$13:$D$72=$D46)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T46" s="75">
         <f>IF(OR($C46="",COUNT($H46:$Q46)=0),"",IF($R46="Fermer","",$J46-$K46-$S46))</f>
@@ -14264,7 +14264,7 @@
         <v>112</v>
       </c>
       <c r="S47" s="74">
-        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M47,$M47+SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I47/SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M47,$M47*SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C47)*($D$13:$D$72=$D47)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T47" s="75">
         <f>IF(OR($C47="",COUNT($H47:$Q47)=0),"",IF($R47="Fermer","",$J47-$K47-$S47))</f>
@@ -14336,7 +14336,7 @@
         <v>115</v>
       </c>
       <c r="S48" s="74">
-        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M48,$M48+SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I48/SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M48,$M48*SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C48)*($D$13:$D$72=$D48)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T48" s="75">
         <f>IF(OR($C48="",COUNT($H48:$Q48)=0),"",IF($R48="Fermer","",$J48-$K48-$S48))</f>
@@ -14408,7 +14408,7 @@
         <v>115</v>
       </c>
       <c r="S49" s="74">
-        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M49,$M49+SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I49/SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M49,$M49*SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C49)*($D$13:$D$72=$D49)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T49" s="75">
         <f>IF(OR($C49="",COUNT($H49:$Q49)=0),"",IF($R49="Fermer","",$J49-$K49-$S49))</f>
@@ -14480,7 +14480,7 @@
         <v>112</v>
       </c>
       <c r="S50" s="74">
-        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M50,$M50+SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I50/SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M50,$M50*SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C50)*($D$13:$D$72=$D50)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T50" s="75">
         <f>IF(OR($C50="",COUNT($H50:$Q50)=0),"",IF($R50="Fermer","",$J50-$K50-$S50))</f>
@@ -14552,7 +14552,7 @@
         <v>115</v>
       </c>
       <c r="S51" s="74">
-        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M51,$M51+SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I51/SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M51,$M51*SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C51)*($D$13:$D$72=$D51)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T51" s="75">
         <f>IF(OR($C51="",COUNT($H51:$Q51)=0),"",IF($R51="Fermer","",$J51-$K51-$S51))</f>
@@ -14624,7 +14624,7 @@
         <v>112</v>
       </c>
       <c r="S52" s="74">
-        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M52,$M52+SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I52/SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M52,$M52*SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C52)*($D$13:$D$72=$D52)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T52" s="75">
         <f>IF(OR($C52="",COUNT($H52:$Q52)=0),"",IF($R52="Fermer","",$J52-$K52-$S52))</f>
@@ -14696,7 +14696,7 @@
         <v>115</v>
       </c>
       <c r="S53" s="74">
-        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M53,$M53+SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I53/SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M53,$M53*SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C53)*($D$13:$D$72=$D53)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T53" s="75">
         <f>IF(OR($C53="",COUNT($H53:$Q53)=0),"",IF($R53="Fermer","",$J53-$K53-$S53))</f>
@@ -14768,7 +14768,7 @@
         <v>115</v>
       </c>
       <c r="S54" s="74">
-        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M54,$M54+SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I54/SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M54,$M54*SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C54)*($D$13:$D$72=$D54)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T54" s="75">
         <f>IF(OR($C54="",COUNT($H54:$Q54)=0),"",IF($R54="Fermer","",$J54-$K54-$S54))</f>
@@ -14840,7 +14840,7 @@
         <v>112</v>
       </c>
       <c r="S55" s="74">
-        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M55,$M55+SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I55/SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M55,$M55*SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C55)*($D$13:$D$72=$D55)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T55" s="75">
         <f>IF(OR($C55="",COUNT($H55:$Q55)=0),"",IF($R55="Fermer","",$J55-$K55-$S55))</f>
@@ -14912,7 +14912,7 @@
         <v>115</v>
       </c>
       <c r="S56" s="74">
-        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M56,$M56+SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I56/SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M56,$M56*SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C56)*($D$13:$D$72=$D56)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T56" s="75">
         <f>IF(OR($C56="",COUNT($H56:$Q56)=0),"",IF($R56="Fermer","",$J56-$K56-$S56))</f>
@@ -14984,7 +14984,7 @@
         <v>112</v>
       </c>
       <c r="S57" s="74">
-        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M57,$M57+SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I57/SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M57,$M57*SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C57)*($D$13:$D$72=$D57)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T57" s="75">
         <f>IF(OR($C57="",COUNT($H57:$Q57)=0),"",IF($R57="Fermer","",$J57-$K57-$S57))</f>
@@ -15056,7 +15056,7 @@
         <v>115</v>
       </c>
       <c r="S58" s="74">
-        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M58,$M58+SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I58/SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M58,$M58*SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C58)*($D$13:$D$72=$D58)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T58" s="75">
         <f>IF(OR($C58="",COUNT($H58:$Q58)=0),"",IF($R58="Fermer","",$J58-$K58-$S58))</f>
@@ -15128,7 +15128,7 @@
         <v>112</v>
       </c>
       <c r="S59" s="74">
-        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M59,$M59+SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I59/SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M59,$M59*SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C59)*($D$13:$D$72=$D59)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T59" s="75">
         <f>IF(OR($C59="",COUNT($H59:$Q59)=0),"",IF($R59="Fermer","",$J59-$K59-$S59))</f>
@@ -15200,7 +15200,7 @@
         <v>115</v>
       </c>
       <c r="S60" s="74">
-        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M60,$M60+SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I60/SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M60,$M60*SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C60)*($D$13:$D$72=$D60)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T60" s="75">
         <f>IF(OR($C60="",COUNT($H60:$Q60)=0),"",IF($R60="Fermer","",$J60-$K60-$S60))</f>
@@ -15263,7 +15263,7 @@
         <v>115</v>
       </c>
       <c r="S61" s="74">
-        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M61,$M61+SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I61/SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M61,$M61*SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C61)*($D$13:$D$72=$D61)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T61" s="75">
         <f>IF(OR($C61="",COUNT($H61:$Q61)=0),"",IF($R61="Fermer","",$J61-$K61-$S61))</f>
@@ -15326,7 +15326,7 @@
         <v>115</v>
       </c>
       <c r="S62" s="74">
-        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M62,$M62+SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I62/SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M62,$M62*SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C62)*($D$13:$D$72=$D62)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T62" s="75">
         <f>IF(OR($C62="",COUNT($H62:$Q62)=0),"",IF($R62="Fermer","",$J62-$K62-$S62))</f>
@@ -15389,7 +15389,7 @@
         <v>115</v>
       </c>
       <c r="S63" s="74">
-        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M63,$M63+SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I63/SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M63,$M63*SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C63)*($D$13:$D$72=$D63)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T63" s="75">
         <f>IF(OR($C63="",COUNT($H63:$Q63)=0),"",IF($R63="Fermer","",$J63-$K63-$S63))</f>
@@ -15452,7 +15452,7 @@
         <v>112</v>
       </c>
       <c r="S64" s="74">
-        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M64,$M64+SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I64/SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M64,$M64*SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C64)*($D$13:$D$72=$D64)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T64" s="75">
         <f>IF(OR($C64="",COUNT($H64:$Q64)=0),"",IF($R64="Fermer","",$J64-$K64-$S64))</f>
@@ -15515,7 +15515,7 @@
         <v>115</v>
       </c>
       <c r="S65" s="74">
-        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M65,$M65+SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I65/SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M65,$M65*SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C65)*($D$13:$D$72=$D65)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T65" s="75">
         <f>IF(OR($C65="",COUNT($H65:$Q65)=0),"",IF($R65="Fermer","",$J65-$K65-$S65))</f>
@@ -15578,7 +15578,7 @@
         <v>112</v>
       </c>
       <c r="S66" s="74">
-        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M66,$M66+SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I66/SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M66,$M66*SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C66)*($D$13:$D$72=$D66)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T66" s="75">
         <f>IF(OR($C66="",COUNT($H66:$Q66)=0),"",IF($R66="Fermer","",$J66-$K66-$S66))</f>
@@ -15641,7 +15641,7 @@
         <v>112</v>
       </c>
       <c r="S67" s="74">
-        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M67,$M67+SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I67/SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M67,$M67*SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C67)*($D$13:$D$72=$D67)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T67" s="75">
         <f>IF(OR($C67="",COUNT($H67:$Q67)=0),"",IF($R67="Fermer","",$J67-$K67-$S67))</f>
@@ -15704,7 +15704,7 @@
         <v>115</v>
       </c>
       <c r="S68" s="74">
-        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M68,$M68+SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I68/SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M68,$M68*SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C68)*($D$13:$D$72=$D68)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T68" s="75">
         <f>IF(OR($C68="",COUNT($H68:$Q68)=0),"",IF($R68="Fermer","",$J68-$K68-$S68))</f>
@@ -15767,7 +15767,7 @@
         <v>115</v>
       </c>
       <c r="S69" s="74">
-        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M69,$M69+SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I69/SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M69,$M69*SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C69)*($D$13:$D$72=$D69)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T69" s="75">
         <f>IF(OR($C69="",COUNT($H69:$Q69)=0),"",IF($R69="Fermer","",$J69-$K69-$S69))</f>
@@ -15830,7 +15830,7 @@
         <v>112</v>
       </c>
       <c r="S70" s="74">
-        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M70,$M70+SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I70/SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M70,$M70*SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C70)*($D$13:$D$72=$D70)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T70" s="75">
         <f>IF(OR($C70="",COUNT($H70:$Q70)=0),"",IF($R70="Fermer","",$J70-$K70-$S70))</f>
@@ -15893,7 +15893,7 @@
         <v>115</v>
       </c>
       <c r="S71" s="74">
-        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M71,$M71+SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I71/SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M71,$M71*SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C71)*($D$13:$D$72=$D71)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T71" s="75">
         <f>IF(OR($C71="",COUNT($H71:$Q71)=0),"",IF($R71="Fermer","",$J71-$K71-$S71))</f>
@@ -15956,7 +15956,7 @@
         <v>115</v>
       </c>
       <c r="S72" s="74">
-        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72)=0,$M72,$M72+SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72="Fermer"),$M$13:$M$72)*$I72/SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72&lt;&gt;"Fermer"),$I$13:$I$72))))</f>
+        <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",IF(SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72)=0,$M72,$M72*SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72),$M$13:$M$72)/SUMPRODUCT(($C$13:$C$72=$C72)*($D$13:$D$72=$D72)*($R$13:$R$72&lt;&gt;"Fermer"),$M$13:$M$72))))</f>
       </c>
       <c r="T72" s="75">
         <f>IF(OR($C72="",COUNT($H72:$Q72)=0),"",IF($R72="Fermer","",$J72-$K72-$S72))</f>
